--- a/LogoJ_Platform_Rest_Test/bin/Debug/Template/Muhasebe Mahsup Fisi.xlsx
+++ b/LogoJ_Platform_Rest_Test/bin/Debug/Template/Muhasebe Mahsup Fisi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DOGUKAN\source\repos\LogoJ_Platform_Rest_Test\LogoJ_Platform_Rest_Test\bin\Debug\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD14FC99-7588-4BB3-A466-6FE6CF081BD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBD88725-DA3D-422C-9160-514619BC891A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9711E6CE-5FD9-4707-B709-915BBF0C49A5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9711E6CE-5FD9-4707-B709-915BBF0C49A5}"/>
   </bookViews>
   <sheets>
     <sheet name="Muhasebe Fişi" sheetId="3" r:id="rId1"/>
@@ -303,13 +303,13 @@
     <t>GBP</t>
   </si>
   <si>
-    <t>C</t>
-  </si>
-  <si>
     <t>01</t>
   </si>
   <si>
     <t>H</t>
+  </si>
+  <si>
+    <t>AHMET</t>
   </si>
 </sst>
 </file>
@@ -931,28 +931,28 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:R472"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="29.7109375" customWidth="1"/>
-    <col min="5" max="5" width="61.7109375" customWidth="1"/>
-    <col min="6" max="6" width="26.5703125" customWidth="1"/>
-    <col min="7" max="7" width="26.28515625" customWidth="1"/>
+    <col min="1" max="1" width="19.109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" customWidth="1"/>
+    <col min="3" max="3" width="20.88671875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="29.6640625" customWidth="1"/>
+    <col min="5" max="5" width="61.6640625" customWidth="1"/>
+    <col min="6" max="6" width="26.5546875" customWidth="1"/>
+    <col min="7" max="7" width="26.33203125" customWidth="1"/>
     <col min="8" max="8" width="27" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.42578125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.44140625" style="3" customWidth="1"/>
     <col min="11" max="11" width="18" style="3" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="61.140625" customWidth="1"/>
-    <col min="15" max="15" width="28.85546875" customWidth="1"/>
-    <col min="16" max="16" width="64.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="61.109375" customWidth="1"/>
+    <col min="15" max="15" width="28.88671875" customWidth="1"/>
+    <col min="16" max="16" width="64.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
         <v>16</v>
       </c>
@@ -1005,17 +1005,19 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C2" s="1">
         <v>45879</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="E2" s="22"/>
       <c r="G2" s="4" t="s">
         <v>29</v>
@@ -1043,12 +1045,12 @@
       <c r="P2" s="22"/>
       <c r="Q2" s="19"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C3" s="1">
         <v>45879</v>
@@ -1056,7 +1058,7 @@
       <c r="D3" s="2"/>
       <c r="E3" s="22"/>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>33</v>
@@ -1083,22 +1085,20 @@
       <c r="P3" s="22"/>
       <c r="Q3" s="19"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C4" s="1">
         <v>45879</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="22" t="s">
-        <v>52</v>
-      </c>
+      <c r="E4" s="22"/>
       <c r="F4" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>31</v>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="Q4" s="19"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C5" s="1">
         <v>45879</v>
@@ -1160,12 +1160,12 @@
       <c r="P5" s="22"/>
       <c r="Q5" s="19"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C6" s="1">
         <v>45879</v>
@@ -1195,12 +1195,12 @@
       <c r="P6" s="22"/>
       <c r="Q6" s="19"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C7" s="1">
         <v>45879</v>
@@ -1230,12 +1230,12 @@
       <c r="P7" s="22"/>
       <c r="Q7" s="19"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C8" s="1">
         <v>45879</v>
@@ -1265,12 +1265,12 @@
       <c r="P8" s="22"/>
       <c r="Q8" s="19"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C9" s="1">
         <v>45879</v>
@@ -1300,12 +1300,12 @@
       <c r="P9" s="22"/>
       <c r="Q9" s="19"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C10" s="1">
         <v>45879</v>
@@ -1335,12 +1335,12 @@
       <c r="P10" s="22"/>
       <c r="Q10" s="19"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C11" s="1">
         <v>45879</v>
@@ -1370,12 +1370,12 @@
       <c r="P11" s="22"/>
       <c r="Q11" s="19"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C12" s="1">
         <v>45879</v>
@@ -1405,12 +1405,12 @@
       <c r="P12" s="22"/>
       <c r="Q12" s="19"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C13" s="1">
         <v>45879</v>
@@ -1440,12 +1440,12 @@
       <c r="P13" s="22"/>
       <c r="Q13" s="19"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C14" s="1">
         <v>45879</v>
@@ -1475,12 +1475,12 @@
       <c r="P14" s="22"/>
       <c r="Q14" s="19"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C15" s="1">
         <v>45879</v>
@@ -1510,12 +1510,12 @@
       <c r="P15" s="22"/>
       <c r="Q15" s="19"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C16" s="1">
         <v>45879</v>
@@ -1545,12 +1545,12 @@
       <c r="P16" s="22"/>
       <c r="Q16" s="19"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C17" s="1">
         <v>45879</v>
@@ -1580,12 +1580,12 @@
       <c r="P17" s="22"/>
       <c r="Q17" s="19"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C18" s="1">
         <v>45879</v>
@@ -1615,12 +1615,12 @@
       <c r="P18" s="22"/>
       <c r="Q18" s="19"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C19" s="1">
         <v>45879</v>
@@ -1650,12 +1650,12 @@
       <c r="P19" s="22"/>
       <c r="Q19" s="19"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C20" s="1">
         <v>45879</v>
@@ -1685,12 +1685,12 @@
       <c r="P20" s="22"/>
       <c r="Q20" s="19"/>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C21" s="1">
         <v>45879</v>
@@ -1720,12 +1720,12 @@
       <c r="P21" s="22"/>
       <c r="Q21" s="19"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C22" s="1">
         <v>45879</v>
@@ -1755,12 +1755,12 @@
       <c r="P22" s="22"/>
       <c r="Q22" s="19"/>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C23" s="1">
         <v>45879</v>
@@ -1790,12 +1790,12 @@
       <c r="P23" s="22"/>
       <c r="Q23" s="19"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C24" s="1">
         <v>45879</v>
@@ -1825,12 +1825,12 @@
       <c r="P24" s="22"/>
       <c r="Q24" s="19"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C25" s="1">
         <v>45879</v>
@@ -1860,12 +1860,12 @@
       <c r="P25" s="22"/>
       <c r="Q25" s="19"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C26" s="1">
         <v>45879</v>
@@ -1895,12 +1895,12 @@
       <c r="P26" s="22"/>
       <c r="Q26" s="19"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C27" s="1">
         <v>45879</v>
@@ -1930,12 +1930,12 @@
       <c r="P27" s="22"/>
       <c r="Q27" s="19"/>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C28" s="1">
         <v>45879</v>
@@ -1965,12 +1965,12 @@
       <c r="P28" s="22"/>
       <c r="Q28" s="19"/>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C29" s="1">
         <v>45879</v>
@@ -2000,12 +2000,12 @@
       <c r="P29" s="22"/>
       <c r="Q29" s="19"/>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C30" s="1">
         <v>45879</v>
@@ -2035,12 +2035,12 @@
       <c r="P30" s="22"/>
       <c r="Q30" s="19"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C31" s="1">
         <v>45879</v>
@@ -2070,12 +2070,12 @@
       <c r="P31" s="22"/>
       <c r="Q31" s="19"/>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C32" s="1">
         <v>45879</v>
@@ -2105,12 +2105,12 @@
       <c r="P32" s="22"/>
       <c r="Q32" s="19"/>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C33" s="1">
         <v>45879</v>
@@ -2141,12 +2141,12 @@
       <c r="Q33" s="19"/>
       <c r="R33" s="10"/>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C34" s="1">
         <v>45879</v>
@@ -2176,7 +2176,7 @@
       <c r="P34" s="22"/>
       <c r="Q34" s="19"/>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="D35" s="2"/>
       <c r="E35" s="11"/>
       <c r="G35" s="4"/>
@@ -2188,7 +2188,7 @@
       <c r="P35" s="11"/>
       <c r="Q35" s="4"/>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="D36" s="2"/>
       <c r="E36" s="11"/>
       <c r="G36" s="4"/>
@@ -2200,7 +2200,7 @@
       <c r="P36" s="11"/>
       <c r="Q36" s="4"/>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="D37" s="2"/>
       <c r="E37" s="11"/>
       <c r="G37" s="4"/>
@@ -2212,7 +2212,7 @@
       <c r="P37" s="11"/>
       <c r="Q37" s="4"/>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="D38" s="2"/>
       <c r="E38" s="11"/>
       <c r="G38" s="4"/>
@@ -2224,7 +2224,7 @@
       <c r="P38" s="11"/>
       <c r="Q38" s="4"/>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="D39" s="2"/>
       <c r="E39" s="11"/>
       <c r="G39" s="4"/>
@@ -2236,7 +2236,7 @@
       <c r="P39" s="11"/>
       <c r="Q39" s="4"/>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="D40" s="2"/>
       <c r="E40" s="11"/>
       <c r="G40" s="4"/>
@@ -2248,7 +2248,7 @@
       <c r="P40" s="11"/>
       <c r="Q40" s="4"/>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="D41" s="2"/>
       <c r="E41" s="11"/>
       <c r="G41" s="4"/>
@@ -2260,7 +2260,7 @@
       <c r="P41" s="11"/>
       <c r="Q41" s="4"/>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="D42" s="2"/>
       <c r="E42" s="11"/>
       <c r="G42" s="4"/>
@@ -2272,7 +2272,7 @@
       <c r="P42" s="11"/>
       <c r="Q42" s="4"/>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="D43" s="2"/>
       <c r="E43" s="11"/>
       <c r="G43" s="4"/>
@@ -2284,7 +2284,7 @@
       <c r="P43" s="11"/>
       <c r="Q43" s="4"/>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="D44" s="2"/>
       <c r="E44" s="11"/>
       <c r="G44" s="4"/>
@@ -2296,7 +2296,7 @@
       <c r="P44" s="11"/>
       <c r="Q44" s="4"/>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="D45" s="2"/>
       <c r="E45" s="11"/>
       <c r="G45" s="4"/>
@@ -2308,7 +2308,7 @@
       <c r="P45" s="11"/>
       <c r="Q45" s="4"/>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="D46" s="2"/>
       <c r="E46" s="11"/>
       <c r="G46" s="4"/>
@@ -2320,7 +2320,7 @@
       <c r="P46" s="11"/>
       <c r="Q46" s="4"/>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="D47" s="2"/>
       <c r="E47" s="11"/>
       <c r="G47" s="4"/>
@@ -2332,7 +2332,7 @@
       <c r="P47" s="11"/>
       <c r="Q47" s="4"/>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="D48" s="2"/>
       <c r="E48" s="11"/>
       <c r="G48" s="4"/>
@@ -2344,7 +2344,7 @@
       <c r="P48" s="11"/>
       <c r="Q48" s="4"/>
     </row>
-    <row r="49" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D49" s="2"/>
       <c r="E49" s="11"/>
       <c r="G49" s="4"/>
@@ -2356,7 +2356,7 @@
       <c r="P49" s="11"/>
       <c r="Q49" s="4"/>
     </row>
-    <row r="50" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D50" s="2"/>
       <c r="E50" s="11"/>
       <c r="G50" s="4"/>
@@ -2368,7 +2368,7 @@
       <c r="P50" s="11"/>
       <c r="Q50" s="4"/>
     </row>
-    <row r="51" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D51" s="2"/>
       <c r="E51" s="11"/>
       <c r="G51" s="4"/>
@@ -2380,7 +2380,7 @@
       <c r="P51" s="11"/>
       <c r="Q51" s="4"/>
     </row>
-    <row r="52" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D52" s="2"/>
       <c r="E52" s="11"/>
       <c r="G52" s="4"/>
@@ -2392,7 +2392,7 @@
       <c r="P52" s="11"/>
       <c r="Q52" s="4"/>
     </row>
-    <row r="53" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D53" s="2"/>
       <c r="E53" s="11"/>
       <c r="G53" s="4"/>
@@ -2404,7 +2404,7 @@
       <c r="P53" s="11"/>
       <c r="Q53" s="4"/>
     </row>
-    <row r="54" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D54" s="2"/>
       <c r="E54" s="11"/>
       <c r="G54" s="4"/>
@@ -2416,7 +2416,7 @@
       <c r="P54" s="11"/>
       <c r="Q54" s="4"/>
     </row>
-    <row r="55" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D55" s="2"/>
       <c r="E55" s="11"/>
       <c r="G55" s="4"/>
@@ -2428,7 +2428,7 @@
       <c r="P55" s="11"/>
       <c r="Q55" s="4"/>
     </row>
-    <row r="56" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D56" s="2"/>
       <c r="E56" s="11"/>
       <c r="G56" s="4"/>
@@ -2440,7 +2440,7 @@
       <c r="P56" s="11"/>
       <c r="Q56" s="4"/>
     </row>
-    <row r="57" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D57" s="2"/>
       <c r="E57" s="11"/>
       <c r="G57" s="4"/>
@@ -2452,7 +2452,7 @@
       <c r="P57" s="11"/>
       <c r="Q57" s="4"/>
     </row>
-    <row r="58" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D58" s="2"/>
       <c r="E58" s="11"/>
       <c r="G58" s="4"/>
@@ -2464,7 +2464,7 @@
       <c r="P58" s="11"/>
       <c r="Q58" s="4"/>
     </row>
-    <row r="59" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D59" s="2"/>
       <c r="E59" s="11"/>
       <c r="G59" s="4"/>
@@ -2476,7 +2476,7 @@
       <c r="P59" s="11"/>
       <c r="Q59" s="4"/>
     </row>
-    <row r="60" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D60" s="2"/>
       <c r="E60" s="11"/>
       <c r="G60" s="4"/>
@@ -2488,7 +2488,7 @@
       <c r="P60" s="11"/>
       <c r="Q60" s="4"/>
     </row>
-    <row r="61" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D61" s="2"/>
       <c r="E61" s="11"/>
       <c r="G61" s="4"/>
@@ -2500,7 +2500,7 @@
       <c r="P61" s="11"/>
       <c r="Q61" s="4"/>
     </row>
-    <row r="62" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D62" s="2"/>
       <c r="E62" s="11"/>
       <c r="G62" s="4"/>
@@ -2512,7 +2512,7 @@
       <c r="P62" s="11"/>
       <c r="Q62" s="4"/>
     </row>
-    <row r="63" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D63" s="2"/>
       <c r="E63" s="11"/>
       <c r="G63" s="4"/>
@@ -2524,7 +2524,7 @@
       <c r="P63" s="11"/>
       <c r="Q63" s="4"/>
     </row>
-    <row r="64" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D64" s="2"/>
       <c r="E64" s="11"/>
       <c r="G64" s="4"/>
@@ -2536,7 +2536,7 @@
       <c r="P64" s="11"/>
       <c r="Q64" s="4"/>
     </row>
-    <row r="65" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D65" s="2"/>
       <c r="E65" s="11"/>
       <c r="G65" s="4"/>
@@ -2548,7 +2548,7 @@
       <c r="P65" s="11"/>
       <c r="Q65" s="4"/>
     </row>
-    <row r="66" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D66" s="2"/>
       <c r="E66" s="11"/>
       <c r="G66" s="4"/>
@@ -2560,7 +2560,7 @@
       <c r="P66" s="11"/>
       <c r="Q66" s="4"/>
     </row>
-    <row r="67" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D67" s="2"/>
       <c r="E67" s="11"/>
       <c r="G67" s="4"/>
@@ -2572,7 +2572,7 @@
       <c r="P67" s="11"/>
       <c r="Q67" s="4"/>
     </row>
-    <row r="68" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D68" s="2"/>
       <c r="E68" s="11"/>
       <c r="G68" s="4"/>
@@ -2584,7 +2584,7 @@
       <c r="P68" s="11"/>
       <c r="Q68" s="4"/>
     </row>
-    <row r="69" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D69" s="2"/>
       <c r="E69" s="11"/>
       <c r="G69" s="4"/>
@@ -2596,7 +2596,7 @@
       <c r="P69" s="11"/>
       <c r="Q69" s="4"/>
     </row>
-    <row r="70" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D70" s="2"/>
       <c r="E70" s="11"/>
       <c r="G70" s="4"/>
@@ -2608,7 +2608,7 @@
       <c r="P70" s="11"/>
       <c r="Q70" s="4"/>
     </row>
-    <row r="71" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D71" s="2"/>
       <c r="E71" s="11"/>
       <c r="G71" s="4"/>
@@ -2620,7 +2620,7 @@
       <c r="P71" s="11"/>
       <c r="Q71" s="4"/>
     </row>
-    <row r="72" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D72" s="2"/>
       <c r="E72" s="11"/>
       <c r="G72" s="4"/>
@@ -2632,7 +2632,7 @@
       <c r="P72" s="11"/>
       <c r="Q72" s="4"/>
     </row>
-    <row r="73" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D73" s="2"/>
       <c r="E73" s="11"/>
       <c r="G73" s="4"/>
@@ -2644,7 +2644,7 @@
       <c r="P73" s="11"/>
       <c r="Q73" s="4"/>
     </row>
-    <row r="74" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D74" s="2"/>
       <c r="E74" s="11"/>
       <c r="G74" s="4"/>
@@ -2656,7 +2656,7 @@
       <c r="P74" s="11"/>
       <c r="Q74" s="4"/>
     </row>
-    <row r="75" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D75" s="2"/>
       <c r="E75" s="11"/>
       <c r="G75" s="4"/>
@@ -2668,7 +2668,7 @@
       <c r="P75" s="11"/>
       <c r="Q75" s="4"/>
     </row>
-    <row r="76" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D76" s="2"/>
       <c r="E76" s="11"/>
       <c r="G76" s="4"/>
@@ -2680,7 +2680,7 @@
       <c r="P76" s="11"/>
       <c r="Q76" s="4"/>
     </row>
-    <row r="77" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D77" s="2"/>
       <c r="E77" s="11"/>
       <c r="G77" s="4"/>
@@ -2692,7 +2692,7 @@
       <c r="P77" s="11"/>
       <c r="Q77" s="4"/>
     </row>
-    <row r="78" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D78" s="2"/>
       <c r="E78" s="11"/>
       <c r="G78" s="4"/>
@@ -2704,7 +2704,7 @@
       <c r="P78" s="11"/>
       <c r="Q78" s="4"/>
     </row>
-    <row r="79" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D79" s="2"/>
       <c r="E79" s="11"/>
       <c r="G79" s="4"/>
@@ -2716,7 +2716,7 @@
       <c r="P79" s="11"/>
       <c r="Q79" s="4"/>
     </row>
-    <row r="80" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D80" s="2"/>
       <c r="E80" s="11"/>
       <c r="G80" s="4"/>
@@ -2728,7 +2728,7 @@
       <c r="P80" s="11"/>
       <c r="Q80" s="4"/>
     </row>
-    <row r="81" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D81" s="2"/>
       <c r="E81" s="11"/>
       <c r="G81" s="4"/>
@@ -2740,7 +2740,7 @@
       <c r="P81" s="11"/>
       <c r="Q81" s="4"/>
     </row>
-    <row r="82" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D82" s="2"/>
       <c r="E82" s="11"/>
       <c r="G82" s="4"/>
@@ -2752,7 +2752,7 @@
       <c r="P82" s="11"/>
       <c r="Q82" s="4"/>
     </row>
-    <row r="83" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D83" s="2"/>
       <c r="E83" s="11"/>
       <c r="G83" s="4"/>
@@ -2764,7 +2764,7 @@
       <c r="P83" s="11"/>
       <c r="Q83" s="4"/>
     </row>
-    <row r="84" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D84" s="2"/>
       <c r="E84" s="11"/>
       <c r="G84" s="4"/>
@@ -2776,7 +2776,7 @@
       <c r="P84" s="11"/>
       <c r="Q84" s="4"/>
     </row>
-    <row r="85" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D85" s="2"/>
       <c r="E85" s="11"/>
       <c r="G85" s="4"/>
@@ -2788,7 +2788,7 @@
       <c r="P85" s="11"/>
       <c r="Q85" s="4"/>
     </row>
-    <row r="86" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D86" s="2"/>
       <c r="E86" s="11"/>
       <c r="G86" s="4"/>
@@ -2800,7 +2800,7 @@
       <c r="P86" s="11"/>
       <c r="Q86" s="4"/>
     </row>
-    <row r="87" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D87" s="2"/>
       <c r="E87" s="11"/>
       <c r="G87" s="4"/>
@@ -2812,7 +2812,7 @@
       <c r="P87" s="11"/>
       <c r="Q87" s="4"/>
     </row>
-    <row r="88" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D88" s="2"/>
       <c r="E88" s="11"/>
       <c r="G88" s="4"/>
@@ -2824,7 +2824,7 @@
       <c r="P88" s="11"/>
       <c r="Q88" s="4"/>
     </row>
-    <row r="89" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D89" s="2"/>
       <c r="E89" s="11"/>
       <c r="G89" s="4"/>
@@ -2836,7 +2836,7 @@
       <c r="P89" s="11"/>
       <c r="Q89" s="4"/>
     </row>
-    <row r="90" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D90" s="2"/>
       <c r="E90" s="11"/>
       <c r="G90" s="4"/>
@@ -2848,7 +2848,7 @@
       <c r="P90" s="11"/>
       <c r="Q90" s="4"/>
     </row>
-    <row r="91" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D91" s="2"/>
       <c r="E91" s="11"/>
       <c r="G91" s="4"/>
@@ -2860,7 +2860,7 @@
       <c r="P91" s="11"/>
       <c r="Q91" s="4"/>
     </row>
-    <row r="92" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D92" s="2"/>
       <c r="E92" s="11"/>
       <c r="G92" s="4"/>
@@ -2872,7 +2872,7 @@
       <c r="P92" s="11"/>
       <c r="Q92" s="4"/>
     </row>
-    <row r="93" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D93" s="2"/>
       <c r="E93" s="11"/>
       <c r="G93" s="4"/>
@@ -2884,7 +2884,7 @@
       <c r="P93" s="11"/>
       <c r="Q93" s="4"/>
     </row>
-    <row r="94" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D94" s="2"/>
       <c r="E94" s="11"/>
       <c r="G94" s="4"/>
@@ -2896,7 +2896,7 @@
       <c r="P94" s="11"/>
       <c r="Q94" s="4"/>
     </row>
-    <row r="95" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D95" s="2"/>
       <c r="E95" s="11"/>
       <c r="G95" s="4"/>
@@ -2908,7 +2908,7 @@
       <c r="P95" s="11"/>
       <c r="Q95" s="4"/>
     </row>
-    <row r="96" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D96" s="2"/>
       <c r="E96" s="11"/>
       <c r="G96" s="4"/>
@@ -2920,7 +2920,7 @@
       <c r="P96" s="11"/>
       <c r="Q96" s="4"/>
     </row>
-    <row r="97" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D97" s="2"/>
       <c r="E97" s="11"/>
       <c r="G97" s="4"/>
@@ -2932,7 +2932,7 @@
       <c r="P97" s="11"/>
       <c r="Q97" s="4"/>
     </row>
-    <row r="98" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D98" s="2"/>
       <c r="E98" s="11"/>
       <c r="G98" s="4"/>
@@ -2944,7 +2944,7 @@
       <c r="P98" s="11"/>
       <c r="Q98" s="4"/>
     </row>
-    <row r="99" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D99" s="2"/>
       <c r="E99" s="11"/>
       <c r="G99" s="4"/>
@@ -2956,7 +2956,7 @@
       <c r="P99" s="11"/>
       <c r="Q99" s="4"/>
     </row>
-    <row r="100" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D100" s="2"/>
       <c r="E100" s="11"/>
       <c r="G100" s="4"/>
@@ -2968,7 +2968,7 @@
       <c r="P100" s="11"/>
       <c r="Q100" s="4"/>
     </row>
-    <row r="101" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D101" s="2"/>
       <c r="E101" s="11"/>
       <c r="G101" s="4"/>
@@ -2980,7 +2980,7 @@
       <c r="P101" s="11"/>
       <c r="Q101" s="4"/>
     </row>
-    <row r="102" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D102" s="2"/>
       <c r="E102" s="11"/>
       <c r="G102" s="4"/>
@@ -2992,7 +2992,7 @@
       <c r="P102" s="11"/>
       <c r="Q102" s="4"/>
     </row>
-    <row r="103" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D103" s="2"/>
       <c r="E103" s="11"/>
       <c r="G103" s="4"/>
@@ -3004,7 +3004,7 @@
       <c r="P103" s="11"/>
       <c r="Q103" s="4"/>
     </row>
-    <row r="104" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D104" s="2"/>
       <c r="E104" s="11"/>
       <c r="G104" s="4"/>
@@ -3016,7 +3016,7 @@
       <c r="P104" s="11"/>
       <c r="Q104" s="4"/>
     </row>
-    <row r="105" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D105" s="2"/>
       <c r="E105" s="11"/>
       <c r="G105" s="4"/>
@@ -3028,7 +3028,7 @@
       <c r="P105" s="11"/>
       <c r="Q105" s="4"/>
     </row>
-    <row r="106" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D106" s="2"/>
       <c r="E106" s="11"/>
       <c r="G106" s="4"/>
@@ -3040,7 +3040,7 @@
       <c r="P106" s="11"/>
       <c r="Q106" s="4"/>
     </row>
-    <row r="107" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D107" s="2"/>
       <c r="E107" s="11"/>
       <c r="G107" s="4"/>
@@ -3052,7 +3052,7 @@
       <c r="P107" s="11"/>
       <c r="Q107" s="4"/>
     </row>
-    <row r="108" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D108" s="2"/>
       <c r="E108" s="11"/>
       <c r="G108" s="4"/>
@@ -3064,7 +3064,7 @@
       <c r="P108" s="11"/>
       <c r="Q108" s="4"/>
     </row>
-    <row r="109" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="109" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D109" s="2"/>
       <c r="E109" s="11"/>
       <c r="G109" s="4"/>
@@ -3076,7 +3076,7 @@
       <c r="P109" s="11"/>
       <c r="Q109" s="4"/>
     </row>
-    <row r="110" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D110" s="2"/>
       <c r="E110" s="11"/>
       <c r="G110" s="4"/>
@@ -3088,7 +3088,7 @@
       <c r="P110" s="11"/>
       <c r="Q110" s="4"/>
     </row>
-    <row r="111" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D111" s="2"/>
       <c r="E111" s="11"/>
       <c r="G111" s="4"/>
@@ -3100,7 +3100,7 @@
       <c r="P111" s="11"/>
       <c r="Q111" s="4"/>
     </row>
-    <row r="112" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D112" s="2"/>
       <c r="E112" s="11"/>
       <c r="G112" s="4"/>
@@ -3112,7 +3112,7 @@
       <c r="P112" s="11"/>
       <c r="Q112" s="4"/>
     </row>
-    <row r="113" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D113" s="2"/>
       <c r="E113" s="11"/>
       <c r="G113" s="4"/>
@@ -3124,7 +3124,7 @@
       <c r="P113" s="11"/>
       <c r="Q113" s="4"/>
     </row>
-    <row r="114" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D114" s="2"/>
       <c r="E114" s="11"/>
       <c r="G114" s="4"/>
@@ -3136,7 +3136,7 @@
       <c r="P114" s="11"/>
       <c r="Q114" s="4"/>
     </row>
-    <row r="115" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D115" s="2"/>
       <c r="E115" s="11"/>
       <c r="G115" s="4"/>
@@ -3148,7 +3148,7 @@
       <c r="P115" s="11"/>
       <c r="Q115" s="4"/>
     </row>
-    <row r="116" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D116" s="2"/>
       <c r="E116" s="11"/>
       <c r="G116" s="4"/>
@@ -3160,7 +3160,7 @@
       <c r="P116" s="11"/>
       <c r="Q116" s="4"/>
     </row>
-    <row r="117" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D117" s="2"/>
       <c r="E117" s="11"/>
       <c r="G117" s="4"/>
@@ -3172,7 +3172,7 @@
       <c r="P117" s="11"/>
       <c r="Q117" s="4"/>
     </row>
-    <row r="118" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D118" s="2"/>
       <c r="E118" s="11"/>
       <c r="G118" s="4"/>
@@ -3184,7 +3184,7 @@
       <c r="P118" s="11"/>
       <c r="Q118" s="4"/>
     </row>
-    <row r="119" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D119" s="2"/>
       <c r="E119" s="11"/>
       <c r="G119" s="4"/>
@@ -3196,7 +3196,7 @@
       <c r="P119" s="11"/>
       <c r="Q119" s="4"/>
     </row>
-    <row r="120" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D120" s="2"/>
       <c r="E120" s="11"/>
       <c r="G120" s="4"/>
@@ -3208,7 +3208,7 @@
       <c r="P120" s="11"/>
       <c r="Q120" s="4"/>
     </row>
-    <row r="121" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D121" s="2"/>
       <c r="E121" s="11"/>
       <c r="G121" s="4"/>
@@ -3220,7 +3220,7 @@
       <c r="P121" s="11"/>
       <c r="Q121" s="4"/>
     </row>
-    <row r="122" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D122" s="2"/>
       <c r="E122" s="11"/>
       <c r="G122" s="4"/>
@@ -3232,7 +3232,7 @@
       <c r="P122" s="11"/>
       <c r="Q122" s="4"/>
     </row>
-    <row r="123" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D123" s="2"/>
       <c r="E123" s="11"/>
       <c r="G123" s="4"/>
@@ -3244,7 +3244,7 @@
       <c r="P123" s="11"/>
       <c r="Q123" s="4"/>
     </row>
-    <row r="124" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D124" s="2"/>
       <c r="E124" s="11"/>
       <c r="G124" s="4"/>
@@ -3256,7 +3256,7 @@
       <c r="P124" s="11"/>
       <c r="Q124" s="4"/>
     </row>
-    <row r="125" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D125" s="2"/>
       <c r="E125" s="11"/>
       <c r="G125" s="4"/>
@@ -3268,7 +3268,7 @@
       <c r="P125" s="11"/>
       <c r="Q125" s="4"/>
     </row>
-    <row r="126" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D126" s="2"/>
       <c r="E126" s="11"/>
       <c r="G126" s="4"/>
@@ -3280,7 +3280,7 @@
       <c r="P126" s="11"/>
       <c r="Q126" s="4"/>
     </row>
-    <row r="127" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D127" s="2"/>
       <c r="E127" s="11"/>
       <c r="G127" s="4"/>
@@ -3292,7 +3292,7 @@
       <c r="P127" s="11"/>
       <c r="Q127" s="4"/>
     </row>
-    <row r="128" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D128" s="2"/>
       <c r="E128" s="11"/>
       <c r="G128" s="4"/>
@@ -3304,7 +3304,7 @@
       <c r="P128" s="11"/>
       <c r="Q128" s="4"/>
     </row>
-    <row r="129" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D129" s="2"/>
       <c r="E129" s="11"/>
       <c r="G129" s="4"/>
@@ -3316,7 +3316,7 @@
       <c r="P129" s="11"/>
       <c r="Q129" s="4"/>
     </row>
-    <row r="130" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D130" s="2"/>
       <c r="E130" s="11"/>
       <c r="G130" s="4"/>
@@ -3328,7 +3328,7 @@
       <c r="P130" s="11"/>
       <c r="Q130" s="4"/>
     </row>
-    <row r="131" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D131" s="2"/>
       <c r="E131" s="11"/>
       <c r="G131" s="4"/>
@@ -3340,7 +3340,7 @@
       <c r="P131" s="11"/>
       <c r="Q131" s="4"/>
     </row>
-    <row r="132" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D132" s="2"/>
       <c r="E132" s="11"/>
       <c r="G132" s="4"/>
@@ -3352,7 +3352,7 @@
       <c r="P132" s="11"/>
       <c r="Q132" s="4"/>
     </row>
-    <row r="133" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="133" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D133" s="2"/>
       <c r="E133" s="11"/>
       <c r="G133" s="4"/>
@@ -3364,7 +3364,7 @@
       <c r="P133" s="11"/>
       <c r="Q133" s="4"/>
     </row>
-    <row r="134" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="134" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D134" s="2"/>
       <c r="E134" s="11"/>
       <c r="G134" s="4"/>
@@ -3376,7 +3376,7 @@
       <c r="P134" s="11"/>
       <c r="Q134" s="4"/>
     </row>
-    <row r="135" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="135" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D135" s="2"/>
       <c r="E135" s="11"/>
       <c r="G135" s="4"/>
@@ -3388,7 +3388,7 @@
       <c r="P135" s="11"/>
       <c r="Q135" s="4"/>
     </row>
-    <row r="136" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="136" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D136" s="2"/>
       <c r="E136" s="11"/>
       <c r="G136" s="4"/>
@@ -3400,7 +3400,7 @@
       <c r="P136" s="11"/>
       <c r="Q136" s="4"/>
     </row>
-    <row r="137" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="137" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D137" s="2"/>
       <c r="E137" s="11"/>
       <c r="G137" s="4"/>
@@ -3412,7 +3412,7 @@
       <c r="P137" s="11"/>
       <c r="Q137" s="4"/>
     </row>
-    <row r="138" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="138" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D138" s="2"/>
       <c r="E138" s="11"/>
       <c r="G138" s="4"/>
@@ -3424,7 +3424,7 @@
       <c r="P138" s="11"/>
       <c r="Q138" s="4"/>
     </row>
-    <row r="139" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="139" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D139" s="2"/>
       <c r="E139" s="11"/>
       <c r="G139" s="4"/>
@@ -3436,7 +3436,7 @@
       <c r="P139" s="11"/>
       <c r="Q139" s="4"/>
     </row>
-    <row r="140" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="140" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D140" s="2"/>
       <c r="E140" s="11"/>
       <c r="G140" s="4"/>
@@ -3448,7 +3448,7 @@
       <c r="P140" s="11"/>
       <c r="Q140" s="4"/>
     </row>
-    <row r="141" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="141" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D141" s="2"/>
       <c r="E141" s="11"/>
       <c r="G141" s="4"/>
@@ -3460,7 +3460,7 @@
       <c r="P141" s="11"/>
       <c r="Q141" s="4"/>
     </row>
-    <row r="142" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D142" s="2"/>
       <c r="E142" s="11"/>
       <c r="G142" s="4"/>
@@ -3472,7 +3472,7 @@
       <c r="P142" s="11"/>
       <c r="Q142" s="4"/>
     </row>
-    <row r="143" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="143" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D143" s="2"/>
       <c r="E143" s="11"/>
       <c r="G143" s="4"/>
@@ -3484,7 +3484,7 @@
       <c r="P143" s="11"/>
       <c r="Q143" s="4"/>
     </row>
-    <row r="144" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="144" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D144" s="2"/>
       <c r="E144" s="11"/>
       <c r="G144" s="4"/>
@@ -3496,7 +3496,7 @@
       <c r="P144" s="11"/>
       <c r="Q144" s="4"/>
     </row>
-    <row r="145" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="145" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D145" s="2"/>
       <c r="E145" s="11"/>
       <c r="G145" s="4"/>
@@ -3508,7 +3508,7 @@
       <c r="P145" s="11"/>
       <c r="Q145" s="4"/>
     </row>
-    <row r="146" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="146" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D146" s="2"/>
       <c r="E146" s="11"/>
       <c r="G146" s="4"/>
@@ -3520,7 +3520,7 @@
       <c r="P146" s="11"/>
       <c r="Q146" s="4"/>
     </row>
-    <row r="147" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="147" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D147" s="2"/>
       <c r="E147" s="11"/>
       <c r="G147" s="4"/>
@@ -3532,7 +3532,7 @@
       <c r="P147" s="11"/>
       <c r="Q147" s="4"/>
     </row>
-    <row r="148" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="148" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D148" s="2"/>
       <c r="E148" s="11"/>
       <c r="G148" s="4"/>
@@ -3544,7 +3544,7 @@
       <c r="P148" s="11"/>
       <c r="Q148" s="4"/>
     </row>
-    <row r="149" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="149" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D149" s="2"/>
       <c r="E149" s="11"/>
       <c r="G149" s="4"/>
@@ -3556,7 +3556,7 @@
       <c r="P149" s="11"/>
       <c r="Q149" s="4"/>
     </row>
-    <row r="150" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="150" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D150" s="2"/>
       <c r="E150" s="11"/>
       <c r="G150" s="4"/>
@@ -3568,7 +3568,7 @@
       <c r="P150" s="11"/>
       <c r="Q150" s="4"/>
     </row>
-    <row r="151" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="151" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D151" s="2"/>
       <c r="E151" s="11"/>
       <c r="G151" s="4"/>
@@ -3580,7 +3580,7 @@
       <c r="P151" s="11"/>
       <c r="Q151" s="4"/>
     </row>
-    <row r="152" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="152" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D152" s="2"/>
       <c r="E152" s="11"/>
       <c r="G152" s="4"/>
@@ -3592,7 +3592,7 @@
       <c r="P152" s="11"/>
       <c r="Q152" s="4"/>
     </row>
-    <row r="153" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="153" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D153" s="2"/>
       <c r="E153" s="11"/>
       <c r="G153" s="4"/>
@@ -3604,7 +3604,7 @@
       <c r="P153" s="11"/>
       <c r="Q153" s="4"/>
     </row>
-    <row r="154" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="154" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D154" s="2"/>
       <c r="E154" s="11"/>
       <c r="G154" s="4"/>
@@ -3616,7 +3616,7 @@
       <c r="P154" s="11"/>
       <c r="Q154" s="4"/>
     </row>
-    <row r="155" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="155" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D155" s="2"/>
       <c r="E155" s="11"/>
       <c r="G155" s="4"/>
@@ -3628,7 +3628,7 @@
       <c r="P155" s="11"/>
       <c r="Q155" s="4"/>
     </row>
-    <row r="156" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="156" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D156" s="2"/>
       <c r="E156" s="11"/>
       <c r="G156" s="4"/>
@@ -3640,7 +3640,7 @@
       <c r="P156" s="11"/>
       <c r="Q156" s="4"/>
     </row>
-    <row r="157" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="157" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D157" s="2"/>
       <c r="E157" s="11"/>
       <c r="G157" s="4"/>
@@ -3652,7 +3652,7 @@
       <c r="P157" s="11"/>
       <c r="Q157" s="4"/>
     </row>
-    <row r="158" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="158" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D158" s="2"/>
       <c r="E158" s="11"/>
       <c r="G158" s="4"/>
@@ -3664,7 +3664,7 @@
       <c r="P158" s="11"/>
       <c r="Q158" s="4"/>
     </row>
-    <row r="159" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="159" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D159" s="2"/>
       <c r="E159" s="11"/>
       <c r="G159" s="4"/>
@@ -3676,7 +3676,7 @@
       <c r="P159" s="11"/>
       <c r="Q159" s="4"/>
     </row>
-    <row r="160" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="160" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D160" s="2"/>
       <c r="E160" s="11"/>
       <c r="G160" s="4"/>
@@ -3688,7 +3688,7 @@
       <c r="P160" s="11"/>
       <c r="Q160" s="4"/>
     </row>
-    <row r="161" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="161" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D161" s="2"/>
       <c r="E161" s="11"/>
       <c r="G161" s="4"/>
@@ -3700,7 +3700,7 @@
       <c r="P161" s="11"/>
       <c r="Q161" s="4"/>
     </row>
-    <row r="162" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="162" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D162" s="2"/>
       <c r="E162" s="11"/>
       <c r="G162" s="4"/>
@@ -3712,7 +3712,7 @@
       <c r="P162" s="11"/>
       <c r="Q162" s="4"/>
     </row>
-    <row r="163" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="163" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D163" s="2"/>
       <c r="E163" s="11"/>
       <c r="G163" s="4"/>
@@ -3724,7 +3724,7 @@
       <c r="P163" s="11"/>
       <c r="Q163" s="4"/>
     </row>
-    <row r="164" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="164" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D164" s="2"/>
       <c r="E164" s="11"/>
       <c r="G164" s="4"/>
@@ -3736,7 +3736,7 @@
       <c r="P164" s="11"/>
       <c r="Q164" s="4"/>
     </row>
-    <row r="165" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="165" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D165" s="2"/>
       <c r="E165" s="11"/>
       <c r="G165" s="4"/>
@@ -3748,7 +3748,7 @@
       <c r="P165" s="11"/>
       <c r="Q165" s="4"/>
     </row>
-    <row r="166" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="166" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D166" s="2"/>
       <c r="E166" s="11"/>
       <c r="G166" s="4"/>
@@ -3760,7 +3760,7 @@
       <c r="P166" s="11"/>
       <c r="Q166" s="4"/>
     </row>
-    <row r="167" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="167" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D167" s="2"/>
       <c r="E167" s="11"/>
       <c r="G167" s="4"/>
@@ -3772,7 +3772,7 @@
       <c r="P167" s="11"/>
       <c r="Q167" s="4"/>
     </row>
-    <row r="168" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="168" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D168" s="2"/>
       <c r="E168" s="11"/>
       <c r="G168" s="4"/>
@@ -3784,7 +3784,7 @@
       <c r="P168" s="11"/>
       <c r="Q168" s="4"/>
     </row>
-    <row r="169" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="169" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D169" s="2"/>
       <c r="E169" s="11"/>
       <c r="G169" s="4"/>
@@ -3796,7 +3796,7 @@
       <c r="P169" s="11"/>
       <c r="Q169" s="4"/>
     </row>
-    <row r="170" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="170" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D170" s="2"/>
       <c r="E170" s="11"/>
       <c r="G170" s="4"/>
@@ -3808,7 +3808,7 @@
       <c r="P170" s="11"/>
       <c r="Q170" s="4"/>
     </row>
-    <row r="171" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="171" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D171" s="2"/>
       <c r="E171" s="11"/>
       <c r="G171" s="4"/>
@@ -3820,7 +3820,7 @@
       <c r="P171" s="11"/>
       <c r="Q171" s="4"/>
     </row>
-    <row r="172" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="172" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D172" s="2"/>
       <c r="E172" s="11"/>
       <c r="G172" s="4"/>
@@ -3832,7 +3832,7 @@
       <c r="P172" s="11"/>
       <c r="Q172" s="4"/>
     </row>
-    <row r="173" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="173" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D173" s="2"/>
       <c r="E173" s="11"/>
       <c r="G173" s="4"/>
@@ -3844,7 +3844,7 @@
       <c r="P173" s="11"/>
       <c r="Q173" s="4"/>
     </row>
-    <row r="174" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="174" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D174" s="2"/>
       <c r="E174" s="11"/>
       <c r="G174" s="4"/>
@@ -3856,7 +3856,7 @@
       <c r="P174" s="11"/>
       <c r="Q174" s="4"/>
     </row>
-    <row r="175" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="175" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D175" s="2"/>
       <c r="E175" s="11"/>
       <c r="G175" s="4"/>
@@ -3868,7 +3868,7 @@
       <c r="P175" s="11"/>
       <c r="Q175" s="4"/>
     </row>
-    <row r="176" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="176" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D176" s="2"/>
       <c r="E176" s="11"/>
       <c r="G176" s="4"/>
@@ -3880,7 +3880,7 @@
       <c r="P176" s="11"/>
       <c r="Q176" s="4"/>
     </row>
-    <row r="177" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="177" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D177" s="2"/>
       <c r="E177" s="11"/>
       <c r="G177" s="4"/>
@@ -3892,7 +3892,7 @@
       <c r="P177" s="11"/>
       <c r="Q177" s="4"/>
     </row>
-    <row r="178" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="178" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D178" s="2"/>
       <c r="E178" s="11"/>
       <c r="G178" s="4"/>
@@ -3904,7 +3904,7 @@
       <c r="P178" s="11"/>
       <c r="Q178" s="4"/>
     </row>
-    <row r="179" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="179" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D179" s="2"/>
       <c r="E179" s="11"/>
       <c r="G179" s="4"/>
@@ -3916,7 +3916,7 @@
       <c r="P179" s="11"/>
       <c r="Q179" s="4"/>
     </row>
-    <row r="180" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="180" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D180" s="2"/>
       <c r="E180" s="11"/>
       <c r="G180" s="4"/>
@@ -3928,7 +3928,7 @@
       <c r="P180" s="11"/>
       <c r="Q180" s="4"/>
     </row>
-    <row r="181" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="181" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D181" s="2"/>
       <c r="E181" s="11"/>
       <c r="G181" s="4"/>
@@ -3940,7 +3940,7 @@
       <c r="P181" s="11"/>
       <c r="Q181" s="4"/>
     </row>
-    <row r="182" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="182" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D182" s="2"/>
       <c r="E182" s="11"/>
       <c r="G182" s="4"/>
@@ -3952,7 +3952,7 @@
       <c r="P182" s="11"/>
       <c r="Q182" s="4"/>
     </row>
-    <row r="183" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="183" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D183" s="2"/>
       <c r="E183" s="11"/>
       <c r="G183" s="4"/>
@@ -3964,7 +3964,7 @@
       <c r="P183" s="11"/>
       <c r="Q183" s="4"/>
     </row>
-    <row r="184" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="184" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D184" s="2"/>
       <c r="E184" s="11"/>
       <c r="G184" s="4"/>
@@ -3976,7 +3976,7 @@
       <c r="P184" s="11"/>
       <c r="Q184" s="4"/>
     </row>
-    <row r="185" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="185" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D185" s="2"/>
       <c r="E185" s="11"/>
       <c r="G185" s="4"/>
@@ -3988,7 +3988,7 @@
       <c r="P185" s="11"/>
       <c r="Q185" s="4"/>
     </row>
-    <row r="186" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="186" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D186" s="2"/>
       <c r="E186" s="11"/>
       <c r="G186" s="4"/>
@@ -4000,7 +4000,7 @@
       <c r="P186" s="11"/>
       <c r="Q186" s="4"/>
     </row>
-    <row r="187" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="187" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D187" s="2"/>
       <c r="E187" s="11"/>
       <c r="G187" s="4"/>
@@ -4012,7 +4012,7 @@
       <c r="P187" s="11"/>
       <c r="Q187" s="4"/>
     </row>
-    <row r="188" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="188" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D188" s="2"/>
       <c r="E188" s="11"/>
       <c r="G188" s="4"/>
@@ -4024,7 +4024,7 @@
       <c r="P188" s="11"/>
       <c r="Q188" s="4"/>
     </row>
-    <row r="189" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="189" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D189" s="2"/>
       <c r="E189" s="11"/>
       <c r="G189" s="4"/>
@@ -4036,7 +4036,7 @@
       <c r="P189" s="11"/>
       <c r="Q189" s="4"/>
     </row>
-    <row r="190" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="190" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D190" s="2"/>
       <c r="E190" s="11"/>
       <c r="G190" s="4"/>
@@ -4048,7 +4048,7 @@
       <c r="P190" s="11"/>
       <c r="Q190" s="4"/>
     </row>
-    <row r="191" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="191" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D191" s="2"/>
       <c r="E191" s="11"/>
       <c r="G191" s="4"/>
@@ -4060,7 +4060,7 @@
       <c r="P191" s="11"/>
       <c r="Q191" s="4"/>
     </row>
-    <row r="192" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="192" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D192" s="2"/>
       <c r="E192" s="11"/>
       <c r="G192" s="4"/>
@@ -4072,7 +4072,7 @@
       <c r="P192" s="11"/>
       <c r="Q192" s="4"/>
     </row>
-    <row r="193" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="193" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D193" s="2"/>
       <c r="E193" s="11"/>
       <c r="G193" s="4"/>
@@ -4084,7 +4084,7 @@
       <c r="P193" s="11"/>
       <c r="Q193" s="4"/>
     </row>
-    <row r="194" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="194" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D194" s="2"/>
       <c r="E194" s="11"/>
       <c r="G194" s="4"/>
@@ -4096,7 +4096,7 @@
       <c r="P194" s="11"/>
       <c r="Q194" s="4"/>
     </row>
-    <row r="195" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="195" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D195" s="2"/>
       <c r="E195" s="11"/>
       <c r="G195" s="4"/>
@@ -4108,7 +4108,7 @@
       <c r="P195" s="11"/>
       <c r="Q195" s="4"/>
     </row>
-    <row r="196" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="196" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D196" s="2"/>
       <c r="E196" s="11"/>
       <c r="G196" s="4"/>
@@ -4120,7 +4120,7 @@
       <c r="P196" s="11"/>
       <c r="Q196" s="4"/>
     </row>
-    <row r="197" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="197" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D197" s="2"/>
       <c r="E197" s="11"/>
       <c r="G197" s="4"/>
@@ -4132,7 +4132,7 @@
       <c r="P197" s="11"/>
       <c r="Q197" s="4"/>
     </row>
-    <row r="198" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="198" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D198" s="2"/>
       <c r="E198" s="11"/>
       <c r="G198" s="4"/>
@@ -4144,7 +4144,7 @@
       <c r="P198" s="11"/>
       <c r="Q198" s="4"/>
     </row>
-    <row r="199" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="199" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D199" s="2"/>
       <c r="E199" s="11"/>
       <c r="G199" s="4"/>
@@ -4156,7 +4156,7 @@
       <c r="P199" s="11"/>
       <c r="Q199" s="4"/>
     </row>
-    <row r="200" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="200" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D200" s="2"/>
       <c r="E200" s="11"/>
       <c r="G200" s="4"/>
@@ -4168,7 +4168,7 @@
       <c r="P200" s="11"/>
       <c r="Q200" s="4"/>
     </row>
-    <row r="201" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="201" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D201" s="2"/>
       <c r="E201" s="11"/>
       <c r="G201" s="4"/>
@@ -4180,7 +4180,7 @@
       <c r="P201" s="11"/>
       <c r="Q201" s="4"/>
     </row>
-    <row r="202" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="202" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D202" s="2"/>
       <c r="E202" s="11"/>
       <c r="G202" s="4"/>
@@ -4192,7 +4192,7 @@
       <c r="P202" s="11"/>
       <c r="Q202" s="4"/>
     </row>
-    <row r="203" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="203" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D203" s="2"/>
       <c r="E203" s="11"/>
       <c r="G203" s="4"/>
@@ -4204,7 +4204,7 @@
       <c r="P203" s="11"/>
       <c r="Q203" s="4"/>
     </row>
-    <row r="204" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="204" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D204" s="2"/>
       <c r="E204" s="11"/>
       <c r="G204" s="4"/>
@@ -4216,7 +4216,7 @@
       <c r="P204" s="11"/>
       <c r="Q204" s="4"/>
     </row>
-    <row r="205" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="205" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D205" s="2"/>
       <c r="E205" s="11"/>
       <c r="G205" s="4"/>
@@ -4228,7 +4228,7 @@
       <c r="P205" s="11"/>
       <c r="Q205" s="4"/>
     </row>
-    <row r="206" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="206" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D206" s="2"/>
       <c r="E206" s="11"/>
       <c r="G206" s="4"/>
@@ -4240,7 +4240,7 @@
       <c r="P206" s="11"/>
       <c r="Q206" s="4"/>
     </row>
-    <row r="207" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="207" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D207" s="2"/>
       <c r="E207" s="11"/>
       <c r="G207" s="4"/>
@@ -4252,7 +4252,7 @@
       <c r="P207" s="11"/>
       <c r="Q207" s="4"/>
     </row>
-    <row r="208" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="208" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D208" s="2"/>
       <c r="E208" s="11"/>
       <c r="G208" s="4"/>
@@ -4264,7 +4264,7 @@
       <c r="P208" s="11"/>
       <c r="Q208" s="4"/>
     </row>
-    <row r="209" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="209" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D209" s="2"/>
       <c r="E209" s="11"/>
       <c r="G209" s="4"/>
@@ -4276,7 +4276,7 @@
       <c r="P209" s="11"/>
       <c r="Q209" s="4"/>
     </row>
-    <row r="210" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="210" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D210" s="2"/>
       <c r="E210" s="11"/>
       <c r="G210" s="4"/>
@@ -4288,7 +4288,7 @@
       <c r="P210" s="11"/>
       <c r="Q210" s="4"/>
     </row>
-    <row r="211" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="211" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D211" s="2"/>
       <c r="E211" s="11"/>
       <c r="G211" s="4"/>
@@ -4300,7 +4300,7 @@
       <c r="P211" s="11"/>
       <c r="Q211" s="4"/>
     </row>
-    <row r="212" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="212" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D212" s="2"/>
       <c r="E212" s="11"/>
       <c r="G212" s="4"/>
@@ -4312,7 +4312,7 @@
       <c r="P212" s="11"/>
       <c r="Q212" s="4"/>
     </row>
-    <row r="213" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="213" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D213" s="2"/>
       <c r="E213" s="11"/>
       <c r="G213" s="4"/>
@@ -4324,7 +4324,7 @@
       <c r="P213" s="11"/>
       <c r="Q213" s="4"/>
     </row>
-    <row r="214" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="214" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D214" s="2"/>
       <c r="E214" s="11"/>
       <c r="G214" s="4"/>
@@ -4336,7 +4336,7 @@
       <c r="P214" s="11"/>
       <c r="Q214" s="4"/>
     </row>
-    <row r="215" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="215" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D215" s="2"/>
       <c r="E215" s="11"/>
       <c r="G215" s="4"/>
@@ -4348,7 +4348,7 @@
       <c r="P215" s="11"/>
       <c r="Q215" s="4"/>
     </row>
-    <row r="216" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="216" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D216" s="2"/>
       <c r="E216" s="11"/>
       <c r="G216" s="4"/>
@@ -4360,7 +4360,7 @@
       <c r="P216" s="11"/>
       <c r="Q216" s="4"/>
     </row>
-    <row r="217" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="217" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D217" s="2"/>
       <c r="E217" s="11"/>
       <c r="G217" s="4"/>
@@ -4372,7 +4372,7 @@
       <c r="P217" s="11"/>
       <c r="Q217" s="4"/>
     </row>
-    <row r="218" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="218" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D218" s="2"/>
       <c r="E218" s="11"/>
       <c r="G218" s="4"/>
@@ -4384,7 +4384,7 @@
       <c r="P218" s="11"/>
       <c r="Q218" s="4"/>
     </row>
-    <row r="219" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="219" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D219" s="2"/>
       <c r="E219" s="11"/>
       <c r="G219" s="4"/>
@@ -4396,7 +4396,7 @@
       <c r="P219" s="11"/>
       <c r="Q219" s="4"/>
     </row>
-    <row r="220" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="220" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D220" s="2"/>
       <c r="E220" s="11"/>
       <c r="G220" s="4"/>
@@ -4408,7 +4408,7 @@
       <c r="P220" s="11"/>
       <c r="Q220" s="4"/>
     </row>
-    <row r="221" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="221" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D221" s="2"/>
       <c r="E221" s="11"/>
       <c r="G221" s="4"/>
@@ -4420,7 +4420,7 @@
       <c r="P221" s="11"/>
       <c r="Q221" s="4"/>
     </row>
-    <row r="222" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="222" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D222" s="2"/>
       <c r="E222" s="11"/>
       <c r="G222" s="4"/>
@@ -4432,7 +4432,7 @@
       <c r="P222" s="11"/>
       <c r="Q222" s="4"/>
     </row>
-    <row r="223" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="223" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D223" s="2"/>
       <c r="E223" s="11"/>
       <c r="G223" s="4"/>
@@ -4444,7 +4444,7 @@
       <c r="P223" s="11"/>
       <c r="Q223" s="4"/>
     </row>
-    <row r="224" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="224" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D224" s="2"/>
       <c r="E224" s="11"/>
       <c r="G224" s="4"/>
@@ -4456,7 +4456,7 @@
       <c r="P224" s="11"/>
       <c r="Q224" s="4"/>
     </row>
-    <row r="225" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="225" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D225" s="2"/>
       <c r="E225" s="11"/>
       <c r="G225" s="4"/>
@@ -4468,7 +4468,7 @@
       <c r="P225" s="11"/>
       <c r="Q225" s="4"/>
     </row>
-    <row r="226" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="226" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D226" s="2"/>
       <c r="E226" s="11"/>
       <c r="G226" s="4"/>
@@ -4480,7 +4480,7 @@
       <c r="P226" s="11"/>
       <c r="Q226" s="4"/>
     </row>
-    <row r="227" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="227" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D227" s="2"/>
       <c r="E227" s="11"/>
       <c r="G227" s="4"/>
@@ -4492,7 +4492,7 @@
       <c r="P227" s="11"/>
       <c r="Q227" s="4"/>
     </row>
-    <row r="228" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="228" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D228" s="2"/>
       <c r="E228" s="11"/>
       <c r="G228" s="4"/>
@@ -4504,7 +4504,7 @@
       <c r="P228" s="11"/>
       <c r="Q228" s="4"/>
     </row>
-    <row r="229" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="229" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D229" s="2"/>
       <c r="E229" s="11"/>
       <c r="G229" s="4"/>
@@ -4516,7 +4516,7 @@
       <c r="P229" s="11"/>
       <c r="Q229" s="4"/>
     </row>
-    <row r="230" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="230" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D230" s="2"/>
       <c r="E230" s="11"/>
       <c r="G230" s="4"/>
@@ -4528,7 +4528,7 @@
       <c r="P230" s="11"/>
       <c r="Q230" s="4"/>
     </row>
-    <row r="231" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="231" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D231" s="2"/>
       <c r="E231" s="11"/>
       <c r="G231" s="4"/>
@@ -4540,7 +4540,7 @@
       <c r="P231" s="11"/>
       <c r="Q231" s="4"/>
     </row>
-    <row r="232" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="232" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D232" s="2"/>
       <c r="E232" s="11"/>
       <c r="G232" s="4"/>
@@ -4552,7 +4552,7 @@
       <c r="P232" s="11"/>
       <c r="Q232" s="4"/>
     </row>
-    <row r="233" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="233" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D233" s="2"/>
       <c r="E233" s="11"/>
       <c r="G233" s="4"/>
@@ -4564,7 +4564,7 @@
       <c r="P233" s="11"/>
       <c r="Q233" s="4"/>
     </row>
-    <row r="234" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="234" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D234" s="2"/>
       <c r="E234" s="11"/>
       <c r="G234" s="4"/>
@@ -4576,7 +4576,7 @@
       <c r="P234" s="11"/>
       <c r="Q234" s="4"/>
     </row>
-    <row r="235" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="235" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D235" s="2"/>
       <c r="E235" s="11"/>
       <c r="G235" s="4"/>
@@ -4588,7 +4588,7 @@
       <c r="P235" s="11"/>
       <c r="Q235" s="4"/>
     </row>
-    <row r="236" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="236" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D236" s="2"/>
       <c r="E236" s="11"/>
       <c r="G236" s="4"/>
@@ -4600,7 +4600,7 @@
       <c r="P236" s="11"/>
       <c r="Q236" s="4"/>
     </row>
-    <row r="237" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="237" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D237" s="2"/>
       <c r="E237" s="11"/>
       <c r="G237" s="4"/>
@@ -4612,7 +4612,7 @@
       <c r="P237" s="11"/>
       <c r="Q237" s="4"/>
     </row>
-    <row r="238" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="238" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D238" s="2"/>
       <c r="E238" s="11"/>
       <c r="G238" s="4"/>
@@ -4624,7 +4624,7 @@
       <c r="P238" s="11"/>
       <c r="Q238" s="4"/>
     </row>
-    <row r="239" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="239" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D239" s="2"/>
       <c r="E239" s="11"/>
       <c r="G239" s="4"/>
@@ -4636,7 +4636,7 @@
       <c r="P239" s="11"/>
       <c r="Q239" s="4"/>
     </row>
-    <row r="240" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="240" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D240" s="2"/>
       <c r="E240" s="11"/>
       <c r="G240" s="4"/>
@@ -4648,7 +4648,7 @@
       <c r="P240" s="11"/>
       <c r="Q240" s="4"/>
     </row>
-    <row r="241" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="241" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D241" s="2"/>
       <c r="E241" s="11"/>
       <c r="G241" s="4"/>
@@ -4660,7 +4660,7 @@
       <c r="P241" s="11"/>
       <c r="Q241" s="4"/>
     </row>
-    <row r="242" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="242" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D242" s="2"/>
       <c r="E242" s="11"/>
       <c r="G242" s="4"/>
@@ -4672,7 +4672,7 @@
       <c r="P242" s="11"/>
       <c r="Q242" s="4"/>
     </row>
-    <row r="243" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="243" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D243" s="2"/>
       <c r="E243" s="11"/>
       <c r="G243" s="4"/>
@@ -4684,7 +4684,7 @@
       <c r="P243" s="11"/>
       <c r="Q243" s="4"/>
     </row>
-    <row r="244" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="244" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D244" s="2"/>
       <c r="E244" s="11"/>
       <c r="G244" s="4"/>
@@ -4696,7 +4696,7 @@
       <c r="P244" s="11"/>
       <c r="Q244" s="4"/>
     </row>
-    <row r="245" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="245" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D245" s="2"/>
       <c r="E245" s="11"/>
       <c r="G245" s="4"/>
@@ -4708,7 +4708,7 @@
       <c r="P245" s="11"/>
       <c r="Q245" s="4"/>
     </row>
-    <row r="246" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="246" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D246" s="2"/>
       <c r="E246" s="11"/>
       <c r="G246" s="4"/>
@@ -4720,7 +4720,7 @@
       <c r="P246" s="11"/>
       <c r="Q246" s="4"/>
     </row>
-    <row r="247" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="247" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D247" s="2"/>
       <c r="E247" s="11"/>
       <c r="G247" s="4"/>
@@ -4732,7 +4732,7 @@
       <c r="P247" s="11"/>
       <c r="Q247" s="4"/>
     </row>
-    <row r="248" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="248" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D248" s="2"/>
       <c r="E248" s="11"/>
       <c r="G248" s="4"/>
@@ -4744,7 +4744,7 @@
       <c r="P248" s="11"/>
       <c r="Q248" s="4"/>
     </row>
-    <row r="249" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="249" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D249" s="2"/>
       <c r="E249" s="11"/>
       <c r="G249" s="4"/>
@@ -4756,7 +4756,7 @@
       <c r="P249" s="11"/>
       <c r="Q249" s="4"/>
     </row>
-    <row r="250" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="250" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D250" s="2"/>
       <c r="E250" s="11"/>
       <c r="G250" s="4"/>
@@ -4768,7 +4768,7 @@
       <c r="P250" s="11"/>
       <c r="Q250" s="4"/>
     </row>
-    <row r="251" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="251" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D251" s="2"/>
       <c r="E251" s="11"/>
       <c r="G251" s="4"/>
@@ -4780,7 +4780,7 @@
       <c r="P251" s="11"/>
       <c r="Q251" s="4"/>
     </row>
-    <row r="252" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="252" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D252" s="2"/>
       <c r="E252" s="11"/>
       <c r="G252" s="4"/>
@@ -4792,7 +4792,7 @@
       <c r="P252" s="11"/>
       <c r="Q252" s="4"/>
     </row>
-    <row r="253" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="253" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D253" s="2"/>
       <c r="E253" s="11"/>
       <c r="G253" s="4"/>
@@ -4804,7 +4804,7 @@
       <c r="P253" s="11"/>
       <c r="Q253" s="4"/>
     </row>
-    <row r="254" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="254" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D254" s="2"/>
       <c r="E254" s="11"/>
       <c r="G254" s="4"/>
@@ -4816,7 +4816,7 @@
       <c r="P254" s="11"/>
       <c r="Q254" s="4"/>
     </row>
-    <row r="255" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="255" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D255" s="2"/>
       <c r="E255" s="11"/>
       <c r="G255" s="4"/>
@@ -4828,7 +4828,7 @@
       <c r="P255" s="11"/>
       <c r="Q255" s="4"/>
     </row>
-    <row r="256" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="256" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D256" s="2"/>
       <c r="E256" s="11"/>
       <c r="G256" s="4"/>
@@ -4840,7 +4840,7 @@
       <c r="P256" s="11"/>
       <c r="Q256" s="4"/>
     </row>
-    <row r="257" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="257" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D257" s="2"/>
       <c r="E257" s="11"/>
       <c r="G257" s="4"/>
@@ -4852,7 +4852,7 @@
       <c r="P257" s="11"/>
       <c r="Q257" s="4"/>
     </row>
-    <row r="258" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="258" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D258" s="2"/>
       <c r="E258" s="11"/>
       <c r="G258" s="4"/>
@@ -4864,7 +4864,7 @@
       <c r="P258" s="11"/>
       <c r="Q258" s="4"/>
     </row>
-    <row r="259" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="259" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D259" s="2"/>
       <c r="E259" s="11"/>
       <c r="G259" s="4"/>
@@ -4876,7 +4876,7 @@
       <c r="P259" s="11"/>
       <c r="Q259" s="4"/>
     </row>
-    <row r="260" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="260" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D260" s="2"/>
       <c r="E260" s="11"/>
       <c r="G260" s="4"/>
@@ -4888,7 +4888,7 @@
       <c r="P260" s="11"/>
       <c r="Q260" s="4"/>
     </row>
-    <row r="261" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="261" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D261" s="2"/>
       <c r="E261" s="11"/>
       <c r="G261" s="4"/>
@@ -4900,7 +4900,7 @@
       <c r="P261" s="11"/>
       <c r="Q261" s="4"/>
     </row>
-    <row r="262" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="262" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D262" s="2"/>
       <c r="E262" s="11"/>
       <c r="G262" s="4"/>
@@ -4912,7 +4912,7 @@
       <c r="P262" s="11"/>
       <c r="Q262" s="4"/>
     </row>
-    <row r="263" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="263" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D263" s="2"/>
       <c r="E263" s="11"/>
       <c r="G263" s="4"/>
@@ -4924,7 +4924,7 @@
       <c r="P263" s="11"/>
       <c r="Q263" s="4"/>
     </row>
-    <row r="264" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="264" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D264" s="2"/>
       <c r="E264" s="11"/>
       <c r="G264" s="4"/>
@@ -4936,7 +4936,7 @@
       <c r="P264" s="11"/>
       <c r="Q264" s="4"/>
     </row>
-    <row r="265" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="265" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D265" s="2"/>
       <c r="E265" s="11"/>
       <c r="G265" s="4"/>
@@ -4948,7 +4948,7 @@
       <c r="P265" s="11"/>
       <c r="Q265" s="4"/>
     </row>
-    <row r="266" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="266" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D266" s="2"/>
       <c r="E266" s="11"/>
       <c r="G266" s="4"/>
@@ -4960,7 +4960,7 @@
       <c r="P266" s="11"/>
       <c r="Q266" s="4"/>
     </row>
-    <row r="267" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="267" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D267" s="2"/>
       <c r="E267" s="11"/>
       <c r="G267" s="4"/>
@@ -4972,7 +4972,7 @@
       <c r="P267" s="11"/>
       <c r="Q267" s="4"/>
     </row>
-    <row r="268" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="268" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D268" s="2"/>
       <c r="E268" s="11"/>
       <c r="G268" s="4"/>
@@ -4984,7 +4984,7 @@
       <c r="P268" s="11"/>
       <c r="Q268" s="4"/>
     </row>
-    <row r="269" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="269" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D269" s="2"/>
       <c r="E269" s="11"/>
       <c r="G269" s="4"/>
@@ -4996,7 +4996,7 @@
       <c r="P269" s="11"/>
       <c r="Q269" s="4"/>
     </row>
-    <row r="270" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="270" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D270" s="2"/>
       <c r="E270" s="11"/>
       <c r="G270" s="4"/>
@@ -5008,7 +5008,7 @@
       <c r="P270" s="11"/>
       <c r="Q270" s="4"/>
     </row>
-    <row r="271" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="271" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D271" s="2"/>
       <c r="E271" s="11"/>
       <c r="G271" s="4"/>
@@ -5020,7 +5020,7 @@
       <c r="P271" s="11"/>
       <c r="Q271" s="4"/>
     </row>
-    <row r="272" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="272" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D272" s="2"/>
       <c r="E272" s="11"/>
       <c r="G272" s="4"/>
@@ -5032,7 +5032,7 @@
       <c r="P272" s="11"/>
       <c r="Q272" s="4"/>
     </row>
-    <row r="273" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="273" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D273" s="2"/>
       <c r="E273" s="11"/>
       <c r="G273" s="4"/>
@@ -5044,7 +5044,7 @@
       <c r="P273" s="11"/>
       <c r="Q273" s="4"/>
     </row>
-    <row r="274" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="274" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D274" s="2"/>
       <c r="E274" s="11"/>
       <c r="G274" s="4"/>
@@ -5056,7 +5056,7 @@
       <c r="P274" s="11"/>
       <c r="Q274" s="4"/>
     </row>
-    <row r="275" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="275" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D275" s="2"/>
       <c r="E275" s="11"/>
       <c r="G275" s="4"/>
@@ -5068,7 +5068,7 @@
       <c r="P275" s="11"/>
       <c r="Q275" s="4"/>
     </row>
-    <row r="276" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="276" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D276" s="2"/>
       <c r="E276" s="11"/>
       <c r="G276" s="4"/>
@@ -5080,7 +5080,7 @@
       <c r="P276" s="11"/>
       <c r="Q276" s="4"/>
     </row>
-    <row r="277" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="277" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D277" s="2"/>
       <c r="E277" s="11"/>
       <c r="G277" s="4"/>
@@ -5092,7 +5092,7 @@
       <c r="P277" s="11"/>
       <c r="Q277" s="4"/>
     </row>
-    <row r="278" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="278" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D278" s="2"/>
       <c r="E278" s="11"/>
       <c r="G278" s="4"/>
@@ -5104,7 +5104,7 @@
       <c r="P278" s="11"/>
       <c r="Q278" s="4"/>
     </row>
-    <row r="279" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="279" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D279" s="2"/>
       <c r="E279" s="11"/>
       <c r="G279" s="4"/>
@@ -5116,7 +5116,7 @@
       <c r="P279" s="11"/>
       <c r="Q279" s="4"/>
     </row>
-    <row r="280" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="280" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D280" s="2"/>
       <c r="E280" s="11"/>
       <c r="G280" s="4"/>
@@ -5128,7 +5128,7 @@
       <c r="P280" s="11"/>
       <c r="Q280" s="4"/>
     </row>
-    <row r="281" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="281" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D281" s="2"/>
       <c r="E281" s="11"/>
       <c r="G281" s="4"/>
@@ -5140,7 +5140,7 @@
       <c r="P281" s="11"/>
       <c r="Q281" s="4"/>
     </row>
-    <row r="282" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="282" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D282" s="2"/>
       <c r="E282" s="11"/>
       <c r="G282" s="4"/>
@@ -5152,7 +5152,7 @@
       <c r="P282" s="11"/>
       <c r="Q282" s="4"/>
     </row>
-    <row r="283" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="283" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D283" s="2"/>
       <c r="E283" s="11"/>
       <c r="G283" s="4"/>
@@ -5164,7 +5164,7 @@
       <c r="P283" s="11"/>
       <c r="Q283" s="4"/>
     </row>
-    <row r="284" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="284" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D284" s="2"/>
       <c r="E284" s="11"/>
       <c r="G284" s="4"/>
@@ -5176,7 +5176,7 @@
       <c r="P284" s="11"/>
       <c r="Q284" s="4"/>
     </row>
-    <row r="285" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="285" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D285" s="2"/>
       <c r="E285" s="11"/>
       <c r="G285" s="4"/>
@@ -5188,7 +5188,7 @@
       <c r="P285" s="11"/>
       <c r="Q285" s="4"/>
     </row>
-    <row r="286" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="286" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D286" s="2"/>
       <c r="E286" s="11"/>
       <c r="G286" s="4"/>
@@ -5200,7 +5200,7 @@
       <c r="P286" s="11"/>
       <c r="Q286" s="4"/>
     </row>
-    <row r="287" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="287" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D287" s="2"/>
       <c r="E287" s="11"/>
       <c r="G287" s="4"/>
@@ -5212,7 +5212,7 @@
       <c r="P287" s="11"/>
       <c r="Q287" s="4"/>
     </row>
-    <row r="288" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="288" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D288" s="2"/>
       <c r="E288" s="11"/>
       <c r="G288" s="4"/>
@@ -5224,7 +5224,7 @@
       <c r="P288" s="11"/>
       <c r="Q288" s="4"/>
     </row>
-    <row r="289" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="289" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D289" s="2"/>
       <c r="E289" s="11"/>
       <c r="G289" s="4"/>
@@ -5236,7 +5236,7 @@
       <c r="P289" s="11"/>
       <c r="Q289" s="4"/>
     </row>
-    <row r="290" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="290" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D290" s="2"/>
       <c r="E290" s="11"/>
       <c r="G290" s="4"/>
@@ -5248,7 +5248,7 @@
       <c r="P290" s="11"/>
       <c r="Q290" s="4"/>
     </row>
-    <row r="291" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="291" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D291" s="2"/>
       <c r="E291" s="11"/>
       <c r="G291" s="4"/>
@@ -5260,7 +5260,7 @@
       <c r="P291" s="11"/>
       <c r="Q291" s="4"/>
     </row>
-    <row r="292" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="292" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D292" s="2"/>
       <c r="E292" s="11"/>
       <c r="G292" s="4"/>
@@ -5272,7 +5272,7 @@
       <c r="P292" s="11"/>
       <c r="Q292" s="4"/>
     </row>
-    <row r="293" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="293" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D293" s="2"/>
       <c r="E293" s="11"/>
       <c r="G293" s="4"/>
@@ -5284,7 +5284,7 @@
       <c r="P293" s="11"/>
       <c r="Q293" s="4"/>
     </row>
-    <row r="294" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="294" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D294" s="2"/>
       <c r="E294" s="11"/>
       <c r="G294" s="4"/>
@@ -5296,7 +5296,7 @@
       <c r="P294" s="11"/>
       <c r="Q294" s="4"/>
     </row>
-    <row r="295" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="295" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D295" s="2"/>
       <c r="E295" s="11"/>
       <c r="G295" s="4"/>
@@ -5308,7 +5308,7 @@
       <c r="P295" s="11"/>
       <c r="Q295" s="4"/>
     </row>
-    <row r="296" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="296" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D296" s="2"/>
       <c r="E296" s="11"/>
       <c r="G296" s="4"/>
@@ -5320,7 +5320,7 @@
       <c r="P296" s="11"/>
       <c r="Q296" s="4"/>
     </row>
-    <row r="297" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="297" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D297" s="2"/>
       <c r="E297" s="11"/>
       <c r="G297" s="4"/>
@@ -5332,7 +5332,7 @@
       <c r="P297" s="11"/>
       <c r="Q297" s="4"/>
     </row>
-    <row r="298" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="298" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D298" s="2"/>
       <c r="E298" s="11"/>
       <c r="G298" s="4"/>
@@ -5344,7 +5344,7 @@
       <c r="P298" s="11"/>
       <c r="Q298" s="4"/>
     </row>
-    <row r="299" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="299" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D299" s="2"/>
       <c r="E299" s="11"/>
       <c r="G299" s="4"/>
@@ -5356,7 +5356,7 @@
       <c r="P299" s="11"/>
       <c r="Q299" s="4"/>
     </row>
-    <row r="300" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="300" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D300" s="2"/>
       <c r="E300" s="11"/>
       <c r="G300" s="4"/>
@@ -5368,7 +5368,7 @@
       <c r="P300" s="11"/>
       <c r="Q300" s="4"/>
     </row>
-    <row r="301" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="301" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D301" s="2"/>
       <c r="E301" s="11"/>
       <c r="G301" s="4"/>
@@ -5380,7 +5380,7 @@
       <c r="P301" s="11"/>
       <c r="Q301" s="4"/>
     </row>
-    <row r="302" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="302" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D302" s="2"/>
       <c r="E302" s="11"/>
       <c r="G302" s="4"/>
@@ -5392,7 +5392,7 @@
       <c r="P302" s="11"/>
       <c r="Q302" s="4"/>
     </row>
-    <row r="303" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="303" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D303" s="2"/>
       <c r="E303" s="11"/>
       <c r="G303" s="4"/>
@@ -5404,7 +5404,7 @@
       <c r="P303" s="11"/>
       <c r="Q303" s="4"/>
     </row>
-    <row r="304" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="304" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D304" s="2"/>
       <c r="E304" s="11"/>
       <c r="G304" s="4"/>
@@ -5416,7 +5416,7 @@
       <c r="P304" s="11"/>
       <c r="Q304" s="4"/>
     </row>
-    <row r="305" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="305" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D305" s="2"/>
       <c r="E305" s="11"/>
       <c r="G305" s="4"/>
@@ -5428,7 +5428,7 @@
       <c r="P305" s="11"/>
       <c r="Q305" s="4"/>
     </row>
-    <row r="306" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="306" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D306" s="2"/>
       <c r="E306" s="11"/>
       <c r="G306" s="4"/>
@@ -5440,7 +5440,7 @@
       <c r="P306" s="11"/>
       <c r="Q306" s="4"/>
     </row>
-    <row r="307" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="307" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D307" s="2"/>
       <c r="E307" s="11"/>
       <c r="G307" s="4"/>
@@ -5452,7 +5452,7 @@
       <c r="P307" s="11"/>
       <c r="Q307" s="4"/>
     </row>
-    <row r="308" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="308" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D308" s="2"/>
       <c r="E308" s="11"/>
       <c r="G308" s="4"/>
@@ -5464,7 +5464,7 @@
       <c r="P308" s="11"/>
       <c r="Q308" s="4"/>
     </row>
-    <row r="309" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="309" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D309" s="2"/>
       <c r="E309" s="11"/>
       <c r="G309" s="4"/>
@@ -5476,7 +5476,7 @@
       <c r="P309" s="11"/>
       <c r="Q309" s="4"/>
     </row>
-    <row r="310" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="310" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D310" s="2"/>
       <c r="E310" s="11"/>
       <c r="G310" s="4"/>
@@ -5488,7 +5488,7 @@
       <c r="P310" s="11"/>
       <c r="Q310" s="4"/>
     </row>
-    <row r="311" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="311" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D311" s="2"/>
       <c r="E311" s="11"/>
       <c r="G311" s="4"/>
@@ -5500,7 +5500,7 @@
       <c r="P311" s="11"/>
       <c r="Q311" s="4"/>
     </row>
-    <row r="312" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="312" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D312" s="2"/>
       <c r="E312" s="11"/>
       <c r="G312" s="4"/>
@@ -5512,7 +5512,7 @@
       <c r="P312" s="11"/>
       <c r="Q312" s="4"/>
     </row>
-    <row r="313" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="313" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D313" s="2"/>
       <c r="E313" s="11"/>
       <c r="G313" s="4"/>
@@ -5524,7 +5524,7 @@
       <c r="P313" s="11"/>
       <c r="Q313" s="4"/>
     </row>
-    <row r="314" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="314" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D314" s="2"/>
       <c r="E314" s="11"/>
       <c r="G314" s="4"/>
@@ -5536,7 +5536,7 @@
       <c r="P314" s="11"/>
       <c r="Q314" s="4"/>
     </row>
-    <row r="315" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="315" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D315" s="2"/>
       <c r="E315" s="11"/>
       <c r="G315" s="4"/>
@@ -5548,7 +5548,7 @@
       <c r="P315" s="11"/>
       <c r="Q315" s="4"/>
     </row>
-    <row r="316" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="316" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D316" s="2"/>
       <c r="E316" s="11"/>
       <c r="G316" s="4"/>
@@ -5560,7 +5560,7 @@
       <c r="P316" s="11"/>
       <c r="Q316" s="4"/>
     </row>
-    <row r="317" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="317" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D317" s="2"/>
       <c r="E317" s="11"/>
       <c r="G317" s="4"/>
@@ -5572,7 +5572,7 @@
       <c r="P317" s="11"/>
       <c r="Q317" s="4"/>
     </row>
-    <row r="318" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="318" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D318" s="2"/>
       <c r="E318" s="11"/>
       <c r="G318" s="4"/>
@@ -5584,7 +5584,7 @@
       <c r="P318" s="11"/>
       <c r="Q318" s="4"/>
     </row>
-    <row r="319" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="319" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D319" s="2"/>
       <c r="E319" s="11"/>
       <c r="G319" s="4"/>
@@ -5596,7 +5596,7 @@
       <c r="P319" s="11"/>
       <c r="Q319" s="4"/>
     </row>
-    <row r="320" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="320" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D320" s="2"/>
       <c r="E320" s="11"/>
       <c r="G320" s="4"/>
@@ -5608,7 +5608,7 @@
       <c r="P320" s="11"/>
       <c r="Q320" s="4"/>
     </row>
-    <row r="321" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="321" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D321" s="2"/>
       <c r="E321" s="11"/>
       <c r="G321" s="4"/>
@@ -5620,7 +5620,7 @@
       <c r="P321" s="11"/>
       <c r="Q321" s="4"/>
     </row>
-    <row r="322" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="322" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D322" s="2"/>
       <c r="E322" s="11"/>
       <c r="G322" s="4"/>
@@ -5632,7 +5632,7 @@
       <c r="P322" s="11"/>
       <c r="Q322" s="4"/>
     </row>
-    <row r="323" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="323" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D323" s="2"/>
       <c r="E323" s="11"/>
       <c r="G323" s="4"/>
@@ -5644,7 +5644,7 @@
       <c r="P323" s="11"/>
       <c r="Q323" s="4"/>
     </row>
-    <row r="324" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="324" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D324" s="2"/>
       <c r="E324" s="11"/>
       <c r="G324" s="4"/>
@@ -5656,7 +5656,7 @@
       <c r="P324" s="11"/>
       <c r="Q324" s="4"/>
     </row>
-    <row r="325" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="325" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D325" s="2"/>
       <c r="E325" s="11"/>
       <c r="G325" s="4"/>
@@ -5668,7 +5668,7 @@
       <c r="P325" s="11"/>
       <c r="Q325" s="4"/>
     </row>
-    <row r="326" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="326" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D326" s="2"/>
       <c r="E326" s="11"/>
       <c r="G326" s="4"/>
@@ -5680,7 +5680,7 @@
       <c r="P326" s="11"/>
       <c r="Q326" s="4"/>
     </row>
-    <row r="327" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="327" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D327" s="2"/>
       <c r="E327" s="11"/>
       <c r="G327" s="4"/>
@@ -5692,7 +5692,7 @@
       <c r="P327" s="11"/>
       <c r="Q327" s="4"/>
     </row>
-    <row r="328" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="328" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D328" s="2"/>
       <c r="E328" s="11"/>
       <c r="G328" s="4"/>
@@ -5704,7 +5704,7 @@
       <c r="P328" s="11"/>
       <c r="Q328" s="4"/>
     </row>
-    <row r="329" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="329" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D329" s="2"/>
       <c r="E329" s="11"/>
       <c r="G329" s="4"/>
@@ -5716,7 +5716,7 @@
       <c r="P329" s="11"/>
       <c r="Q329" s="4"/>
     </row>
-    <row r="330" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="330" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D330" s="2"/>
       <c r="E330" s="11"/>
       <c r="G330" s="4"/>
@@ -5728,7 +5728,7 @@
       <c r="P330" s="11"/>
       <c r="Q330" s="4"/>
     </row>
-    <row r="331" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="331" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D331" s="2"/>
       <c r="E331" s="11"/>
       <c r="G331" s="4"/>
@@ -5740,7 +5740,7 @@
       <c r="P331" s="11"/>
       <c r="Q331" s="4"/>
     </row>
-    <row r="332" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="332" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D332" s="2"/>
       <c r="E332" s="11"/>
       <c r="G332" s="4"/>
@@ -5752,7 +5752,7 @@
       <c r="P332" s="11"/>
       <c r="Q332" s="4"/>
     </row>
-    <row r="333" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="333" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D333" s="2"/>
       <c r="E333" s="11"/>
       <c r="G333" s="4"/>
@@ -5764,7 +5764,7 @@
       <c r="P333" s="11"/>
       <c r="Q333" s="4"/>
     </row>
-    <row r="334" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="334" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D334" s="2"/>
       <c r="E334" s="11"/>
       <c r="G334" s="4"/>
@@ -5776,7 +5776,7 @@
       <c r="P334" s="11"/>
       <c r="Q334" s="4"/>
     </row>
-    <row r="335" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="335" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D335" s="2"/>
       <c r="E335" s="11"/>
       <c r="G335" s="4"/>
@@ -5788,7 +5788,7 @@
       <c r="P335" s="11"/>
       <c r="Q335" s="4"/>
     </row>
-    <row r="336" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="336" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D336" s="2"/>
       <c r="E336" s="11"/>
       <c r="G336" s="4"/>
@@ -5800,7 +5800,7 @@
       <c r="P336" s="11"/>
       <c r="Q336" s="4"/>
     </row>
-    <row r="337" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="337" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D337" s="2"/>
       <c r="E337" s="11"/>
       <c r="G337" s="4"/>
@@ -5812,7 +5812,7 @@
       <c r="P337" s="11"/>
       <c r="Q337" s="4"/>
     </row>
-    <row r="338" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="338" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D338" s="2"/>
       <c r="E338" s="11"/>
       <c r="G338" s="4"/>
@@ -5824,7 +5824,7 @@
       <c r="P338" s="11"/>
       <c r="Q338" s="4"/>
     </row>
-    <row r="339" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="339" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D339" s="2"/>
       <c r="E339" s="11"/>
       <c r="G339" s="4"/>
@@ -5836,7 +5836,7 @@
       <c r="P339" s="11"/>
       <c r="Q339" s="4"/>
     </row>
-    <row r="340" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="340" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D340" s="2"/>
       <c r="E340" s="11"/>
       <c r="G340" s="4"/>
@@ -5848,7 +5848,7 @@
       <c r="P340" s="11"/>
       <c r="Q340" s="4"/>
     </row>
-    <row r="341" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="341" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D341" s="2"/>
       <c r="E341" s="11"/>
       <c r="G341" s="4"/>
@@ -5860,7 +5860,7 @@
       <c r="P341" s="11"/>
       <c r="Q341" s="4"/>
     </row>
-    <row r="342" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="342" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D342" s="2"/>
       <c r="E342" s="11"/>
       <c r="G342" s="4"/>
@@ -5872,7 +5872,7 @@
       <c r="P342" s="11"/>
       <c r="Q342" s="4"/>
     </row>
-    <row r="343" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="343" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D343" s="2"/>
       <c r="E343" s="11"/>
       <c r="G343" s="4"/>
@@ -5884,7 +5884,7 @@
       <c r="P343" s="11"/>
       <c r="Q343" s="4"/>
     </row>
-    <row r="344" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="344" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D344" s="2"/>
       <c r="E344" s="11"/>
       <c r="G344" s="4"/>
@@ -5896,7 +5896,7 @@
       <c r="P344" s="11"/>
       <c r="Q344" s="4"/>
     </row>
-    <row r="345" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="345" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D345" s="2"/>
       <c r="E345" s="11"/>
       <c r="G345" s="4"/>
@@ -5908,7 +5908,7 @@
       <c r="P345" s="11"/>
       <c r="Q345" s="4"/>
     </row>
-    <row r="346" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="346" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D346" s="2"/>
       <c r="E346" s="11"/>
       <c r="G346" s="4"/>
@@ -5920,7 +5920,7 @@
       <c r="P346" s="11"/>
       <c r="Q346" s="4"/>
     </row>
-    <row r="347" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="347" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D347" s="2"/>
       <c r="E347" s="11"/>
       <c r="G347" s="4"/>
@@ -5932,7 +5932,7 @@
       <c r="P347" s="11"/>
       <c r="Q347" s="4"/>
     </row>
-    <row r="348" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="348" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D348" s="2"/>
       <c r="E348" s="11"/>
       <c r="G348" s="4"/>
@@ -5944,7 +5944,7 @@
       <c r="P348" s="11"/>
       <c r="Q348" s="4"/>
     </row>
-    <row r="349" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="349" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D349" s="2"/>
       <c r="E349" s="11"/>
       <c r="G349" s="4"/>
@@ -5956,7 +5956,7 @@
       <c r="P349" s="11"/>
       <c r="Q349" s="4"/>
     </row>
-    <row r="350" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="350" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D350" s="2"/>
       <c r="E350" s="11"/>
       <c r="G350" s="4"/>
@@ -5968,7 +5968,7 @@
       <c r="P350" s="11"/>
       <c r="Q350" s="4"/>
     </row>
-    <row r="351" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="351" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D351" s="2"/>
       <c r="E351" s="11"/>
       <c r="G351" s="4"/>
@@ -5980,7 +5980,7 @@
       <c r="P351" s="11"/>
       <c r="Q351" s="4"/>
     </row>
-    <row r="352" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="352" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D352" s="2"/>
       <c r="E352" s="11"/>
       <c r="G352" s="4"/>
@@ -5992,7 +5992,7 @@
       <c r="P352" s="11"/>
       <c r="Q352" s="4"/>
     </row>
-    <row r="353" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="353" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D353" s="2"/>
       <c r="E353" s="11"/>
       <c r="G353" s="4"/>
@@ -6004,7 +6004,7 @@
       <c r="P353" s="11"/>
       <c r="Q353" s="4"/>
     </row>
-    <row r="354" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="354" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D354" s="2"/>
       <c r="E354" s="11"/>
       <c r="G354" s="4"/>
@@ -6016,7 +6016,7 @@
       <c r="P354" s="11"/>
       <c r="Q354" s="4"/>
     </row>
-    <row r="355" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="355" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D355" s="2"/>
       <c r="E355" s="11"/>
       <c r="G355" s="4"/>
@@ -6028,7 +6028,7 @@
       <c r="P355" s="11"/>
       <c r="Q355" s="4"/>
     </row>
-    <row r="356" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="356" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D356" s="2"/>
       <c r="E356" s="11"/>
       <c r="G356" s="4"/>
@@ -6040,7 +6040,7 @@
       <c r="P356" s="11"/>
       <c r="Q356" s="4"/>
     </row>
-    <row r="357" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="357" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D357" s="2"/>
       <c r="E357" s="11"/>
       <c r="G357" s="4"/>
@@ -6052,7 +6052,7 @@
       <c r="P357" s="11"/>
       <c r="Q357" s="4"/>
     </row>
-    <row r="358" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="358" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D358" s="2"/>
       <c r="E358" s="11"/>
       <c r="G358" s="4"/>
@@ -6064,7 +6064,7 @@
       <c r="P358" s="11"/>
       <c r="Q358" s="4"/>
     </row>
-    <row r="359" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="359" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D359" s="2"/>
       <c r="E359" s="11"/>
       <c r="G359" s="4"/>
@@ -6076,7 +6076,7 @@
       <c r="P359" s="11"/>
       <c r="Q359" s="4"/>
     </row>
-    <row r="360" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="360" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D360" s="2"/>
       <c r="E360" s="11"/>
       <c r="G360" s="4"/>
@@ -6088,7 +6088,7 @@
       <c r="P360" s="11"/>
       <c r="Q360" s="4"/>
     </row>
-    <row r="361" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="361" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D361" s="2"/>
       <c r="E361" s="11"/>
       <c r="G361" s="4"/>
@@ -6100,7 +6100,7 @@
       <c r="P361" s="11"/>
       <c r="Q361" s="4"/>
     </row>
-    <row r="362" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="362" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D362" s="2"/>
       <c r="E362" s="11"/>
       <c r="G362" s="4"/>
@@ -6112,7 +6112,7 @@
       <c r="P362" s="11"/>
       <c r="Q362" s="4"/>
     </row>
-    <row r="363" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="363" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D363" s="2"/>
       <c r="E363" s="11"/>
       <c r="G363" s="4"/>
@@ -6124,7 +6124,7 @@
       <c r="P363" s="11"/>
       <c r="Q363" s="4"/>
     </row>
-    <row r="364" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="364" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D364" s="2"/>
       <c r="E364" s="11"/>
       <c r="G364" s="4"/>
@@ -6136,7 +6136,7 @@
       <c r="P364" s="11"/>
       <c r="Q364" s="4"/>
     </row>
-    <row r="365" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="365" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D365" s="2"/>
       <c r="E365" s="11"/>
       <c r="G365" s="4"/>
@@ -6148,7 +6148,7 @@
       <c r="P365" s="11"/>
       <c r="Q365" s="4"/>
     </row>
-    <row r="366" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="366" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D366" s="2"/>
       <c r="E366" s="11"/>
       <c r="G366" s="4"/>
@@ -6160,7 +6160,7 @@
       <c r="P366" s="11"/>
       <c r="Q366" s="4"/>
     </row>
-    <row r="367" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="367" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D367" s="2"/>
       <c r="E367" s="11"/>
       <c r="G367" s="4"/>
@@ -6172,7 +6172,7 @@
       <c r="P367" s="11"/>
       <c r="Q367" s="4"/>
     </row>
-    <row r="368" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="368" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D368" s="2"/>
       <c r="E368" s="11"/>
       <c r="G368" s="4"/>
@@ -6184,7 +6184,7 @@
       <c r="P368" s="11"/>
       <c r="Q368" s="4"/>
     </row>
-    <row r="369" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="369" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D369" s="2"/>
       <c r="E369" s="11"/>
       <c r="G369" s="4"/>
@@ -6196,7 +6196,7 @@
       <c r="P369" s="11"/>
       <c r="Q369" s="4"/>
     </row>
-    <row r="370" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="370" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D370" s="2"/>
       <c r="E370" s="11"/>
       <c r="G370" s="4"/>
@@ -6208,7 +6208,7 @@
       <c r="P370" s="11"/>
       <c r="Q370" s="4"/>
     </row>
-    <row r="371" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="371" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D371" s="2"/>
       <c r="E371" s="11"/>
       <c r="G371" s="4"/>
@@ -6220,7 +6220,7 @@
       <c r="P371" s="11"/>
       <c r="Q371" s="4"/>
     </row>
-    <row r="372" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="372" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D372" s="2"/>
       <c r="E372" s="11"/>
       <c r="G372" s="4"/>
@@ -6232,7 +6232,7 @@
       <c r="P372" s="11"/>
       <c r="Q372" s="4"/>
     </row>
-    <row r="373" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="373" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D373" s="2"/>
       <c r="E373" s="11"/>
       <c r="G373" s="4"/>
@@ -6244,7 +6244,7 @@
       <c r="P373" s="11"/>
       <c r="Q373" s="4"/>
     </row>
-    <row r="374" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="374" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D374" s="2"/>
       <c r="E374" s="11"/>
       <c r="G374" s="4"/>
@@ -6256,7 +6256,7 @@
       <c r="P374" s="11"/>
       <c r="Q374" s="4"/>
     </row>
-    <row r="375" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="375" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D375" s="2"/>
       <c r="E375" s="11"/>
       <c r="G375" s="4"/>
@@ -6268,7 +6268,7 @@
       <c r="P375" s="11"/>
       <c r="Q375" s="4"/>
     </row>
-    <row r="376" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="376" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D376" s="2"/>
       <c r="E376" s="11"/>
       <c r="G376" s="4"/>
@@ -6280,7 +6280,7 @@
       <c r="P376" s="11"/>
       <c r="Q376" s="4"/>
     </row>
-    <row r="377" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="377" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D377" s="2"/>
       <c r="E377" s="11"/>
       <c r="G377" s="4"/>
@@ -6292,7 +6292,7 @@
       <c r="P377" s="11"/>
       <c r="Q377" s="4"/>
     </row>
-    <row r="378" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="378" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D378" s="2"/>
       <c r="E378" s="11"/>
       <c r="G378" s="4"/>
@@ -6304,7 +6304,7 @@
       <c r="P378" s="11"/>
       <c r="Q378" s="4"/>
     </row>
-    <row r="379" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="379" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D379" s="2"/>
       <c r="E379" s="11"/>
       <c r="G379" s="4"/>
@@ -6316,7 +6316,7 @@
       <c r="P379" s="11"/>
       <c r="Q379" s="4"/>
     </row>
-    <row r="380" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="380" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D380" s="2"/>
       <c r="E380" s="11"/>
       <c r="G380" s="4"/>
@@ -6328,7 +6328,7 @@
       <c r="P380" s="11"/>
       <c r="Q380" s="4"/>
     </row>
-    <row r="381" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="381" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D381" s="2"/>
       <c r="E381" s="11"/>
       <c r="G381" s="4"/>
@@ -6340,7 +6340,7 @@
       <c r="P381" s="11"/>
       <c r="Q381" s="4"/>
     </row>
-    <row r="382" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="382" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D382" s="2"/>
       <c r="E382" s="11"/>
       <c r="G382" s="4"/>
@@ -6352,7 +6352,7 @@
       <c r="P382" s="11"/>
       <c r="Q382" s="4"/>
     </row>
-    <row r="383" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="383" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D383" s="2"/>
       <c r="E383" s="11"/>
       <c r="G383" s="4"/>
@@ -6364,7 +6364,7 @@
       <c r="P383" s="11"/>
       <c r="Q383" s="4"/>
     </row>
-    <row r="384" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="384" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D384" s="2"/>
       <c r="E384" s="11"/>
       <c r="G384" s="4"/>
@@ -6376,7 +6376,7 @@
       <c r="P384" s="11"/>
       <c r="Q384" s="4"/>
     </row>
-    <row r="385" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="385" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D385" s="2"/>
       <c r="E385" s="11"/>
       <c r="G385" s="4"/>
@@ -6388,7 +6388,7 @@
       <c r="P385" s="11"/>
       <c r="Q385" s="4"/>
     </row>
-    <row r="386" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="386" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D386" s="2"/>
       <c r="E386" s="11"/>
       <c r="G386" s="4"/>
@@ -6400,7 +6400,7 @@
       <c r="P386" s="11"/>
       <c r="Q386" s="4"/>
     </row>
-    <row r="387" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="387" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D387" s="2"/>
       <c r="E387" s="11"/>
       <c r="G387" s="4"/>
@@ -6412,7 +6412,7 @@
       <c r="P387" s="11"/>
       <c r="Q387" s="4"/>
     </row>
-    <row r="388" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="388" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D388" s="2"/>
       <c r="E388" s="11"/>
       <c r="G388" s="4"/>
@@ -6424,7 +6424,7 @@
       <c r="P388" s="11"/>
       <c r="Q388" s="4"/>
     </row>
-    <row r="389" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="389" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D389" s="2"/>
       <c r="E389" s="11"/>
       <c r="G389" s="4"/>
@@ -6436,7 +6436,7 @@
       <c r="P389" s="11"/>
       <c r="Q389" s="4"/>
     </row>
-    <row r="390" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="390" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D390" s="2"/>
       <c r="E390" s="11"/>
       <c r="G390" s="4"/>
@@ -6448,7 +6448,7 @@
       <c r="P390" s="11"/>
       <c r="Q390" s="4"/>
     </row>
-    <row r="391" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="391" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D391" s="2"/>
       <c r="E391" s="11"/>
       <c r="G391" s="4"/>
@@ -6460,7 +6460,7 @@
       <c r="P391" s="11"/>
       <c r="Q391" s="4"/>
     </row>
-    <row r="392" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="392" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D392" s="2"/>
       <c r="E392" s="11"/>
       <c r="G392" s="4"/>
@@ -6472,7 +6472,7 @@
       <c r="P392" s="11"/>
       <c r="Q392" s="4"/>
     </row>
-    <row r="393" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="393" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D393" s="2"/>
       <c r="E393" s="11"/>
       <c r="G393" s="4"/>
@@ -6484,7 +6484,7 @@
       <c r="P393" s="11"/>
       <c r="Q393" s="4"/>
     </row>
-    <row r="394" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="394" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D394" s="2"/>
       <c r="E394" s="11"/>
       <c r="G394" s="4"/>
@@ -6496,7 +6496,7 @@
       <c r="P394" s="11"/>
       <c r="Q394" s="4"/>
     </row>
-    <row r="395" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="395" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D395" s="2"/>
       <c r="E395" s="11"/>
       <c r="G395" s="4"/>
@@ -6508,7 +6508,7 @@
       <c r="P395" s="11"/>
       <c r="Q395" s="4"/>
     </row>
-    <row r="396" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="396" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D396" s="2"/>
       <c r="E396" s="11"/>
       <c r="G396" s="4"/>
@@ -6520,7 +6520,7 @@
       <c r="P396" s="11"/>
       <c r="Q396" s="4"/>
     </row>
-    <row r="397" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="397" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D397" s="2"/>
       <c r="E397" s="11"/>
       <c r="G397" s="4"/>
@@ -6532,7 +6532,7 @@
       <c r="P397" s="11"/>
       <c r="Q397" s="4"/>
     </row>
-    <row r="398" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="398" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D398" s="2"/>
       <c r="E398" s="11"/>
       <c r="G398" s="4"/>
@@ -6544,7 +6544,7 @@
       <c r="P398" s="11"/>
       <c r="Q398" s="4"/>
     </row>
-    <row r="399" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="399" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D399" s="2"/>
       <c r="E399" s="11"/>
       <c r="G399" s="4"/>
@@ -6556,7 +6556,7 @@
       <c r="P399" s="11"/>
       <c r="Q399" s="4"/>
     </row>
-    <row r="400" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="400" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D400" s="2"/>
       <c r="E400" s="11"/>
       <c r="G400" s="4"/>
@@ -6568,7 +6568,7 @@
       <c r="P400" s="11"/>
       <c r="Q400" s="4"/>
     </row>
-    <row r="401" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="401" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D401" s="2"/>
       <c r="E401" s="11"/>
       <c r="G401" s="4"/>
@@ -6580,7 +6580,7 @@
       <c r="P401" s="11"/>
       <c r="Q401" s="4"/>
     </row>
-    <row r="402" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="402" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D402" s="2"/>
       <c r="E402" s="11"/>
       <c r="G402" s="4"/>
@@ -6592,7 +6592,7 @@
       <c r="P402" s="11"/>
       <c r="Q402" s="4"/>
     </row>
-    <row r="403" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="403" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D403" s="2"/>
       <c r="E403" s="11"/>
       <c r="G403" s="4"/>
@@ -6604,7 +6604,7 @@
       <c r="P403" s="11"/>
       <c r="Q403" s="4"/>
     </row>
-    <row r="404" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="404" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D404" s="2"/>
       <c r="E404" s="11"/>
       <c r="G404" s="4"/>
@@ -6616,7 +6616,7 @@
       <c r="P404" s="11"/>
       <c r="Q404" s="4"/>
     </row>
-    <row r="405" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="405" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D405" s="2"/>
       <c r="E405" s="11"/>
       <c r="G405" s="4"/>
@@ -6628,7 +6628,7 @@
       <c r="P405" s="11"/>
       <c r="Q405" s="4"/>
     </row>
-    <row r="406" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="406" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D406" s="2"/>
       <c r="E406" s="11"/>
       <c r="G406" s="4"/>
@@ -6640,7 +6640,7 @@
       <c r="P406" s="11"/>
       <c r="Q406" s="4"/>
     </row>
-    <row r="407" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="407" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D407" s="2"/>
       <c r="E407" s="11"/>
       <c r="G407" s="4"/>
@@ -6652,7 +6652,7 @@
       <c r="P407" s="11"/>
       <c r="Q407" s="4"/>
     </row>
-    <row r="408" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="408" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D408" s="2"/>
       <c r="E408" s="11"/>
       <c r="G408" s="4"/>
@@ -6664,7 +6664,7 @@
       <c r="P408" s="11"/>
       <c r="Q408" s="4"/>
     </row>
-    <row r="409" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="409" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D409" s="2"/>
       <c r="E409" s="11"/>
       <c r="G409" s="4"/>
@@ -6676,7 +6676,7 @@
       <c r="P409" s="11"/>
       <c r="Q409" s="4"/>
     </row>
-    <row r="410" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="410" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D410" s="2"/>
       <c r="E410" s="11"/>
       <c r="G410" s="4"/>
@@ -6688,7 +6688,7 @@
       <c r="P410" s="11"/>
       <c r="Q410" s="4"/>
     </row>
-    <row r="411" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="411" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D411" s="2"/>
       <c r="E411" s="11"/>
       <c r="G411" s="4"/>
@@ -6700,7 +6700,7 @@
       <c r="P411" s="11"/>
       <c r="Q411" s="4"/>
     </row>
-    <row r="412" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="412" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D412" s="2"/>
       <c r="E412" s="11"/>
       <c r="G412" s="4"/>
@@ -6712,7 +6712,7 @@
       <c r="P412" s="11"/>
       <c r="Q412" s="4"/>
     </row>
-    <row r="413" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="413" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D413" s="2"/>
       <c r="E413" s="11"/>
       <c r="G413" s="4"/>
@@ -6724,7 +6724,7 @@
       <c r="P413" s="11"/>
       <c r="Q413" s="4"/>
     </row>
-    <row r="414" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="414" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D414" s="2"/>
       <c r="E414" s="11"/>
       <c r="G414" s="4"/>
@@ -6736,7 +6736,7 @@
       <c r="P414" s="11"/>
       <c r="Q414" s="4"/>
     </row>
-    <row r="415" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="415" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D415" s="2"/>
       <c r="E415" s="11"/>
       <c r="G415" s="4"/>
@@ -6748,7 +6748,7 @@
       <c r="P415" s="11"/>
       <c r="Q415" s="4"/>
     </row>
-    <row r="416" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="416" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D416" s="2"/>
       <c r="E416" s="11"/>
       <c r="G416" s="4"/>
@@ -6760,7 +6760,7 @@
       <c r="P416" s="11"/>
       <c r="Q416" s="4"/>
     </row>
-    <row r="417" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="417" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D417" s="2"/>
       <c r="E417" s="11"/>
       <c r="G417" s="4"/>
@@ -6772,7 +6772,7 @@
       <c r="P417" s="11"/>
       <c r="Q417" s="4"/>
     </row>
-    <row r="418" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="418" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D418" s="2"/>
       <c r="E418" s="11"/>
       <c r="G418" s="4"/>
@@ -6784,7 +6784,7 @@
       <c r="P418" s="11"/>
       <c r="Q418" s="4"/>
     </row>
-    <row r="419" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="419" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D419" s="2"/>
       <c r="E419" s="11"/>
       <c r="G419" s="4"/>
@@ -6796,7 +6796,7 @@
       <c r="P419" s="11"/>
       <c r="Q419" s="4"/>
     </row>
-    <row r="420" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="420" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D420" s="2"/>
       <c r="E420" s="11"/>
       <c r="G420" s="4"/>
@@ -6808,7 +6808,7 @@
       <c r="P420" s="11"/>
       <c r="Q420" s="4"/>
     </row>
-    <row r="421" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="421" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D421" s="2"/>
       <c r="E421" s="11"/>
       <c r="G421" s="4"/>
@@ -6820,7 +6820,7 @@
       <c r="P421" s="11"/>
       <c r="Q421" s="4"/>
     </row>
-    <row r="422" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="422" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D422" s="2"/>
       <c r="E422" s="11"/>
       <c r="G422" s="4"/>
@@ -6832,7 +6832,7 @@
       <c r="P422" s="11"/>
       <c r="Q422" s="4"/>
     </row>
-    <row r="423" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="423" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D423" s="2"/>
       <c r="E423" s="11"/>
       <c r="G423" s="4"/>
@@ -6844,7 +6844,7 @@
       <c r="P423" s="11"/>
       <c r="Q423" s="4"/>
     </row>
-    <row r="424" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="424" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D424" s="2"/>
       <c r="E424" s="11"/>
       <c r="G424" s="4"/>
@@ -6856,7 +6856,7 @@
       <c r="P424" s="11"/>
       <c r="Q424" s="4"/>
     </row>
-    <row r="425" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="425" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D425" s="2"/>
       <c r="E425" s="11"/>
       <c r="G425" s="4"/>
@@ -6868,7 +6868,7 @@
       <c r="P425" s="11"/>
       <c r="Q425" s="4"/>
     </row>
-    <row r="426" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="426" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D426" s="2"/>
       <c r="E426" s="11"/>
       <c r="G426" s="4"/>
@@ -6880,7 +6880,7 @@
       <c r="P426" s="11"/>
       <c r="Q426" s="4"/>
     </row>
-    <row r="427" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="427" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D427" s="2"/>
       <c r="E427" s="11"/>
       <c r="G427" s="4"/>
@@ -6892,7 +6892,7 @@
       <c r="P427" s="11"/>
       <c r="Q427" s="4"/>
     </row>
-    <row r="428" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="428" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D428" s="2"/>
       <c r="E428" s="11"/>
       <c r="G428" s="4"/>
@@ -6904,7 +6904,7 @@
       <c r="P428" s="11"/>
       <c r="Q428" s="4"/>
     </row>
-    <row r="429" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="429" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D429" s="2"/>
       <c r="E429" s="11"/>
       <c r="G429" s="4"/>
@@ -6916,7 +6916,7 @@
       <c r="P429" s="11"/>
       <c r="Q429" s="4"/>
     </row>
-    <row r="430" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="430" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D430" s="2"/>
       <c r="E430" s="11"/>
       <c r="G430" s="4"/>
@@ -6928,7 +6928,7 @@
       <c r="P430" s="11"/>
       <c r="Q430" s="4"/>
     </row>
-    <row r="431" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="431" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D431" s="2"/>
       <c r="E431" s="11"/>
       <c r="G431" s="4"/>
@@ -6940,7 +6940,7 @@
       <c r="P431" s="11"/>
       <c r="Q431" s="4"/>
     </row>
-    <row r="432" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="432" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D432" s="2"/>
       <c r="E432" s="11"/>
       <c r="G432" s="4"/>
@@ -6952,7 +6952,7 @@
       <c r="P432" s="11"/>
       <c r="Q432" s="4"/>
     </row>
-    <row r="433" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="433" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D433" s="2"/>
       <c r="E433" s="11"/>
       <c r="G433" s="4"/>
@@ -6964,7 +6964,7 @@
       <c r="P433" s="11"/>
       <c r="Q433" s="4"/>
     </row>
-    <row r="434" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="434" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D434" s="2"/>
       <c r="E434" s="11"/>
       <c r="G434" s="4"/>
@@ -6976,7 +6976,7 @@
       <c r="P434" s="11"/>
       <c r="Q434" s="4"/>
     </row>
-    <row r="435" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="435" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D435" s="2"/>
       <c r="E435" s="11"/>
       <c r="G435" s="4"/>
@@ -6988,7 +6988,7 @@
       <c r="P435" s="11"/>
       <c r="Q435" s="4"/>
     </row>
-    <row r="436" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="436" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D436" s="2"/>
       <c r="E436" s="11"/>
       <c r="G436" s="4"/>
@@ -7000,7 +7000,7 @@
       <c r="P436" s="11"/>
       <c r="Q436" s="4"/>
     </row>
-    <row r="437" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="437" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D437" s="2"/>
       <c r="E437" s="11"/>
       <c r="G437" s="4"/>
@@ -7012,7 +7012,7 @@
       <c r="P437" s="11"/>
       <c r="Q437" s="4"/>
     </row>
-    <row r="438" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="438" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D438" s="2"/>
       <c r="E438" s="11"/>
       <c r="G438" s="4"/>
@@ -7024,7 +7024,7 @@
       <c r="P438" s="11"/>
       <c r="Q438" s="4"/>
     </row>
-    <row r="439" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="439" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D439" s="2"/>
       <c r="E439" s="11"/>
       <c r="G439" s="4"/>
@@ -7036,7 +7036,7 @@
       <c r="P439" s="11"/>
       <c r="Q439" s="4"/>
     </row>
-    <row r="440" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="440" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D440" s="2"/>
       <c r="E440" s="11"/>
       <c r="G440" s="4"/>
@@ -7048,7 +7048,7 @@
       <c r="P440" s="11"/>
       <c r="Q440" s="4"/>
     </row>
-    <row r="441" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="441" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D441" s="2"/>
       <c r="E441" s="11"/>
       <c r="G441" s="4"/>
@@ -7060,7 +7060,7 @@
       <c r="P441" s="11"/>
       <c r="Q441" s="4"/>
     </row>
-    <row r="442" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="442" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D442" s="2"/>
       <c r="E442" s="11"/>
       <c r="G442" s="4"/>
@@ -7072,7 +7072,7 @@
       <c r="P442" s="11"/>
       <c r="Q442" s="4"/>
     </row>
-    <row r="443" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="443" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D443" s="2"/>
       <c r="E443" s="11"/>
       <c r="G443" s="4"/>
@@ -7084,7 +7084,7 @@
       <c r="P443" s="11"/>
       <c r="Q443" s="4"/>
     </row>
-    <row r="444" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="444" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D444" s="2"/>
       <c r="E444" s="11"/>
       <c r="G444" s="4"/>
@@ -7094,7 +7094,7 @@
       <c r="N444" s="4"/>
       <c r="P444" s="11"/>
     </row>
-    <row r="445" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="445" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D445" s="2"/>
       <c r="E445" s="11"/>
       <c r="G445" s="4"/>
@@ -7104,7 +7104,7 @@
       <c r="N445" s="4"/>
       <c r="P445" s="11"/>
     </row>
-    <row r="446" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="446" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D446" s="2"/>
       <c r="E446" s="11"/>
       <c r="G446" s="4"/>
@@ -7114,7 +7114,7 @@
       <c r="N446" s="4"/>
       <c r="P446" s="11"/>
     </row>
-    <row r="447" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="447" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D447" s="2"/>
       <c r="E447" s="11"/>
       <c r="G447" s="4"/>
@@ -7124,7 +7124,7 @@
       <c r="N447" s="4"/>
       <c r="P447" s="11"/>
     </row>
-    <row r="448" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="448" spans="4:17" x14ac:dyDescent="0.3">
       <c r="D448" s="2"/>
       <c r="E448" s="11"/>
       <c r="G448" s="4"/>
@@ -7134,7 +7134,7 @@
       <c r="N448" s="4"/>
       <c r="P448" s="11"/>
     </row>
-    <row r="449" spans="4:16" x14ac:dyDescent="0.25">
+    <row r="449" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D449" s="2"/>
       <c r="E449" s="11"/>
       <c r="G449" s="4"/>
@@ -7144,7 +7144,7 @@
       <c r="N449" s="4"/>
       <c r="P449" s="11"/>
     </row>
-    <row r="450" spans="4:16" x14ac:dyDescent="0.25">
+    <row r="450" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D450" s="2"/>
       <c r="E450" s="11"/>
       <c r="G450" s="7"/>
@@ -7154,7 +7154,7 @@
       <c r="N450" s="4"/>
       <c r="P450" s="11"/>
     </row>
-    <row r="451" spans="4:16" x14ac:dyDescent="0.25">
+    <row r="451" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D451" s="2"/>
       <c r="E451" s="11"/>
       <c r="G451" s="4"/>
@@ -7164,7 +7164,7 @@
       <c r="N451" s="4"/>
       <c r="P451" s="11"/>
     </row>
-    <row r="452" spans="4:16" x14ac:dyDescent="0.25">
+    <row r="452" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D452" s="2"/>
       <c r="E452" s="11"/>
       <c r="G452" s="7"/>
@@ -7174,7 +7174,7 @@
       <c r="N452" s="4"/>
       <c r="P452" s="11"/>
     </row>
-    <row r="453" spans="4:16" x14ac:dyDescent="0.25">
+    <row r="453" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D453" s="2"/>
       <c r="E453" s="11"/>
       <c r="G453" s="4"/>
@@ -7184,7 +7184,7 @@
       <c r="N453" s="4"/>
       <c r="P453" s="11"/>
     </row>
-    <row r="454" spans="4:16" x14ac:dyDescent="0.25">
+    <row r="454" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D454" s="2"/>
       <c r="E454" s="11"/>
       <c r="G454" s="4"/>
@@ -7194,7 +7194,7 @@
       <c r="N454" s="4"/>
       <c r="P454" s="11"/>
     </row>
-    <row r="455" spans="4:16" x14ac:dyDescent="0.25">
+    <row r="455" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D455" s="2"/>
       <c r="E455" s="11"/>
       <c r="G455" s="4"/>
@@ -7204,7 +7204,7 @@
       <c r="N455" s="4"/>
       <c r="P455" s="11"/>
     </row>
-    <row r="456" spans="4:16" x14ac:dyDescent="0.25">
+    <row r="456" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D456" s="2"/>
       <c r="E456" s="11"/>
       <c r="G456" s="4"/>
@@ -7214,7 +7214,7 @@
       <c r="N456" s="4"/>
       <c r="P456" s="11"/>
     </row>
-    <row r="457" spans="4:16" x14ac:dyDescent="0.25">
+    <row r="457" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D457" s="2"/>
       <c r="E457" s="11"/>
       <c r="G457" s="4"/>
@@ -7224,7 +7224,7 @@
       <c r="N457" s="4"/>
       <c r="P457" s="11"/>
     </row>
-    <row r="458" spans="4:16" x14ac:dyDescent="0.25">
+    <row r="458" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D458" s="2"/>
       <c r="E458" s="11"/>
       <c r="G458" s="4"/>
@@ -7234,7 +7234,7 @@
       <c r="N458" s="4"/>
       <c r="P458" s="11"/>
     </row>
-    <row r="459" spans="4:16" x14ac:dyDescent="0.25">
+    <row r="459" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D459" s="2"/>
       <c r="E459" s="11"/>
       <c r="G459" s="4"/>
@@ -7244,7 +7244,7 @@
       <c r="N459" s="4"/>
       <c r="P459" s="11"/>
     </row>
-    <row r="460" spans="4:16" x14ac:dyDescent="0.25">
+    <row r="460" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D460" s="2"/>
       <c r="E460" s="11"/>
       <c r="G460" s="4"/>
@@ -7254,7 +7254,7 @@
       <c r="N460" s="4"/>
       <c r="P460" s="11"/>
     </row>
-    <row r="461" spans="4:16" x14ac:dyDescent="0.25">
+    <row r="461" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D461" s="2"/>
       <c r="E461" s="11"/>
       <c r="G461" s="4"/>
@@ -7264,7 +7264,7 @@
       <c r="N461" s="4"/>
       <c r="P461" s="11"/>
     </row>
-    <row r="462" spans="4:16" x14ac:dyDescent="0.25">
+    <row r="462" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D462" s="2"/>
       <c r="E462" s="11"/>
       <c r="G462" s="4"/>
@@ -7274,7 +7274,7 @@
       <c r="N462" s="4"/>
       <c r="P462" s="11"/>
     </row>
-    <row r="463" spans="4:16" x14ac:dyDescent="0.25">
+    <row r="463" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D463" s="2"/>
       <c r="E463" s="11"/>
       <c r="G463" s="4"/>
@@ -7284,7 +7284,7 @@
       <c r="N463" s="4"/>
       <c r="P463" s="11"/>
     </row>
-    <row r="464" spans="4:16" x14ac:dyDescent="0.25">
+    <row r="464" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D464" s="2"/>
       <c r="E464" s="11"/>
       <c r="G464" s="7"/>
@@ -7294,7 +7294,7 @@
       <c r="N464" s="4"/>
       <c r="P464" s="11"/>
     </row>
-    <row r="465" spans="4:16" x14ac:dyDescent="0.25">
+    <row r="465" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D465" s="2"/>
       <c r="E465" s="11"/>
       <c r="G465" s="4"/>
@@ -7304,7 +7304,7 @@
       <c r="N465" s="4"/>
       <c r="P465" s="11"/>
     </row>
-    <row r="466" spans="4:16" x14ac:dyDescent="0.25">
+    <row r="466" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D466" s="2"/>
       <c r="E466" s="11"/>
       <c r="G466" s="7"/>
@@ -7314,7 +7314,7 @@
       <c r="N466" s="4"/>
       <c r="P466" s="11"/>
     </row>
-    <row r="467" spans="4:16" x14ac:dyDescent="0.25">
+    <row r="467" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D467" s="2"/>
       <c r="E467" s="11"/>
       <c r="G467" s="4"/>
@@ -7324,7 +7324,7 @@
       <c r="N467" s="4"/>
       <c r="P467" s="11"/>
     </row>
-    <row r="468" spans="4:16" x14ac:dyDescent="0.25">
+    <row r="468" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D468" s="2"/>
       <c r="E468" s="11"/>
       <c r="G468" s="4"/>
@@ -7334,7 +7334,7 @@
       <c r="N468" s="4"/>
       <c r="P468" s="11"/>
     </row>
-    <row r="469" spans="4:16" x14ac:dyDescent="0.25">
+    <row r="469" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D469" s="2"/>
       <c r="E469" s="11"/>
       <c r="G469" s="4"/>
@@ -7344,7 +7344,7 @@
       <c r="N469" s="4"/>
       <c r="P469" s="11"/>
     </row>
-    <row r="470" spans="4:16" x14ac:dyDescent="0.25">
+    <row r="470" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D470" s="2"/>
       <c r="E470" s="11"/>
       <c r="G470" s="4"/>
@@ -7354,7 +7354,7 @@
       <c r="N470" s="4"/>
       <c r="P470" s="11"/>
     </row>
-    <row r="471" spans="4:16" x14ac:dyDescent="0.25">
+    <row r="471" spans="4:16" x14ac:dyDescent="0.3">
       <c r="E471" s="11"/>
       <c r="G471" s="4"/>
       <c r="H471" s="4"/>
@@ -7363,7 +7363,7 @@
       <c r="N471" s="4"/>
       <c r="P471" s="11"/>
     </row>
-    <row r="472" spans="4:16" x14ac:dyDescent="0.25">
+    <row r="472" spans="4:16" x14ac:dyDescent="0.3">
       <c r="E472" s="11"/>
       <c r="G472" s="4"/>
       <c r="H472" s="4"/>
@@ -7384,13 +7384,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC130FB4-2F37-4474-8AA2-B01341A5EC99}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="57.85546875" customWidth="1"/>
-    <col min="2" max="2" width="52.7109375" customWidth="1"/>
+    <col min="1" max="1" width="57.88671875" customWidth="1"/>
+    <col min="2" max="2" width="52.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>21</v>
       </c>
@@ -7398,7 +7398,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>23</v>
       </c>
@@ -7406,7 +7406,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
         <v>24</v>
       </c>
@@ -7414,7 +7414,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
         <v>25</v>
       </c>
@@ -7422,7 +7422,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
         <v>26</v>
       </c>
@@ -7438,13 +7438,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DB5104C-39AB-4F23-89F3-98B2DF5E239C}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="48.7109375" customWidth="1"/>
-    <col min="2" max="2" width="66.85546875" customWidth="1"/>
+    <col min="1" max="1" width="48.6640625" customWidth="1"/>
+    <col min="2" max="2" width="66.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>21</v>
       </c>
@@ -7452,7 +7452,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>23</v>
       </c>
@@ -7460,7 +7460,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
         <v>25</v>
       </c>
@@ -7468,7 +7468,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
         <v>26</v>
       </c>

--- a/LogoJ_Platform_Rest_Test/bin/Debug/Template/Muhasebe Mahsup Fisi.xlsx
+++ b/LogoJ_Platform_Rest_Test/bin/Debug/Template/Muhasebe Mahsup Fisi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DOGUKAN\source\repos\LogoJ_Platform_Rest_Test\LogoJ_Platform_Rest_Test\bin\Debug\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBD88725-DA3D-422C-9160-514619BC891A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45B5E9B7-BA95-403A-BFE9-99DC2422E073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9711E6CE-5FD9-4707-B709-915BBF0C49A5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9711E6CE-5FD9-4707-B709-915BBF0C49A5}"/>
   </bookViews>
   <sheets>
     <sheet name="Muhasebe Fişi" sheetId="3" r:id="rId1"/>
@@ -38,114 +38,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Sule Kinatas</author>
-  </authors>
-  <commentList>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{C0290A25-E4E6-40E3-A4A6-D10AA74901CC}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Sule Kinatas:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-3. CoA Code : Raporlamalarda Görülmelidir</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{C403598F-789A-47CE-A50B-415A6F71B5A6}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Sule Kinatas:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-REFERENCE</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{A2241919-AB21-4DF0-8EF5-BB7E9F10711D}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Sule Kinatas:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Doc Header Text</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Q1" authorId="0" shapeId="0" xr:uid="{81A0F59C-C3E4-4B8B-AA87-862291F20EFE}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Sule Kinatas:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Cost Center</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="50">
   <si>
     <t>TARIH</t>
   </si>
@@ -285,15 +179,6 @@
     <t>230.100.0101</t>
   </si>
   <si>
-    <t>a</t>
-  </si>
-  <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
     <t>USD</t>
   </si>
   <si>
@@ -305,12 +190,6 @@
   <si>
     <t>01</t>
   </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>AHMET</t>
-  </si>
 </sst>
 </file>
 
@@ -320,7 +199,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -335,19 +214,6 @@
       <family val="2"/>
       <charset val="162"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -444,28 +310,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <sz val="9"/>
+      <name val="Tahoma"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="162"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -498,12 +349,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -531,70 +376,70 @@
   </borders>
   <cellStyleXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="5"/>
-    <xf numFmtId="4" fontId="8" fillId="0" borderId="0" xfId="5" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="5" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="5" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="13" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="5"/>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="5" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="5" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="5" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="13" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="16" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="14" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="16" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="14" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="5" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="5" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="43" fontId="17" fillId="0" borderId="0" xfId="17" applyFont="1"/>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="18"/>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="18" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="18"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="18" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" xfId="17" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="19">
     <cellStyle name="Giriş 2" xfId="13" xr:uid="{26C81C11-CC4B-4025-B09D-5E7408D276C6}"/>
@@ -926,33 +771,33 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{708B321D-D895-452C-B37F-2B4F07A0DB44}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{708B321D-D895-452C-B37F-2B4F07A0DB44}">
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:R472"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.109375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="18.44140625" customWidth="1"/>
-    <col min="3" max="3" width="20.88671875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="29.6640625" customWidth="1"/>
-    <col min="5" max="5" width="61.6640625" customWidth="1"/>
-    <col min="6" max="6" width="26.5546875" customWidth="1"/>
-    <col min="7" max="7" width="26.33203125" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="29.7109375" customWidth="1"/>
+    <col min="5" max="5" width="61.7109375" customWidth="1"/>
+    <col min="6" max="6" width="26.5703125" customWidth="1"/>
+    <col min="7" max="7" width="26.28515625" customWidth="1"/>
     <col min="8" max="8" width="27" customWidth="1"/>
-    <col min="9" max="9" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.44140625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.42578125" style="3" customWidth="1"/>
     <col min="11" max="11" width="18" style="3" customWidth="1"/>
-    <col min="12" max="12" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="61.109375" customWidth="1"/>
-    <col min="15" max="15" width="28.88671875" customWidth="1"/>
-    <col min="16" max="16" width="64.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="61.140625" customWidth="1"/>
+    <col min="15" max="15" width="28.85546875" customWidth="1"/>
+    <col min="16" max="16" width="64.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>16</v>
       </c>
@@ -1005,148 +850,133 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C2" s="1">
         <v>45879</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E2" s="22"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="20"/>
       <c r="G2" s="4" t="s">
         <v>29</v>
       </c>
       <c r="H2" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I2" s="24">
+      <c r="I2" s="21">
         <v>51120</v>
       </c>
-      <c r="J2" s="20">
+      <c r="J2" s="24">
         <v>7053704.1831734795</v>
       </c>
       <c r="K2" s="10"/>
       <c r="L2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="M2">
-        <v>50</v>
-      </c>
-      <c r="N2" s="22"/>
-      <c r="O2" t="s">
-        <v>47</v>
-      </c>
-      <c r="P2" s="22"/>
+        <v>1</v>
+      </c>
+      <c r="N2" s="20"/>
+      <c r="P2" s="20"/>
       <c r="Q2" s="19"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C3" s="1">
         <v>45879</v>
       </c>
       <c r="D3" s="2"/>
-      <c r="E3" s="22"/>
-      <c r="F3" t="s">
-        <v>53</v>
-      </c>
+      <c r="E3" s="20"/>
       <c r="G3" s="4" t="s">
         <v>33</v>
       </c>
       <c r="H3" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="24">
+      <c r="I3" s="21">
         <v>51120</v>
       </c>
-      <c r="J3" s="20">
+      <c r="J3" s="24">
         <v>1771712.4772185795</v>
       </c>
       <c r="K3" s="10"/>
       <c r="L3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="M3">
-        <v>60</v>
-      </c>
-      <c r="N3" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="P3" s="22"/>
+        <v>1</v>
+      </c>
+      <c r="N3" s="20"/>
+      <c r="P3" s="20"/>
       <c r="Q3" s="19"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C4" s="1">
         <v>45879</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="2" t="s">
-        <v>53</v>
-      </c>
+      <c r="E4" s="20"/>
+      <c r="F4" s="2"/>
       <c r="G4" s="4" t="s">
         <v>31</v>
       </c>
       <c r="H4" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I4" s="24">
+      <c r="I4" s="21">
         <v>51120</v>
       </c>
-      <c r="J4" s="20">
+      <c r="J4" s="24">
         <v>7776300.0000000019</v>
       </c>
       <c r="K4" s="10"/>
       <c r="L4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="M4">
-        <v>70</v>
-      </c>
-      <c r="N4" s="22"/>
-      <c r="P4" s="22" t="s">
-        <v>48</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="N4" s="20"/>
       <c r="Q4" s="19"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C5" s="1">
         <v>45879</v>
       </c>
       <c r="D5" s="2"/>
-      <c r="E5" s="22"/>
+      <c r="E5" s="20"/>
       <c r="G5" s="4" t="s">
         <v>32</v>
       </c>
       <c r="H5" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I5" s="24">
+      <c r="I5" s="21">
         <v>51120</v>
       </c>
-      <c r="J5" s="20">
+      <c r="J5" s="24">
         <v>2013117.7022599997</v>
       </c>
       <c r="K5" s="10"/>
@@ -1156,32 +986,32 @@
       <c r="M5">
         <v>1</v>
       </c>
-      <c r="N5" s="22"/>
-      <c r="P5" s="22"/>
+      <c r="N5" s="20"/>
+      <c r="P5" s="20"/>
       <c r="Q5" s="19"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C6" s="1">
         <v>45879</v>
       </c>
       <c r="D6" s="2"/>
-      <c r="E6" s="22"/>
+      <c r="E6" s="20"/>
       <c r="G6" s="4" t="s">
         <v>33</v>
       </c>
       <c r="H6" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I6" s="24">
+      <c r="I6" s="21">
         <v>51120</v>
       </c>
-      <c r="J6" s="20">
+      <c r="J6" s="24">
         <v>766120.7040899999</v>
       </c>
       <c r="K6" s="10"/>
@@ -1191,32 +1021,32 @@
       <c r="M6">
         <v>1</v>
       </c>
-      <c r="N6" s="22"/>
-      <c r="P6" s="22"/>
+      <c r="N6" s="20"/>
+      <c r="P6" s="20"/>
       <c r="Q6" s="19"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C7" s="1">
         <v>45879</v>
       </c>
       <c r="D7" s="2"/>
-      <c r="E7" s="22"/>
+      <c r="E7" s="20"/>
       <c r="G7" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H7" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I7" s="24">
+      <c r="I7" s="21">
         <v>51120</v>
       </c>
-      <c r="J7" s="20">
+      <c r="J7" s="24">
         <v>1899593.0288088345</v>
       </c>
       <c r="K7" s="10"/>
@@ -1226,32 +1056,32 @@
       <c r="M7">
         <v>1</v>
       </c>
-      <c r="N7" s="22"/>
-      <c r="P7" s="22"/>
+      <c r="N7" s="20"/>
+      <c r="P7" s="20"/>
       <c r="Q7" s="19"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C8" s="1">
         <v>45879</v>
       </c>
       <c r="D8" s="2"/>
-      <c r="E8" s="22"/>
+      <c r="E8" s="20"/>
       <c r="G8" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H8" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I8" s="24">
+      <c r="I8" s="21">
         <v>51120</v>
       </c>
-      <c r="J8" s="20">
+      <c r="J8" s="24">
         <v>347709.01613</v>
       </c>
       <c r="K8" s="10"/>
@@ -1261,32 +1091,32 @@
       <c r="M8">
         <v>1</v>
       </c>
-      <c r="N8" s="22"/>
-      <c r="P8" s="22"/>
+      <c r="N8" s="20"/>
+      <c r="P8" s="20"/>
       <c r="Q8" s="19"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C9" s="1">
         <v>45879</v>
       </c>
       <c r="D9" s="2"/>
-      <c r="E9" s="22"/>
+      <c r="E9" s="20"/>
       <c r="G9" s="7" t="s">
         <v>35</v>
       </c>
       <c r="H9" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I9" s="24">
+      <c r="I9" s="21">
         <v>51120</v>
       </c>
-      <c r="J9" s="20">
+      <c r="J9" s="24">
         <v>195803.08663999999</v>
       </c>
       <c r="K9" s="10"/>
@@ -1296,32 +1126,32 @@
       <c r="M9">
         <v>1</v>
       </c>
-      <c r="N9" s="22"/>
-      <c r="P9" s="22"/>
+      <c r="N9" s="20"/>
+      <c r="P9" s="20"/>
       <c r="Q9" s="19"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C10" s="1">
         <v>45879</v>
       </c>
       <c r="D10" s="2"/>
-      <c r="E10" s="22"/>
+      <c r="E10" s="20"/>
       <c r="G10" s="4" t="s">
         <v>36</v>
       </c>
       <c r="H10" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I10" s="24">
+      <c r="I10" s="21">
         <v>51120</v>
       </c>
-      <c r="J10" s="20">
+      <c r="J10" s="24">
         <v>322547.90714999998</v>
       </c>
       <c r="K10" s="10"/>
@@ -1331,32 +1161,32 @@
       <c r="M10">
         <v>1</v>
       </c>
-      <c r="N10" s="22"/>
-      <c r="P10" s="22"/>
+      <c r="N10" s="20"/>
+      <c r="P10" s="20"/>
       <c r="Q10" s="19"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C11" s="1">
         <v>45879</v>
       </c>
       <c r="D11" s="2"/>
-      <c r="E11" s="22"/>
+      <c r="E11" s="20"/>
       <c r="G11" s="4" t="s">
         <v>37</v>
       </c>
       <c r="H11" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I11" s="24">
+      <c r="I11" s="21">
         <v>51120</v>
       </c>
-      <c r="J11" s="20">
+      <c r="J11" s="24">
         <v>426335.88416999998</v>
       </c>
       <c r="K11" s="10"/>
@@ -1366,32 +1196,32 @@
       <c r="M11">
         <v>1</v>
       </c>
-      <c r="N11" s="22"/>
-      <c r="P11" s="22"/>
+      <c r="N11" s="20"/>
+      <c r="P11" s="20"/>
       <c r="Q11" s="19"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C12" s="1">
         <v>45879</v>
       </c>
       <c r="D12" s="2"/>
-      <c r="E12" s="22"/>
+      <c r="E12" s="20"/>
       <c r="G12" s="4" t="s">
         <v>38</v>
       </c>
       <c r="H12" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I12" s="24">
+      <c r="I12" s="21">
         <v>51120</v>
       </c>
-      <c r="J12" s="20">
+      <c r="J12" s="24">
         <v>531996.96900000004</v>
       </c>
       <c r="K12" s="10"/>
@@ -1401,32 +1231,32 @@
       <c r="M12">
         <v>1</v>
       </c>
-      <c r="N12" s="22"/>
-      <c r="P12" s="22"/>
+      <c r="N12" s="20"/>
+      <c r="P12" s="20"/>
       <c r="Q12" s="19"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C13" s="1">
         <v>45879</v>
       </c>
       <c r="D13" s="2"/>
-      <c r="E13" s="22"/>
+      <c r="E13" s="20"/>
       <c r="G13" s="4" t="s">
         <v>39</v>
       </c>
       <c r="H13" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I13" s="24">
+      <c r="I13" s="21">
         <v>51120</v>
       </c>
-      <c r="J13" s="20">
+      <c r="J13" s="24">
         <v>9271318.7774319388</v>
       </c>
       <c r="K13" s="10"/>
@@ -1436,32 +1266,32 @@
       <c r="M13">
         <v>1</v>
       </c>
-      <c r="N13" s="22"/>
-      <c r="P13" s="22"/>
+      <c r="N13" s="20"/>
+      <c r="P13" s="20"/>
       <c r="Q13" s="19"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C14" s="1">
         <v>45879</v>
       </c>
       <c r="D14" s="2"/>
-      <c r="E14" s="22"/>
+      <c r="E14" s="20"/>
       <c r="G14" s="4" t="s">
         <v>40</v>
       </c>
       <c r="H14" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I14" s="24">
+      <c r="I14" s="21">
         <v>51120</v>
       </c>
-      <c r="J14" s="20">
+      <c r="J14" s="24">
         <v>123962.06591999999</v>
       </c>
       <c r="K14" s="10"/>
@@ -1471,32 +1301,32 @@
       <c r="M14">
         <v>1</v>
       </c>
-      <c r="N14" s="22"/>
-      <c r="P14" s="22"/>
+      <c r="N14" s="20"/>
+      <c r="P14" s="20"/>
       <c r="Q14" s="19"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C15" s="1">
         <v>45879</v>
       </c>
       <c r="D15" s="2"/>
-      <c r="E15" s="22"/>
+      <c r="E15" s="20"/>
       <c r="G15" s="4" t="s">
         <v>41</v>
       </c>
       <c r="H15" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I15" s="24">
+      <c r="I15" s="21">
         <v>51120</v>
       </c>
-      <c r="J15" s="20">
+      <c r="J15" s="24">
         <v>3815874.5111869741</v>
       </c>
       <c r="K15" s="10"/>
@@ -1506,32 +1336,32 @@
       <c r="M15">
         <v>1</v>
       </c>
-      <c r="N15" s="22"/>
-      <c r="P15" s="22"/>
+      <c r="N15" s="20"/>
+      <c r="P15" s="20"/>
       <c r="Q15" s="19"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C16" s="1">
         <v>45879</v>
       </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="22"/>
+      <c r="E16" s="20"/>
       <c r="G16" s="4" t="s">
         <v>40</v>
       </c>
       <c r="H16" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I16" s="24">
+      <c r="I16" s="21">
         <v>51120</v>
       </c>
-      <c r="J16" s="20">
+      <c r="J16" s="24">
         <v>3806386.9999999995</v>
       </c>
       <c r="K16" s="10"/>
@@ -1541,32 +1371,32 @@
       <c r="M16">
         <v>1</v>
       </c>
-      <c r="N16" s="22"/>
-      <c r="P16" s="22"/>
+      <c r="N16" s="20"/>
+      <c r="P16" s="20"/>
       <c r="Q16" s="19"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C17" s="1">
         <v>45879</v>
       </c>
       <c r="D17" s="2"/>
-      <c r="E17" s="22"/>
+      <c r="E17" s="20"/>
       <c r="G17" s="4" t="s">
         <v>40</v>
       </c>
       <c r="H17" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I17" s="24">
+      <c r="I17" s="21">
         <v>51120</v>
       </c>
-      <c r="J17" s="20">
+      <c r="J17" s="24">
         <v>3155599.9999999995</v>
       </c>
       <c r="K17" s="10"/>
@@ -1576,32 +1406,32 @@
       <c r="M17">
         <v>1</v>
       </c>
-      <c r="N17" s="22"/>
-      <c r="P17" s="22"/>
+      <c r="N17" s="20"/>
+      <c r="P17" s="20"/>
       <c r="Q17" s="19"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C18" s="1">
         <v>45879</v>
       </c>
       <c r="D18" s="2"/>
-      <c r="E18" s="22"/>
+      <c r="E18" s="20"/>
       <c r="G18" s="4" t="s">
         <v>29</v>
       </c>
       <c r="H18" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I18" s="24">
+      <c r="I18" s="21">
         <v>51120</v>
       </c>
-      <c r="J18" s="20">
+      <c r="J18" s="24">
         <v>1706977.0393945777</v>
       </c>
       <c r="K18" s="10"/>
@@ -1611,32 +1441,32 @@
       <c r="M18">
         <v>1</v>
       </c>
-      <c r="N18" s="22"/>
-      <c r="P18" s="22"/>
+      <c r="N18" s="20"/>
+      <c r="P18" s="20"/>
       <c r="Q18" s="19"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C19" s="1">
         <v>45879</v>
       </c>
       <c r="D19" s="2"/>
-      <c r="E19" s="22"/>
+      <c r="E19" s="20"/>
       <c r="G19" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H19" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I19" s="24">
+      <c r="I19" s="21">
         <v>51120</v>
       </c>
-      <c r="J19" s="20">
+      <c r="J19" s="24">
         <v>610957.81221999996</v>
       </c>
       <c r="K19" s="10"/>
@@ -1646,32 +1476,32 @@
       <c r="M19">
         <v>1</v>
       </c>
-      <c r="N19" s="22"/>
-      <c r="P19" s="22"/>
+      <c r="N19" s="20"/>
+      <c r="P19" s="20"/>
       <c r="Q19" s="19"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C20" s="1">
         <v>45879</v>
       </c>
       <c r="D20" s="2"/>
-      <c r="E20" s="22"/>
+      <c r="E20" s="20"/>
       <c r="G20" s="4" t="s">
         <v>31</v>
       </c>
       <c r="H20" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I20" s="24">
+      <c r="I20" s="21">
         <v>51120</v>
       </c>
-      <c r="J20" s="20">
+      <c r="J20" s="24">
         <v>974197.40677000012</v>
       </c>
       <c r="K20" s="10"/>
@@ -1681,32 +1511,32 @@
       <c r="M20">
         <v>1</v>
       </c>
-      <c r="N20" s="22"/>
-      <c r="P20" s="22"/>
+      <c r="N20" s="20"/>
+      <c r="P20" s="20"/>
       <c r="Q20" s="19"/>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C21" s="1">
         <v>45879</v>
       </c>
       <c r="D21" s="2"/>
-      <c r="E21" s="22"/>
+      <c r="E21" s="20"/>
       <c r="G21" s="4" t="s">
         <v>32</v>
       </c>
       <c r="H21" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I21" s="24">
+      <c r="I21" s="21">
         <v>51120</v>
       </c>
-      <c r="J21" s="20">
+      <c r="J21" s="24">
         <v>2141300</v>
       </c>
       <c r="K21" s="10"/>
@@ -1716,32 +1546,32 @@
       <c r="M21">
         <v>1</v>
       </c>
-      <c r="N21" s="22"/>
-      <c r="P21" s="22"/>
+      <c r="N21" s="20"/>
+      <c r="P21" s="20"/>
       <c r="Q21" s="19"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C22" s="1">
         <v>45879</v>
       </c>
       <c r="D22" s="2"/>
-      <c r="E22" s="22"/>
+      <c r="E22" s="20"/>
       <c r="G22" s="4" t="s">
         <v>33</v>
       </c>
       <c r="H22" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I22" s="24">
+      <c r="I22" s="21">
         <v>51120</v>
       </c>
-      <c r="J22" s="20">
+      <c r="J22" s="24">
         <v>4008219.9827856207</v>
       </c>
       <c r="K22" s="10"/>
@@ -1751,32 +1581,32 @@
       <c r="M22">
         <v>1</v>
       </c>
-      <c r="N22" s="22"/>
-      <c r="P22" s="22"/>
+      <c r="N22" s="20"/>
+      <c r="P22" s="20"/>
       <c r="Q22" s="19"/>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C23" s="1">
         <v>45879</v>
       </c>
       <c r="D23" s="2"/>
-      <c r="E23" s="22"/>
+      <c r="E23" s="20"/>
       <c r="G23" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H23" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I23" s="24">
+      <c r="I23" s="21">
         <v>51120</v>
       </c>
-      <c r="J23" s="20">
+      <c r="J23" s="24">
         <v>8658015.9999999981</v>
       </c>
       <c r="K23" s="10"/>
@@ -1786,32 +1616,32 @@
       <c r="M23">
         <v>1</v>
       </c>
-      <c r="N23" s="22"/>
-      <c r="P23" s="22"/>
+      <c r="N23" s="20"/>
+      <c r="P23" s="20"/>
       <c r="Q23" s="19"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C24" s="1">
         <v>45879</v>
       </c>
       <c r="D24" s="2"/>
-      <c r="E24" s="22"/>
+      <c r="E24" s="20"/>
       <c r="G24" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H24" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I24" s="24">
+      <c r="I24" s="21">
         <v>51120</v>
       </c>
-      <c r="J24" s="20">
+      <c r="J24" s="24">
         <v>2075461.0000000002</v>
       </c>
       <c r="K24" s="10"/>
@@ -1821,32 +1651,32 @@
       <c r="M24">
         <v>1</v>
       </c>
-      <c r="N24" s="22"/>
-      <c r="P24" s="22"/>
+      <c r="N24" s="20"/>
+      <c r="P24" s="20"/>
       <c r="Q24" s="19"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C25" s="1">
         <v>45879</v>
       </c>
       <c r="D25" s="2"/>
-      <c r="E25" s="22"/>
+      <c r="E25" s="20"/>
       <c r="G25" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H25" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I25" s="24">
+      <c r="I25" s="21">
         <v>51120</v>
       </c>
-      <c r="J25" s="20">
+      <c r="J25" s="24">
         <v>2527528.05039</v>
       </c>
       <c r="K25" s="10"/>
@@ -1856,32 +1686,32 @@
       <c r="M25">
         <v>1</v>
       </c>
-      <c r="N25" s="22"/>
-      <c r="P25" s="22"/>
+      <c r="N25" s="20"/>
+      <c r="P25" s="20"/>
       <c r="Q25" s="19"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C26" s="1">
         <v>45879</v>
       </c>
       <c r="D26" s="2"/>
-      <c r="E26" s="22"/>
+      <c r="E26" s="20"/>
       <c r="G26" s="4" t="s">
         <v>36</v>
       </c>
       <c r="H26" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I26" s="24">
+      <c r="I26" s="21">
         <v>51120</v>
       </c>
-      <c r="J26" s="20">
+      <c r="J26" s="24">
         <v>761530.97405000019</v>
       </c>
       <c r="K26" s="10"/>
@@ -1891,32 +1721,32 @@
       <c r="M26">
         <v>1</v>
       </c>
-      <c r="N26" s="22"/>
-      <c r="P26" s="22"/>
+      <c r="N26" s="20"/>
+      <c r="P26" s="20"/>
       <c r="Q26" s="19"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C27" s="1">
         <v>45879</v>
       </c>
       <c r="D27" s="2"/>
-      <c r="E27" s="22"/>
+      <c r="E27" s="20"/>
       <c r="G27" s="4" t="s">
         <v>37</v>
       </c>
       <c r="H27" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I27" s="24">
+      <c r="I27" s="21">
         <v>51120</v>
       </c>
-      <c r="J27" s="20">
+      <c r="J27" s="24">
         <v>103628.52906</v>
       </c>
       <c r="K27" s="10"/>
@@ -1926,32 +1756,32 @@
       <c r="M27">
         <v>1</v>
       </c>
-      <c r="N27" s="22"/>
-      <c r="P27" s="22"/>
+      <c r="N27" s="20"/>
+      <c r="P27" s="20"/>
       <c r="Q27" s="19"/>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C28" s="1">
         <v>45879</v>
       </c>
       <c r="D28" s="2"/>
-      <c r="E28" s="22"/>
+      <c r="E28" s="20"/>
       <c r="G28" s="4" t="s">
         <v>36</v>
       </c>
       <c r="H28" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I28" s="24">
+      <c r="I28" s="21">
         <v>51120</v>
       </c>
-      <c r="J28" s="20">
+      <c r="J28" s="24">
         <v>124487.77761</v>
       </c>
       <c r="K28" s="10"/>
@@ -1961,32 +1791,32 @@
       <c r="M28">
         <v>1</v>
       </c>
-      <c r="N28" s="22"/>
-      <c r="P28" s="22"/>
+      <c r="N28" s="20"/>
+      <c r="P28" s="20"/>
       <c r="Q28" s="19"/>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C29" s="1">
         <v>45879</v>
       </c>
       <c r="D29" s="2"/>
-      <c r="E29" s="22"/>
+      <c r="E29" s="20"/>
       <c r="G29" s="4" t="s">
         <v>40</v>
       </c>
       <c r="H29" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I29" s="24">
+      <c r="I29" s="21">
         <v>51120</v>
       </c>
-      <c r="J29" s="20">
+      <c r="J29" s="24">
         <v>134718.40186000001</v>
       </c>
       <c r="K29" s="10"/>
@@ -1996,32 +1826,32 @@
       <c r="M29">
         <v>1</v>
       </c>
-      <c r="N29" s="22"/>
-      <c r="P29" s="22"/>
+      <c r="N29" s="20"/>
+      <c r="P29" s="20"/>
       <c r="Q29" s="19"/>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C30" s="1">
         <v>45879</v>
       </c>
       <c r="D30" s="2"/>
-      <c r="E30" s="22"/>
+      <c r="E30" s="20"/>
       <c r="G30" s="4" t="s">
         <v>39</v>
       </c>
       <c r="H30" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I30" s="24">
+      <c r="I30" s="21">
         <v>51120</v>
       </c>
-      <c r="J30" s="20">
+      <c r="J30" s="24">
         <v>4555838</v>
       </c>
       <c r="K30" s="10"/>
@@ -2031,32 +1861,32 @@
       <c r="M30">
         <v>1</v>
       </c>
-      <c r="N30" s="22"/>
-      <c r="P30" s="22"/>
+      <c r="N30" s="20"/>
+      <c r="P30" s="20"/>
       <c r="Q30" s="19"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C31" s="1">
         <v>45879</v>
       </c>
       <c r="D31" s="2"/>
-      <c r="E31" s="22"/>
+      <c r="E31" s="20"/>
       <c r="G31" s="4" t="s">
         <v>39</v>
       </c>
       <c r="H31" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I31" s="24">
+      <c r="I31" s="21">
         <v>51120</v>
       </c>
-      <c r="J31" s="20">
+      <c r="J31" s="24">
         <v>1363421.6880899998</v>
       </c>
       <c r="K31" s="10"/>
@@ -2066,32 +1896,32 @@
       <c r="M31">
         <v>1</v>
       </c>
-      <c r="N31" s="22"/>
-      <c r="P31" s="22"/>
+      <c r="N31" s="20"/>
+      <c r="P31" s="20"/>
       <c r="Q31" s="19"/>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C32" s="1">
         <v>45879</v>
       </c>
       <c r="D32" s="2"/>
-      <c r="E32" s="22"/>
+      <c r="E32" s="20"/>
       <c r="G32" s="4" t="s">
         <v>42</v>
       </c>
       <c r="H32" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I32" s="24">
+      <c r="I32" s="21">
         <v>51120</v>
       </c>
-      <c r="J32" s="20">
+      <c r="J32" s="24">
         <v>304489.55</v>
       </c>
       <c r="K32" s="10"/>
@@ -2101,32 +1931,32 @@
       <c r="M32">
         <v>1</v>
       </c>
-      <c r="N32" s="22"/>
-      <c r="P32" s="22"/>
+      <c r="N32" s="20"/>
+      <c r="P32" s="20"/>
       <c r="Q32" s="19"/>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C33" s="1">
         <v>45879</v>
       </c>
       <c r="D33" s="2"/>
-      <c r="E33" s="22"/>
+      <c r="E33" s="20"/>
       <c r="G33" s="4" t="s">
         <v>42</v>
       </c>
       <c r="H33" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I33" s="24">
+      <c r="I33" s="21">
         <v>51120</v>
       </c>
-      <c r="J33" s="20">
+      <c r="J33" s="24">
         <v>590080</v>
       </c>
       <c r="K33" s="6"/>
@@ -2136,34 +1966,34 @@
       <c r="M33">
         <v>1</v>
       </c>
-      <c r="N33" s="22"/>
-      <c r="P33" s="22"/>
+      <c r="N33" s="20"/>
+      <c r="P33" s="20"/>
       <c r="Q33" s="19"/>
       <c r="R33" s="10"/>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C34" s="1">
         <v>45879</v>
       </c>
       <c r="D34" s="2"/>
-      <c r="E34" s="22"/>
+      <c r="E34" s="20"/>
       <c r="G34" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H34" s="23" t="s">
+      <c r="H34" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="I34" s="25">
+      <c r="I34" s="23">
         <v>23010</v>
       </c>
       <c r="J34" s="5"/>
-      <c r="K34" s="21">
+      <c r="K34" s="25">
         <v>73918935.533299983</v>
       </c>
       <c r="L34" t="s">
@@ -2172,11 +2002,11 @@
       <c r="M34">
         <v>1</v>
       </c>
-      <c r="N34" s="22"/>
-      <c r="P34" s="22"/>
+      <c r="N34" s="20"/>
+      <c r="P34" s="20"/>
       <c r="Q34" s="19"/>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="D35" s="2"/>
       <c r="E35" s="11"/>
       <c r="G35" s="4"/>
@@ -2188,7 +2018,7 @@
       <c r="P35" s="11"/>
       <c r="Q35" s="4"/>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="D36" s="2"/>
       <c r="E36" s="11"/>
       <c r="G36" s="4"/>
@@ -2200,7 +2030,7 @@
       <c r="P36" s="11"/>
       <c r="Q36" s="4"/>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="D37" s="2"/>
       <c r="E37" s="11"/>
       <c r="G37" s="4"/>
@@ -2212,7 +2042,7 @@
       <c r="P37" s="11"/>
       <c r="Q37" s="4"/>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="D38" s="2"/>
       <c r="E38" s="11"/>
       <c r="G38" s="4"/>
@@ -2224,7 +2054,7 @@
       <c r="P38" s="11"/>
       <c r="Q38" s="4"/>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="D39" s="2"/>
       <c r="E39" s="11"/>
       <c r="G39" s="4"/>
@@ -2236,7 +2066,7 @@
       <c r="P39" s="11"/>
       <c r="Q39" s="4"/>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="D40" s="2"/>
       <c r="E40" s="11"/>
       <c r="G40" s="4"/>
@@ -2248,7 +2078,7 @@
       <c r="P40" s="11"/>
       <c r="Q40" s="4"/>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="D41" s="2"/>
       <c r="E41" s="11"/>
       <c r="G41" s="4"/>
@@ -2260,7 +2090,7 @@
       <c r="P41" s="11"/>
       <c r="Q41" s="4"/>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="D42" s="2"/>
       <c r="E42" s="11"/>
       <c r="G42" s="4"/>
@@ -2272,7 +2102,7 @@
       <c r="P42" s="11"/>
       <c r="Q42" s="4"/>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="D43" s="2"/>
       <c r="E43" s="11"/>
       <c r="G43" s="4"/>
@@ -2284,7 +2114,7 @@
       <c r="P43" s="11"/>
       <c r="Q43" s="4"/>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="D44" s="2"/>
       <c r="E44" s="11"/>
       <c r="G44" s="4"/>
@@ -2296,7 +2126,7 @@
       <c r="P44" s="11"/>
       <c r="Q44" s="4"/>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="D45" s="2"/>
       <c r="E45" s="11"/>
       <c r="G45" s="4"/>
@@ -2308,7 +2138,7 @@
       <c r="P45" s="11"/>
       <c r="Q45" s="4"/>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="D46" s="2"/>
       <c r="E46" s="11"/>
       <c r="G46" s="4"/>
@@ -2320,7 +2150,7 @@
       <c r="P46" s="11"/>
       <c r="Q46" s="4"/>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="D47" s="2"/>
       <c r="E47" s="11"/>
       <c r="G47" s="4"/>
@@ -2332,7 +2162,7 @@
       <c r="P47" s="11"/>
       <c r="Q47" s="4"/>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="D48" s="2"/>
       <c r="E48" s="11"/>
       <c r="G48" s="4"/>
@@ -2344,7 +2174,7 @@
       <c r="P48" s="11"/>
       <c r="Q48" s="4"/>
     </row>
-    <row r="49" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D49" s="2"/>
       <c r="E49" s="11"/>
       <c r="G49" s="4"/>
@@ -2356,7 +2186,7 @@
       <c r="P49" s="11"/>
       <c r="Q49" s="4"/>
     </row>
-    <row r="50" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D50" s="2"/>
       <c r="E50" s="11"/>
       <c r="G50" s="4"/>
@@ -2368,7 +2198,7 @@
       <c r="P50" s="11"/>
       <c r="Q50" s="4"/>
     </row>
-    <row r="51" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D51" s="2"/>
       <c r="E51" s="11"/>
       <c r="G51" s="4"/>
@@ -2380,7 +2210,7 @@
       <c r="P51" s="11"/>
       <c r="Q51" s="4"/>
     </row>
-    <row r="52" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="52" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D52" s="2"/>
       <c r="E52" s="11"/>
       <c r="G52" s="4"/>
@@ -2392,7 +2222,7 @@
       <c r="P52" s="11"/>
       <c r="Q52" s="4"/>
     </row>
-    <row r="53" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D53" s="2"/>
       <c r="E53" s="11"/>
       <c r="G53" s="4"/>
@@ -2404,7 +2234,7 @@
       <c r="P53" s="11"/>
       <c r="Q53" s="4"/>
     </row>
-    <row r="54" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D54" s="2"/>
       <c r="E54" s="11"/>
       <c r="G54" s="4"/>
@@ -2416,7 +2246,7 @@
       <c r="P54" s="11"/>
       <c r="Q54" s="4"/>
     </row>
-    <row r="55" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="55" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D55" s="2"/>
       <c r="E55" s="11"/>
       <c r="G55" s="4"/>
@@ -2428,7 +2258,7 @@
       <c r="P55" s="11"/>
       <c r="Q55" s="4"/>
     </row>
-    <row r="56" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D56" s="2"/>
       <c r="E56" s="11"/>
       <c r="G56" s="4"/>
@@ -2440,7 +2270,7 @@
       <c r="P56" s="11"/>
       <c r="Q56" s="4"/>
     </row>
-    <row r="57" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D57" s="2"/>
       <c r="E57" s="11"/>
       <c r="G57" s="4"/>
@@ -2452,7 +2282,7 @@
       <c r="P57" s="11"/>
       <c r="Q57" s="4"/>
     </row>
-    <row r="58" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="58" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D58" s="2"/>
       <c r="E58" s="11"/>
       <c r="G58" s="4"/>
@@ -2464,7 +2294,7 @@
       <c r="P58" s="11"/>
       <c r="Q58" s="4"/>
     </row>
-    <row r="59" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="59" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D59" s="2"/>
       <c r="E59" s="11"/>
       <c r="G59" s="4"/>
@@ -2476,7 +2306,7 @@
       <c r="P59" s="11"/>
       <c r="Q59" s="4"/>
     </row>
-    <row r="60" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="60" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D60" s="2"/>
       <c r="E60" s="11"/>
       <c r="G60" s="4"/>
@@ -2488,7 +2318,7 @@
       <c r="P60" s="11"/>
       <c r="Q60" s="4"/>
     </row>
-    <row r="61" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="61" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D61" s="2"/>
       <c r="E61" s="11"/>
       <c r="G61" s="4"/>
@@ -2500,7 +2330,7 @@
       <c r="P61" s="11"/>
       <c r="Q61" s="4"/>
     </row>
-    <row r="62" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="62" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D62" s="2"/>
       <c r="E62" s="11"/>
       <c r="G62" s="4"/>
@@ -2512,7 +2342,7 @@
       <c r="P62" s="11"/>
       <c r="Q62" s="4"/>
     </row>
-    <row r="63" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="63" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D63" s="2"/>
       <c r="E63" s="11"/>
       <c r="G63" s="4"/>
@@ -2524,7 +2354,7 @@
       <c r="P63" s="11"/>
       <c r="Q63" s="4"/>
     </row>
-    <row r="64" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="64" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D64" s="2"/>
       <c r="E64" s="11"/>
       <c r="G64" s="4"/>
@@ -2536,7 +2366,7 @@
       <c r="P64" s="11"/>
       <c r="Q64" s="4"/>
     </row>
-    <row r="65" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="65" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D65" s="2"/>
       <c r="E65" s="11"/>
       <c r="G65" s="4"/>
@@ -2548,7 +2378,7 @@
       <c r="P65" s="11"/>
       <c r="Q65" s="4"/>
     </row>
-    <row r="66" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="66" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D66" s="2"/>
       <c r="E66" s="11"/>
       <c r="G66" s="4"/>
@@ -2560,7 +2390,7 @@
       <c r="P66" s="11"/>
       <c r="Q66" s="4"/>
     </row>
-    <row r="67" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="67" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D67" s="2"/>
       <c r="E67" s="11"/>
       <c r="G67" s="4"/>
@@ -2572,7 +2402,7 @@
       <c r="P67" s="11"/>
       <c r="Q67" s="4"/>
     </row>
-    <row r="68" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="68" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D68" s="2"/>
       <c r="E68" s="11"/>
       <c r="G68" s="4"/>
@@ -2584,7 +2414,7 @@
       <c r="P68" s="11"/>
       <c r="Q68" s="4"/>
     </row>
-    <row r="69" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="69" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D69" s="2"/>
       <c r="E69" s="11"/>
       <c r="G69" s="4"/>
@@ -2596,7 +2426,7 @@
       <c r="P69" s="11"/>
       <c r="Q69" s="4"/>
     </row>
-    <row r="70" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="70" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D70" s="2"/>
       <c r="E70" s="11"/>
       <c r="G70" s="4"/>
@@ -2608,7 +2438,7 @@
       <c r="P70" s="11"/>
       <c r="Q70" s="4"/>
     </row>
-    <row r="71" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="71" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D71" s="2"/>
       <c r="E71" s="11"/>
       <c r="G71" s="4"/>
@@ -2620,7 +2450,7 @@
       <c r="P71" s="11"/>
       <c r="Q71" s="4"/>
     </row>
-    <row r="72" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="72" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D72" s="2"/>
       <c r="E72" s="11"/>
       <c r="G72" s="4"/>
@@ -2632,7 +2462,7 @@
       <c r="P72" s="11"/>
       <c r="Q72" s="4"/>
     </row>
-    <row r="73" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="73" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D73" s="2"/>
       <c r="E73" s="11"/>
       <c r="G73" s="4"/>
@@ -2644,7 +2474,7 @@
       <c r="P73" s="11"/>
       <c r="Q73" s="4"/>
     </row>
-    <row r="74" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="74" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D74" s="2"/>
       <c r="E74" s="11"/>
       <c r="G74" s="4"/>
@@ -2656,7 +2486,7 @@
       <c r="P74" s="11"/>
       <c r="Q74" s="4"/>
     </row>
-    <row r="75" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="75" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D75" s="2"/>
       <c r="E75" s="11"/>
       <c r="G75" s="4"/>
@@ -2668,7 +2498,7 @@
       <c r="P75" s="11"/>
       <c r="Q75" s="4"/>
     </row>
-    <row r="76" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="76" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D76" s="2"/>
       <c r="E76" s="11"/>
       <c r="G76" s="4"/>
@@ -2680,7 +2510,7 @@
       <c r="P76" s="11"/>
       <c r="Q76" s="4"/>
     </row>
-    <row r="77" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="77" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D77" s="2"/>
       <c r="E77" s="11"/>
       <c r="G77" s="4"/>
@@ -2692,7 +2522,7 @@
       <c r="P77" s="11"/>
       <c r="Q77" s="4"/>
     </row>
-    <row r="78" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="78" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D78" s="2"/>
       <c r="E78" s="11"/>
       <c r="G78" s="4"/>
@@ -2704,7 +2534,7 @@
       <c r="P78" s="11"/>
       <c r="Q78" s="4"/>
     </row>
-    <row r="79" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="79" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D79" s="2"/>
       <c r="E79" s="11"/>
       <c r="G79" s="4"/>
@@ -2716,7 +2546,7 @@
       <c r="P79" s="11"/>
       <c r="Q79" s="4"/>
     </row>
-    <row r="80" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="80" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D80" s="2"/>
       <c r="E80" s="11"/>
       <c r="G80" s="4"/>
@@ -2728,7 +2558,7 @@
       <c r="P80" s="11"/>
       <c r="Q80" s="4"/>
     </row>
-    <row r="81" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="81" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D81" s="2"/>
       <c r="E81" s="11"/>
       <c r="G81" s="4"/>
@@ -2740,7 +2570,7 @@
       <c r="P81" s="11"/>
       <c r="Q81" s="4"/>
     </row>
-    <row r="82" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="82" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D82" s="2"/>
       <c r="E82" s="11"/>
       <c r="G82" s="4"/>
@@ -2752,7 +2582,7 @@
       <c r="P82" s="11"/>
       <c r="Q82" s="4"/>
     </row>
-    <row r="83" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="83" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D83" s="2"/>
       <c r="E83" s="11"/>
       <c r="G83" s="4"/>
@@ -2764,7 +2594,7 @@
       <c r="P83" s="11"/>
       <c r="Q83" s="4"/>
     </row>
-    <row r="84" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="84" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D84" s="2"/>
       <c r="E84" s="11"/>
       <c r="G84" s="4"/>
@@ -2776,7 +2606,7 @@
       <c r="P84" s="11"/>
       <c r="Q84" s="4"/>
     </row>
-    <row r="85" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="85" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D85" s="2"/>
       <c r="E85" s="11"/>
       <c r="G85" s="4"/>
@@ -2788,7 +2618,7 @@
       <c r="P85" s="11"/>
       <c r="Q85" s="4"/>
     </row>
-    <row r="86" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="86" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D86" s="2"/>
       <c r="E86" s="11"/>
       <c r="G86" s="4"/>
@@ -2800,7 +2630,7 @@
       <c r="P86" s="11"/>
       <c r="Q86" s="4"/>
     </row>
-    <row r="87" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="87" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D87" s="2"/>
       <c r="E87" s="11"/>
       <c r="G87" s="4"/>
@@ -2812,7 +2642,7 @@
       <c r="P87" s="11"/>
       <c r="Q87" s="4"/>
     </row>
-    <row r="88" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="88" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D88" s="2"/>
       <c r="E88" s="11"/>
       <c r="G88" s="4"/>
@@ -2824,7 +2654,7 @@
       <c r="P88" s="11"/>
       <c r="Q88" s="4"/>
     </row>
-    <row r="89" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="89" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D89" s="2"/>
       <c r="E89" s="11"/>
       <c r="G89" s="4"/>
@@ -2836,7 +2666,7 @@
       <c r="P89" s="11"/>
       <c r="Q89" s="4"/>
     </row>
-    <row r="90" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="90" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D90" s="2"/>
       <c r="E90" s="11"/>
       <c r="G90" s="4"/>
@@ -2848,7 +2678,7 @@
       <c r="P90" s="11"/>
       <c r="Q90" s="4"/>
     </row>
-    <row r="91" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D91" s="2"/>
       <c r="E91" s="11"/>
       <c r="G91" s="4"/>
@@ -2860,7 +2690,7 @@
       <c r="P91" s="11"/>
       <c r="Q91" s="4"/>
     </row>
-    <row r="92" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="92" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D92" s="2"/>
       <c r="E92" s="11"/>
       <c r="G92" s="4"/>
@@ -2872,7 +2702,7 @@
       <c r="P92" s="11"/>
       <c r="Q92" s="4"/>
     </row>
-    <row r="93" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="93" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D93" s="2"/>
       <c r="E93" s="11"/>
       <c r="G93" s="4"/>
@@ -2884,7 +2714,7 @@
       <c r="P93" s="11"/>
       <c r="Q93" s="4"/>
     </row>
-    <row r="94" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="94" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D94" s="2"/>
       <c r="E94" s="11"/>
       <c r="G94" s="4"/>
@@ -2896,7 +2726,7 @@
       <c r="P94" s="11"/>
       <c r="Q94" s="4"/>
     </row>
-    <row r="95" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="95" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D95" s="2"/>
       <c r="E95" s="11"/>
       <c r="G95" s="4"/>
@@ -2908,7 +2738,7 @@
       <c r="P95" s="11"/>
       <c r="Q95" s="4"/>
     </row>
-    <row r="96" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="96" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D96" s="2"/>
       <c r="E96" s="11"/>
       <c r="G96" s="4"/>
@@ -2920,7 +2750,7 @@
       <c r="P96" s="11"/>
       <c r="Q96" s="4"/>
     </row>
-    <row r="97" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="97" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D97" s="2"/>
       <c r="E97" s="11"/>
       <c r="G97" s="4"/>
@@ -2932,7 +2762,7 @@
       <c r="P97" s="11"/>
       <c r="Q97" s="4"/>
     </row>
-    <row r="98" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="98" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D98" s="2"/>
       <c r="E98" s="11"/>
       <c r="G98" s="4"/>
@@ -2944,7 +2774,7 @@
       <c r="P98" s="11"/>
       <c r="Q98" s="4"/>
     </row>
-    <row r="99" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="99" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D99" s="2"/>
       <c r="E99" s="11"/>
       <c r="G99" s="4"/>
@@ -2956,7 +2786,7 @@
       <c r="P99" s="11"/>
       <c r="Q99" s="4"/>
     </row>
-    <row r="100" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="100" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D100" s="2"/>
       <c r="E100" s="11"/>
       <c r="G100" s="4"/>
@@ -2968,7 +2798,7 @@
       <c r="P100" s="11"/>
       <c r="Q100" s="4"/>
     </row>
-    <row r="101" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="101" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D101" s="2"/>
       <c r="E101" s="11"/>
       <c r="G101" s="4"/>
@@ -2980,7 +2810,7 @@
       <c r="P101" s="11"/>
       <c r="Q101" s="4"/>
     </row>
-    <row r="102" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="102" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D102" s="2"/>
       <c r="E102" s="11"/>
       <c r="G102" s="4"/>
@@ -2992,7 +2822,7 @@
       <c r="P102" s="11"/>
       <c r="Q102" s="4"/>
     </row>
-    <row r="103" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="103" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D103" s="2"/>
       <c r="E103" s="11"/>
       <c r="G103" s="4"/>
@@ -3004,7 +2834,7 @@
       <c r="P103" s="11"/>
       <c r="Q103" s="4"/>
     </row>
-    <row r="104" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="104" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D104" s="2"/>
       <c r="E104" s="11"/>
       <c r="G104" s="4"/>
@@ -3016,7 +2846,7 @@
       <c r="P104" s="11"/>
       <c r="Q104" s="4"/>
     </row>
-    <row r="105" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="105" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D105" s="2"/>
       <c r="E105" s="11"/>
       <c r="G105" s="4"/>
@@ -3028,7 +2858,7 @@
       <c r="P105" s="11"/>
       <c r="Q105" s="4"/>
     </row>
-    <row r="106" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="106" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D106" s="2"/>
       <c r="E106" s="11"/>
       <c r="G106" s="4"/>
@@ -3040,7 +2870,7 @@
       <c r="P106" s="11"/>
       <c r="Q106" s="4"/>
     </row>
-    <row r="107" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="107" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D107" s="2"/>
       <c r="E107" s="11"/>
       <c r="G107" s="4"/>
@@ -3052,7 +2882,7 @@
       <c r="P107" s="11"/>
       <c r="Q107" s="4"/>
     </row>
-    <row r="108" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="108" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D108" s="2"/>
       <c r="E108" s="11"/>
       <c r="G108" s="4"/>
@@ -3064,7 +2894,7 @@
       <c r="P108" s="11"/>
       <c r="Q108" s="4"/>
     </row>
-    <row r="109" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="109" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D109" s="2"/>
       <c r="E109" s="11"/>
       <c r="G109" s="4"/>
@@ -3076,7 +2906,7 @@
       <c r="P109" s="11"/>
       <c r="Q109" s="4"/>
     </row>
-    <row r="110" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="110" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D110" s="2"/>
       <c r="E110" s="11"/>
       <c r="G110" s="4"/>
@@ -3088,7 +2918,7 @@
       <c r="P110" s="11"/>
       <c r="Q110" s="4"/>
     </row>
-    <row r="111" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="111" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D111" s="2"/>
       <c r="E111" s="11"/>
       <c r="G111" s="4"/>
@@ -3100,7 +2930,7 @@
       <c r="P111" s="11"/>
       <c r="Q111" s="4"/>
     </row>
-    <row r="112" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="112" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D112" s="2"/>
       <c r="E112" s="11"/>
       <c r="G112" s="4"/>
@@ -3112,7 +2942,7 @@
       <c r="P112" s="11"/>
       <c r="Q112" s="4"/>
     </row>
-    <row r="113" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="113" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D113" s="2"/>
       <c r="E113" s="11"/>
       <c r="G113" s="4"/>
@@ -3124,7 +2954,7 @@
       <c r="P113" s="11"/>
       <c r="Q113" s="4"/>
     </row>
-    <row r="114" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="114" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D114" s="2"/>
       <c r="E114" s="11"/>
       <c r="G114" s="4"/>
@@ -3136,7 +2966,7 @@
       <c r="P114" s="11"/>
       <c r="Q114" s="4"/>
     </row>
-    <row r="115" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="115" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D115" s="2"/>
       <c r="E115" s="11"/>
       <c r="G115" s="4"/>
@@ -3148,7 +2978,7 @@
       <c r="P115" s="11"/>
       <c r="Q115" s="4"/>
     </row>
-    <row r="116" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="116" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D116" s="2"/>
       <c r="E116" s="11"/>
       <c r="G116" s="4"/>
@@ -3160,7 +2990,7 @@
       <c r="P116" s="11"/>
       <c r="Q116" s="4"/>
     </row>
-    <row r="117" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="117" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D117" s="2"/>
       <c r="E117" s="11"/>
       <c r="G117" s="4"/>
@@ -3172,7 +3002,7 @@
       <c r="P117" s="11"/>
       <c r="Q117" s="4"/>
     </row>
-    <row r="118" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="118" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D118" s="2"/>
       <c r="E118" s="11"/>
       <c r="G118" s="4"/>
@@ -3184,7 +3014,7 @@
       <c r="P118" s="11"/>
       <c r="Q118" s="4"/>
     </row>
-    <row r="119" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="119" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D119" s="2"/>
       <c r="E119" s="11"/>
       <c r="G119" s="4"/>
@@ -3196,7 +3026,7 @@
       <c r="P119" s="11"/>
       <c r="Q119" s="4"/>
     </row>
-    <row r="120" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="120" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D120" s="2"/>
       <c r="E120" s="11"/>
       <c r="G120" s="4"/>
@@ -3208,7 +3038,7 @@
       <c r="P120" s="11"/>
       <c r="Q120" s="4"/>
     </row>
-    <row r="121" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="121" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D121" s="2"/>
       <c r="E121" s="11"/>
       <c r="G121" s="4"/>
@@ -3220,7 +3050,7 @@
       <c r="P121" s="11"/>
       <c r="Q121" s="4"/>
     </row>
-    <row r="122" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="122" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D122" s="2"/>
       <c r="E122" s="11"/>
       <c r="G122" s="4"/>
@@ -3232,7 +3062,7 @@
       <c r="P122" s="11"/>
       <c r="Q122" s="4"/>
     </row>
-    <row r="123" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="123" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D123" s="2"/>
       <c r="E123" s="11"/>
       <c r="G123" s="4"/>
@@ -3244,7 +3074,7 @@
       <c r="P123" s="11"/>
       <c r="Q123" s="4"/>
     </row>
-    <row r="124" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="124" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D124" s="2"/>
       <c r="E124" s="11"/>
       <c r="G124" s="4"/>
@@ -3256,7 +3086,7 @@
       <c r="P124" s="11"/>
       <c r="Q124" s="4"/>
     </row>
-    <row r="125" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="125" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D125" s="2"/>
       <c r="E125" s="11"/>
       <c r="G125" s="4"/>
@@ -3268,7 +3098,7 @@
       <c r="P125" s="11"/>
       <c r="Q125" s="4"/>
     </row>
-    <row r="126" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="126" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D126" s="2"/>
       <c r="E126" s="11"/>
       <c r="G126" s="4"/>
@@ -3280,7 +3110,7 @@
       <c r="P126" s="11"/>
       <c r="Q126" s="4"/>
     </row>
-    <row r="127" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="127" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D127" s="2"/>
       <c r="E127" s="11"/>
       <c r="G127" s="4"/>
@@ -3292,7 +3122,7 @@
       <c r="P127" s="11"/>
       <c r="Q127" s="4"/>
     </row>
-    <row r="128" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="128" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D128" s="2"/>
       <c r="E128" s="11"/>
       <c r="G128" s="4"/>
@@ -3304,7 +3134,7 @@
       <c r="P128" s="11"/>
       <c r="Q128" s="4"/>
     </row>
-    <row r="129" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="129" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D129" s="2"/>
       <c r="E129" s="11"/>
       <c r="G129" s="4"/>
@@ -3316,7 +3146,7 @@
       <c r="P129" s="11"/>
       <c r="Q129" s="4"/>
     </row>
-    <row r="130" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="130" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D130" s="2"/>
       <c r="E130" s="11"/>
       <c r="G130" s="4"/>
@@ -3328,7 +3158,7 @@
       <c r="P130" s="11"/>
       <c r="Q130" s="4"/>
     </row>
-    <row r="131" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="131" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D131" s="2"/>
       <c r="E131" s="11"/>
       <c r="G131" s="4"/>
@@ -3340,7 +3170,7 @@
       <c r="P131" s="11"/>
       <c r="Q131" s="4"/>
     </row>
-    <row r="132" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="132" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D132" s="2"/>
       <c r="E132" s="11"/>
       <c r="G132" s="4"/>
@@ -3352,7 +3182,7 @@
       <c r="P132" s="11"/>
       <c r="Q132" s="4"/>
     </row>
-    <row r="133" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="133" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D133" s="2"/>
       <c r="E133" s="11"/>
       <c r="G133" s="4"/>
@@ -3364,7 +3194,7 @@
       <c r="P133" s="11"/>
       <c r="Q133" s="4"/>
     </row>
-    <row r="134" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="134" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D134" s="2"/>
       <c r="E134" s="11"/>
       <c r="G134" s="4"/>
@@ -3376,7 +3206,7 @@
       <c r="P134" s="11"/>
       <c r="Q134" s="4"/>
     </row>
-    <row r="135" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="135" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D135" s="2"/>
       <c r="E135" s="11"/>
       <c r="G135" s="4"/>
@@ -3388,7 +3218,7 @@
       <c r="P135" s="11"/>
       <c r="Q135" s="4"/>
     </row>
-    <row r="136" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="136" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D136" s="2"/>
       <c r="E136" s="11"/>
       <c r="G136" s="4"/>
@@ -3400,7 +3230,7 @@
       <c r="P136" s="11"/>
       <c r="Q136" s="4"/>
     </row>
-    <row r="137" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="137" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D137" s="2"/>
       <c r="E137" s="11"/>
       <c r="G137" s="4"/>
@@ -3412,7 +3242,7 @@
       <c r="P137" s="11"/>
       <c r="Q137" s="4"/>
     </row>
-    <row r="138" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="138" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D138" s="2"/>
       <c r="E138" s="11"/>
       <c r="G138" s="4"/>
@@ -3424,7 +3254,7 @@
       <c r="P138" s="11"/>
       <c r="Q138" s="4"/>
     </row>
-    <row r="139" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="139" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D139" s="2"/>
       <c r="E139" s="11"/>
       <c r="G139" s="4"/>
@@ -3436,7 +3266,7 @@
       <c r="P139" s="11"/>
       <c r="Q139" s="4"/>
     </row>
-    <row r="140" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="140" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D140" s="2"/>
       <c r="E140" s="11"/>
       <c r="G140" s="4"/>
@@ -3448,7 +3278,7 @@
       <c r="P140" s="11"/>
       <c r="Q140" s="4"/>
     </row>
-    <row r="141" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="141" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D141" s="2"/>
       <c r="E141" s="11"/>
       <c r="G141" s="4"/>
@@ -3460,7 +3290,7 @@
       <c r="P141" s="11"/>
       <c r="Q141" s="4"/>
     </row>
-    <row r="142" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="142" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D142" s="2"/>
       <c r="E142" s="11"/>
       <c r="G142" s="4"/>
@@ -3472,7 +3302,7 @@
       <c r="P142" s="11"/>
       <c r="Q142" s="4"/>
     </row>
-    <row r="143" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="143" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D143" s="2"/>
       <c r="E143" s="11"/>
       <c r="G143" s="4"/>
@@ -3484,7 +3314,7 @@
       <c r="P143" s="11"/>
       <c r="Q143" s="4"/>
     </row>
-    <row r="144" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="144" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D144" s="2"/>
       <c r="E144" s="11"/>
       <c r="G144" s="4"/>
@@ -3496,7 +3326,7 @@
       <c r="P144" s="11"/>
       <c r="Q144" s="4"/>
     </row>
-    <row r="145" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="145" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D145" s="2"/>
       <c r="E145" s="11"/>
       <c r="G145" s="4"/>
@@ -3508,7 +3338,7 @@
       <c r="P145" s="11"/>
       <c r="Q145" s="4"/>
     </row>
-    <row r="146" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="146" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D146" s="2"/>
       <c r="E146" s="11"/>
       <c r="G146" s="4"/>
@@ -3520,7 +3350,7 @@
       <c r="P146" s="11"/>
       <c r="Q146" s="4"/>
     </row>
-    <row r="147" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="147" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D147" s="2"/>
       <c r="E147" s="11"/>
       <c r="G147" s="4"/>
@@ -3532,7 +3362,7 @@
       <c r="P147" s="11"/>
       <c r="Q147" s="4"/>
     </row>
-    <row r="148" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="148" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D148" s="2"/>
       <c r="E148" s="11"/>
       <c r="G148" s="4"/>
@@ -3544,7 +3374,7 @@
       <c r="P148" s="11"/>
       <c r="Q148" s="4"/>
     </row>
-    <row r="149" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="149" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D149" s="2"/>
       <c r="E149" s="11"/>
       <c r="G149" s="4"/>
@@ -3556,7 +3386,7 @@
       <c r="P149" s="11"/>
       <c r="Q149" s="4"/>
     </row>
-    <row r="150" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="150" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D150" s="2"/>
       <c r="E150" s="11"/>
       <c r="G150" s="4"/>
@@ -3568,7 +3398,7 @@
       <c r="P150" s="11"/>
       <c r="Q150" s="4"/>
     </row>
-    <row r="151" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="151" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D151" s="2"/>
       <c r="E151" s="11"/>
       <c r="G151" s="4"/>
@@ -3580,7 +3410,7 @@
       <c r="P151" s="11"/>
       <c r="Q151" s="4"/>
     </row>
-    <row r="152" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="152" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D152" s="2"/>
       <c r="E152" s="11"/>
       <c r="G152" s="4"/>
@@ -3592,7 +3422,7 @@
       <c r="P152" s="11"/>
       <c r="Q152" s="4"/>
     </row>
-    <row r="153" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="153" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D153" s="2"/>
       <c r="E153" s="11"/>
       <c r="G153" s="4"/>
@@ -3604,7 +3434,7 @@
       <c r="P153" s="11"/>
       <c r="Q153" s="4"/>
     </row>
-    <row r="154" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="154" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D154" s="2"/>
       <c r="E154" s="11"/>
       <c r="G154" s="4"/>
@@ -3616,7 +3446,7 @@
       <c r="P154" s="11"/>
       <c r="Q154" s="4"/>
     </row>
-    <row r="155" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="155" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D155" s="2"/>
       <c r="E155" s="11"/>
       <c r="G155" s="4"/>
@@ -3628,7 +3458,7 @@
       <c r="P155" s="11"/>
       <c r="Q155" s="4"/>
     </row>
-    <row r="156" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="156" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D156" s="2"/>
       <c r="E156" s="11"/>
       <c r="G156" s="4"/>
@@ -3640,7 +3470,7 @@
       <c r="P156" s="11"/>
       <c r="Q156" s="4"/>
     </row>
-    <row r="157" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="157" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D157" s="2"/>
       <c r="E157" s="11"/>
       <c r="G157" s="4"/>
@@ -3652,7 +3482,7 @@
       <c r="P157" s="11"/>
       <c r="Q157" s="4"/>
     </row>
-    <row r="158" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="158" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D158" s="2"/>
       <c r="E158" s="11"/>
       <c r="G158" s="4"/>
@@ -3664,7 +3494,7 @@
       <c r="P158" s="11"/>
       <c r="Q158" s="4"/>
     </row>
-    <row r="159" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="159" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D159" s="2"/>
       <c r="E159" s="11"/>
       <c r="G159" s="4"/>
@@ -3676,7 +3506,7 @@
       <c r="P159" s="11"/>
       <c r="Q159" s="4"/>
     </row>
-    <row r="160" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="160" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D160" s="2"/>
       <c r="E160" s="11"/>
       <c r="G160" s="4"/>
@@ -3688,7 +3518,7 @@
       <c r="P160" s="11"/>
       <c r="Q160" s="4"/>
     </row>
-    <row r="161" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="161" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D161" s="2"/>
       <c r="E161" s="11"/>
       <c r="G161" s="4"/>
@@ -3700,7 +3530,7 @@
       <c r="P161" s="11"/>
       <c r="Q161" s="4"/>
     </row>
-    <row r="162" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="162" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D162" s="2"/>
       <c r="E162" s="11"/>
       <c r="G162" s="4"/>
@@ -3712,7 +3542,7 @@
       <c r="P162" s="11"/>
       <c r="Q162" s="4"/>
     </row>
-    <row r="163" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="163" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D163" s="2"/>
       <c r="E163" s="11"/>
       <c r="G163" s="4"/>
@@ -3724,7 +3554,7 @@
       <c r="P163" s="11"/>
       <c r="Q163" s="4"/>
     </row>
-    <row r="164" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="164" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D164" s="2"/>
       <c r="E164" s="11"/>
       <c r="G164" s="4"/>
@@ -3736,7 +3566,7 @@
       <c r="P164" s="11"/>
       <c r="Q164" s="4"/>
     </row>
-    <row r="165" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="165" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D165" s="2"/>
       <c r="E165" s="11"/>
       <c r="G165" s="4"/>
@@ -3748,7 +3578,7 @@
       <c r="P165" s="11"/>
       <c r="Q165" s="4"/>
     </row>
-    <row r="166" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="166" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D166" s="2"/>
       <c r="E166" s="11"/>
       <c r="G166" s="4"/>
@@ -3760,7 +3590,7 @@
       <c r="P166" s="11"/>
       <c r="Q166" s="4"/>
     </row>
-    <row r="167" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="167" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D167" s="2"/>
       <c r="E167" s="11"/>
       <c r="G167" s="4"/>
@@ -3772,7 +3602,7 @@
       <c r="P167" s="11"/>
       <c r="Q167" s="4"/>
     </row>
-    <row r="168" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="168" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D168" s="2"/>
       <c r="E168" s="11"/>
       <c r="G168" s="4"/>
@@ -3784,7 +3614,7 @@
       <c r="P168" s="11"/>
       <c r="Q168" s="4"/>
     </row>
-    <row r="169" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="169" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D169" s="2"/>
       <c r="E169" s="11"/>
       <c r="G169" s="4"/>
@@ -3796,7 +3626,7 @@
       <c r="P169" s="11"/>
       <c r="Q169" s="4"/>
     </row>
-    <row r="170" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="170" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D170" s="2"/>
       <c r="E170" s="11"/>
       <c r="G170" s="4"/>
@@ -3808,7 +3638,7 @@
       <c r="P170" s="11"/>
       <c r="Q170" s="4"/>
     </row>
-    <row r="171" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="171" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D171" s="2"/>
       <c r="E171" s="11"/>
       <c r="G171" s="4"/>
@@ -3820,7 +3650,7 @@
       <c r="P171" s="11"/>
       <c r="Q171" s="4"/>
     </row>
-    <row r="172" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="172" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D172" s="2"/>
       <c r="E172" s="11"/>
       <c r="G172" s="4"/>
@@ -3832,7 +3662,7 @@
       <c r="P172" s="11"/>
       <c r="Q172" s="4"/>
     </row>
-    <row r="173" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="173" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D173" s="2"/>
       <c r="E173" s="11"/>
       <c r="G173" s="4"/>
@@ -3844,7 +3674,7 @@
       <c r="P173" s="11"/>
       <c r="Q173" s="4"/>
     </row>
-    <row r="174" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="174" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D174" s="2"/>
       <c r="E174" s="11"/>
       <c r="G174" s="4"/>
@@ -3856,7 +3686,7 @@
       <c r="P174" s="11"/>
       <c r="Q174" s="4"/>
     </row>
-    <row r="175" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="175" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D175" s="2"/>
       <c r="E175" s="11"/>
       <c r="G175" s="4"/>
@@ -3868,7 +3698,7 @@
       <c r="P175" s="11"/>
       <c r="Q175" s="4"/>
     </row>
-    <row r="176" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="176" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D176" s="2"/>
       <c r="E176" s="11"/>
       <c r="G176" s="4"/>
@@ -3880,7 +3710,7 @@
       <c r="P176" s="11"/>
       <c r="Q176" s="4"/>
     </row>
-    <row r="177" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="177" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D177" s="2"/>
       <c r="E177" s="11"/>
       <c r="G177" s="4"/>
@@ -3892,7 +3722,7 @@
       <c r="P177" s="11"/>
       <c r="Q177" s="4"/>
     </row>
-    <row r="178" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="178" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D178" s="2"/>
       <c r="E178" s="11"/>
       <c r="G178" s="4"/>
@@ -3904,7 +3734,7 @@
       <c r="P178" s="11"/>
       <c r="Q178" s="4"/>
     </row>
-    <row r="179" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="179" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D179" s="2"/>
       <c r="E179" s="11"/>
       <c r="G179" s="4"/>
@@ -3916,7 +3746,7 @@
       <c r="P179" s="11"/>
       <c r="Q179" s="4"/>
     </row>
-    <row r="180" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="180" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D180" s="2"/>
       <c r="E180" s="11"/>
       <c r="G180" s="4"/>
@@ -3928,7 +3758,7 @@
       <c r="P180" s="11"/>
       <c r="Q180" s="4"/>
     </row>
-    <row r="181" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="181" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D181" s="2"/>
       <c r="E181" s="11"/>
       <c r="G181" s="4"/>
@@ -3940,7 +3770,7 @@
       <c r="P181" s="11"/>
       <c r="Q181" s="4"/>
     </row>
-    <row r="182" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="182" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D182" s="2"/>
       <c r="E182" s="11"/>
       <c r="G182" s="4"/>
@@ -3952,7 +3782,7 @@
       <c r="P182" s="11"/>
       <c r="Q182" s="4"/>
     </row>
-    <row r="183" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="183" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D183" s="2"/>
       <c r="E183" s="11"/>
       <c r="G183" s="4"/>
@@ -3964,7 +3794,7 @@
       <c r="P183" s="11"/>
       <c r="Q183" s="4"/>
     </row>
-    <row r="184" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="184" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D184" s="2"/>
       <c r="E184" s="11"/>
       <c r="G184" s="4"/>
@@ -3976,7 +3806,7 @@
       <c r="P184" s="11"/>
       <c r="Q184" s="4"/>
     </row>
-    <row r="185" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="185" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D185" s="2"/>
       <c r="E185" s="11"/>
       <c r="G185" s="4"/>
@@ -3988,7 +3818,7 @@
       <c r="P185" s="11"/>
       <c r="Q185" s="4"/>
     </row>
-    <row r="186" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="186" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D186" s="2"/>
       <c r="E186" s="11"/>
       <c r="G186" s="4"/>
@@ -4000,7 +3830,7 @@
       <c r="P186" s="11"/>
       <c r="Q186" s="4"/>
     </row>
-    <row r="187" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="187" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D187" s="2"/>
       <c r="E187" s="11"/>
       <c r="G187" s="4"/>
@@ -4012,7 +3842,7 @@
       <c r="P187" s="11"/>
       <c r="Q187" s="4"/>
     </row>
-    <row r="188" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="188" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D188" s="2"/>
       <c r="E188" s="11"/>
       <c r="G188" s="4"/>
@@ -4024,7 +3854,7 @@
       <c r="P188" s="11"/>
       <c r="Q188" s="4"/>
     </row>
-    <row r="189" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="189" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D189" s="2"/>
       <c r="E189" s="11"/>
       <c r="G189" s="4"/>
@@ -4036,7 +3866,7 @@
       <c r="P189" s="11"/>
       <c r="Q189" s="4"/>
     </row>
-    <row r="190" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="190" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D190" s="2"/>
       <c r="E190" s="11"/>
       <c r="G190" s="4"/>
@@ -4048,7 +3878,7 @@
       <c r="P190" s="11"/>
       <c r="Q190" s="4"/>
     </row>
-    <row r="191" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="191" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D191" s="2"/>
       <c r="E191" s="11"/>
       <c r="G191" s="4"/>
@@ -4060,7 +3890,7 @@
       <c r="P191" s="11"/>
       <c r="Q191" s="4"/>
     </row>
-    <row r="192" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="192" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D192" s="2"/>
       <c r="E192" s="11"/>
       <c r="G192" s="4"/>
@@ -4072,7 +3902,7 @@
       <c r="P192" s="11"/>
       <c r="Q192" s="4"/>
     </row>
-    <row r="193" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="193" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D193" s="2"/>
       <c r="E193" s="11"/>
       <c r="G193" s="4"/>
@@ -4084,7 +3914,7 @@
       <c r="P193" s="11"/>
       <c r="Q193" s="4"/>
     </row>
-    <row r="194" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="194" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D194" s="2"/>
       <c r="E194" s="11"/>
       <c r="G194" s="4"/>
@@ -4096,7 +3926,7 @@
       <c r="P194" s="11"/>
       <c r="Q194" s="4"/>
     </row>
-    <row r="195" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="195" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D195" s="2"/>
       <c r="E195" s="11"/>
       <c r="G195" s="4"/>
@@ -4108,7 +3938,7 @@
       <c r="P195" s="11"/>
       <c r="Q195" s="4"/>
     </row>
-    <row r="196" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="196" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D196" s="2"/>
       <c r="E196" s="11"/>
       <c r="G196" s="4"/>
@@ -4120,7 +3950,7 @@
       <c r="P196" s="11"/>
       <c r="Q196" s="4"/>
     </row>
-    <row r="197" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="197" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D197" s="2"/>
       <c r="E197" s="11"/>
       <c r="G197" s="4"/>
@@ -4132,7 +3962,7 @@
       <c r="P197" s="11"/>
       <c r="Q197" s="4"/>
     </row>
-    <row r="198" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="198" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D198" s="2"/>
       <c r="E198" s="11"/>
       <c r="G198" s="4"/>
@@ -4144,7 +3974,7 @@
       <c r="P198" s="11"/>
       <c r="Q198" s="4"/>
     </row>
-    <row r="199" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="199" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D199" s="2"/>
       <c r="E199" s="11"/>
       <c r="G199" s="4"/>
@@ -4156,7 +3986,7 @@
       <c r="P199" s="11"/>
       <c r="Q199" s="4"/>
     </row>
-    <row r="200" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="200" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D200" s="2"/>
       <c r="E200" s="11"/>
       <c r="G200" s="4"/>
@@ -4168,7 +3998,7 @@
       <c r="P200" s="11"/>
       <c r="Q200" s="4"/>
     </row>
-    <row r="201" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="201" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D201" s="2"/>
       <c r="E201" s="11"/>
       <c r="G201" s="4"/>
@@ -4180,7 +4010,7 @@
       <c r="P201" s="11"/>
       <c r="Q201" s="4"/>
     </row>
-    <row r="202" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="202" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D202" s="2"/>
       <c r="E202" s="11"/>
       <c r="G202" s="4"/>
@@ -4192,7 +4022,7 @@
       <c r="P202" s="11"/>
       <c r="Q202" s="4"/>
     </row>
-    <row r="203" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="203" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D203" s="2"/>
       <c r="E203" s="11"/>
       <c r="G203" s="4"/>
@@ -4204,7 +4034,7 @@
       <c r="P203" s="11"/>
       <c r="Q203" s="4"/>
     </row>
-    <row r="204" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="204" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D204" s="2"/>
       <c r="E204" s="11"/>
       <c r="G204" s="4"/>
@@ -4216,7 +4046,7 @@
       <c r="P204" s="11"/>
       <c r="Q204" s="4"/>
     </row>
-    <row r="205" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="205" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D205" s="2"/>
       <c r="E205" s="11"/>
       <c r="G205" s="4"/>
@@ -4228,7 +4058,7 @@
       <c r="P205" s="11"/>
       <c r="Q205" s="4"/>
     </row>
-    <row r="206" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="206" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D206" s="2"/>
       <c r="E206" s="11"/>
       <c r="G206" s="4"/>
@@ -4240,7 +4070,7 @@
       <c r="P206" s="11"/>
       <c r="Q206" s="4"/>
     </row>
-    <row r="207" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="207" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D207" s="2"/>
       <c r="E207" s="11"/>
       <c r="G207" s="4"/>
@@ -4252,7 +4082,7 @@
       <c r="P207" s="11"/>
       <c r="Q207" s="4"/>
     </row>
-    <row r="208" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="208" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D208" s="2"/>
       <c r="E208" s="11"/>
       <c r="G208" s="4"/>
@@ -4264,7 +4094,7 @@
       <c r="P208" s="11"/>
       <c r="Q208" s="4"/>
     </row>
-    <row r="209" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="209" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D209" s="2"/>
       <c r="E209" s="11"/>
       <c r="G209" s="4"/>
@@ -4276,7 +4106,7 @@
       <c r="P209" s="11"/>
       <c r="Q209" s="4"/>
     </row>
-    <row r="210" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="210" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D210" s="2"/>
       <c r="E210" s="11"/>
       <c r="G210" s="4"/>
@@ -4288,7 +4118,7 @@
       <c r="P210" s="11"/>
       <c r="Q210" s="4"/>
     </row>
-    <row r="211" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="211" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D211" s="2"/>
       <c r="E211" s="11"/>
       <c r="G211" s="4"/>
@@ -4300,7 +4130,7 @@
       <c r="P211" s="11"/>
       <c r="Q211" s="4"/>
     </row>
-    <row r="212" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="212" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D212" s="2"/>
       <c r="E212" s="11"/>
       <c r="G212" s="4"/>
@@ -4312,7 +4142,7 @@
       <c r="P212" s="11"/>
       <c r="Q212" s="4"/>
     </row>
-    <row r="213" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="213" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D213" s="2"/>
       <c r="E213" s="11"/>
       <c r="G213" s="4"/>
@@ -4324,7 +4154,7 @@
       <c r="P213" s="11"/>
       <c r="Q213" s="4"/>
     </row>
-    <row r="214" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="214" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D214" s="2"/>
       <c r="E214" s="11"/>
       <c r="G214" s="4"/>
@@ -4336,7 +4166,7 @@
       <c r="P214" s="11"/>
       <c r="Q214" s="4"/>
     </row>
-    <row r="215" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="215" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D215" s="2"/>
       <c r="E215" s="11"/>
       <c r="G215" s="4"/>
@@ -4348,7 +4178,7 @@
       <c r="P215" s="11"/>
       <c r="Q215" s="4"/>
     </row>
-    <row r="216" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="216" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D216" s="2"/>
       <c r="E216" s="11"/>
       <c r="G216" s="4"/>
@@ -4360,7 +4190,7 @@
       <c r="P216" s="11"/>
       <c r="Q216" s="4"/>
     </row>
-    <row r="217" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="217" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D217" s="2"/>
       <c r="E217" s="11"/>
       <c r="G217" s="4"/>
@@ -4372,7 +4202,7 @@
       <c r="P217" s="11"/>
       <c r="Q217" s="4"/>
     </row>
-    <row r="218" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="218" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D218" s="2"/>
       <c r="E218" s="11"/>
       <c r="G218" s="4"/>
@@ -4384,7 +4214,7 @@
       <c r="P218" s="11"/>
       <c r="Q218" s="4"/>
     </row>
-    <row r="219" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="219" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D219" s="2"/>
       <c r="E219" s="11"/>
       <c r="G219" s="4"/>
@@ -4396,7 +4226,7 @@
       <c r="P219" s="11"/>
       <c r="Q219" s="4"/>
     </row>
-    <row r="220" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="220" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D220" s="2"/>
       <c r="E220" s="11"/>
       <c r="G220" s="4"/>
@@ -4408,7 +4238,7 @@
       <c r="P220" s="11"/>
       <c r="Q220" s="4"/>
     </row>
-    <row r="221" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="221" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D221" s="2"/>
       <c r="E221" s="11"/>
       <c r="G221" s="4"/>
@@ -4420,7 +4250,7 @@
       <c r="P221" s="11"/>
       <c r="Q221" s="4"/>
     </row>
-    <row r="222" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="222" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D222" s="2"/>
       <c r="E222" s="11"/>
       <c r="G222" s="4"/>
@@ -4432,7 +4262,7 @@
       <c r="P222" s="11"/>
       <c r="Q222" s="4"/>
     </row>
-    <row r="223" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="223" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D223" s="2"/>
       <c r="E223" s="11"/>
       <c r="G223" s="4"/>
@@ -4444,7 +4274,7 @@
       <c r="P223" s="11"/>
       <c r="Q223" s="4"/>
     </row>
-    <row r="224" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="224" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D224" s="2"/>
       <c r="E224" s="11"/>
       <c r="G224" s="4"/>
@@ -4456,7 +4286,7 @@
       <c r="P224" s="11"/>
       <c r="Q224" s="4"/>
     </row>
-    <row r="225" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="225" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D225" s="2"/>
       <c r="E225" s="11"/>
       <c r="G225" s="4"/>
@@ -4468,7 +4298,7 @@
       <c r="P225" s="11"/>
       <c r="Q225" s="4"/>
     </row>
-    <row r="226" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="226" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D226" s="2"/>
       <c r="E226" s="11"/>
       <c r="G226" s="4"/>
@@ -4480,7 +4310,7 @@
       <c r="P226" s="11"/>
       <c r="Q226" s="4"/>
     </row>
-    <row r="227" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="227" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D227" s="2"/>
       <c r="E227" s="11"/>
       <c r="G227" s="4"/>
@@ -4492,7 +4322,7 @@
       <c r="P227" s="11"/>
       <c r="Q227" s="4"/>
     </row>
-    <row r="228" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="228" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D228" s="2"/>
       <c r="E228" s="11"/>
       <c r="G228" s="4"/>
@@ -4504,7 +4334,7 @@
       <c r="P228" s="11"/>
       <c r="Q228" s="4"/>
     </row>
-    <row r="229" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="229" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D229" s="2"/>
       <c r="E229" s="11"/>
       <c r="G229" s="4"/>
@@ -4516,7 +4346,7 @@
       <c r="P229" s="11"/>
       <c r="Q229" s="4"/>
     </row>
-    <row r="230" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="230" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D230" s="2"/>
       <c r="E230" s="11"/>
       <c r="G230" s="4"/>
@@ -4528,7 +4358,7 @@
       <c r="P230" s="11"/>
       <c r="Q230" s="4"/>
     </row>
-    <row r="231" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="231" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D231" s="2"/>
       <c r="E231" s="11"/>
       <c r="G231" s="4"/>
@@ -4540,7 +4370,7 @@
       <c r="P231" s="11"/>
       <c r="Q231" s="4"/>
     </row>
-    <row r="232" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="232" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D232" s="2"/>
       <c r="E232" s="11"/>
       <c r="G232" s="4"/>
@@ -4552,7 +4382,7 @@
       <c r="P232" s="11"/>
       <c r="Q232" s="4"/>
     </row>
-    <row r="233" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="233" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D233" s="2"/>
       <c r="E233" s="11"/>
       <c r="G233" s="4"/>
@@ -4564,7 +4394,7 @@
       <c r="P233" s="11"/>
       <c r="Q233" s="4"/>
     </row>
-    <row r="234" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="234" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D234" s="2"/>
       <c r="E234" s="11"/>
       <c r="G234" s="4"/>
@@ -4576,7 +4406,7 @@
       <c r="P234" s="11"/>
       <c r="Q234" s="4"/>
     </row>
-    <row r="235" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="235" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D235" s="2"/>
       <c r="E235" s="11"/>
       <c r="G235" s="4"/>
@@ -4588,7 +4418,7 @@
       <c r="P235" s="11"/>
       <c r="Q235" s="4"/>
     </row>
-    <row r="236" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="236" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D236" s="2"/>
       <c r="E236" s="11"/>
       <c r="G236" s="4"/>
@@ -4600,7 +4430,7 @@
       <c r="P236" s="11"/>
       <c r="Q236" s="4"/>
     </row>
-    <row r="237" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="237" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D237" s="2"/>
       <c r="E237" s="11"/>
       <c r="G237" s="4"/>
@@ -4612,7 +4442,7 @@
       <c r="P237" s="11"/>
       <c r="Q237" s="4"/>
     </row>
-    <row r="238" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="238" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D238" s="2"/>
       <c r="E238" s="11"/>
       <c r="G238" s="4"/>
@@ -4624,7 +4454,7 @@
       <c r="P238" s="11"/>
       <c r="Q238" s="4"/>
     </row>
-    <row r="239" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="239" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D239" s="2"/>
       <c r="E239" s="11"/>
       <c r="G239" s="4"/>
@@ -4636,7 +4466,7 @@
       <c r="P239" s="11"/>
       <c r="Q239" s="4"/>
     </row>
-    <row r="240" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="240" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D240" s="2"/>
       <c r="E240" s="11"/>
       <c r="G240" s="4"/>
@@ -4648,7 +4478,7 @@
       <c r="P240" s="11"/>
       <c r="Q240" s="4"/>
     </row>
-    <row r="241" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="241" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D241" s="2"/>
       <c r="E241" s="11"/>
       <c r="G241" s="4"/>
@@ -4660,7 +4490,7 @@
       <c r="P241" s="11"/>
       <c r="Q241" s="4"/>
     </row>
-    <row r="242" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="242" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D242" s="2"/>
       <c r="E242" s="11"/>
       <c r="G242" s="4"/>
@@ -4672,7 +4502,7 @@
       <c r="P242" s="11"/>
       <c r="Q242" s="4"/>
     </row>
-    <row r="243" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="243" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D243" s="2"/>
       <c r="E243" s="11"/>
       <c r="G243" s="4"/>
@@ -4684,7 +4514,7 @@
       <c r="P243" s="11"/>
       <c r="Q243" s="4"/>
     </row>
-    <row r="244" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="244" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D244" s="2"/>
       <c r="E244" s="11"/>
       <c r="G244" s="4"/>
@@ -4696,7 +4526,7 @@
       <c r="P244" s="11"/>
       <c r="Q244" s="4"/>
     </row>
-    <row r="245" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="245" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D245" s="2"/>
       <c r="E245" s="11"/>
       <c r="G245" s="4"/>
@@ -4708,7 +4538,7 @@
       <c r="P245" s="11"/>
       <c r="Q245" s="4"/>
     </row>
-    <row r="246" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="246" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D246" s="2"/>
       <c r="E246" s="11"/>
       <c r="G246" s="4"/>
@@ -4720,7 +4550,7 @@
       <c r="P246" s="11"/>
       <c r="Q246" s="4"/>
     </row>
-    <row r="247" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="247" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D247" s="2"/>
       <c r="E247" s="11"/>
       <c r="G247" s="4"/>
@@ -4732,7 +4562,7 @@
       <c r="P247" s="11"/>
       <c r="Q247" s="4"/>
     </row>
-    <row r="248" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="248" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D248" s="2"/>
       <c r="E248" s="11"/>
       <c r="G248" s="4"/>
@@ -4744,7 +4574,7 @@
       <c r="P248" s="11"/>
       <c r="Q248" s="4"/>
     </row>
-    <row r="249" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="249" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D249" s="2"/>
       <c r="E249" s="11"/>
       <c r="G249" s="4"/>
@@ -4756,7 +4586,7 @@
       <c r="P249" s="11"/>
       <c r="Q249" s="4"/>
     </row>
-    <row r="250" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="250" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D250" s="2"/>
       <c r="E250" s="11"/>
       <c r="G250" s="4"/>
@@ -4768,7 +4598,7 @@
       <c r="P250" s="11"/>
       <c r="Q250" s="4"/>
     </row>
-    <row r="251" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="251" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D251" s="2"/>
       <c r="E251" s="11"/>
       <c r="G251" s="4"/>
@@ -4780,7 +4610,7 @@
       <c r="P251" s="11"/>
       <c r="Q251" s="4"/>
     </row>
-    <row r="252" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="252" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D252" s="2"/>
       <c r="E252" s="11"/>
       <c r="G252" s="4"/>
@@ -4792,7 +4622,7 @@
       <c r="P252" s="11"/>
       <c r="Q252" s="4"/>
     </row>
-    <row r="253" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="253" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D253" s="2"/>
       <c r="E253" s="11"/>
       <c r="G253" s="4"/>
@@ -4804,7 +4634,7 @@
       <c r="P253" s="11"/>
       <c r="Q253" s="4"/>
     </row>
-    <row r="254" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="254" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D254" s="2"/>
       <c r="E254" s="11"/>
       <c r="G254" s="4"/>
@@ -4816,7 +4646,7 @@
       <c r="P254" s="11"/>
       <c r="Q254" s="4"/>
     </row>
-    <row r="255" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="255" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D255" s="2"/>
       <c r="E255" s="11"/>
       <c r="G255" s="4"/>
@@ -4828,7 +4658,7 @@
       <c r="P255" s="11"/>
       <c r="Q255" s="4"/>
     </row>
-    <row r="256" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="256" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D256" s="2"/>
       <c r="E256" s="11"/>
       <c r="G256" s="4"/>
@@ -4840,7 +4670,7 @@
       <c r="P256" s="11"/>
       <c r="Q256" s="4"/>
     </row>
-    <row r="257" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="257" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D257" s="2"/>
       <c r="E257" s="11"/>
       <c r="G257" s="4"/>
@@ -4852,7 +4682,7 @@
       <c r="P257" s="11"/>
       <c r="Q257" s="4"/>
     </row>
-    <row r="258" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="258" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D258" s="2"/>
       <c r="E258" s="11"/>
       <c r="G258" s="4"/>
@@ -4864,7 +4694,7 @@
       <c r="P258" s="11"/>
       <c r="Q258" s="4"/>
     </row>
-    <row r="259" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="259" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D259" s="2"/>
       <c r="E259" s="11"/>
       <c r="G259" s="4"/>
@@ -4876,7 +4706,7 @@
       <c r="P259" s="11"/>
       <c r="Q259" s="4"/>
     </row>
-    <row r="260" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="260" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D260" s="2"/>
       <c r="E260" s="11"/>
       <c r="G260" s="4"/>
@@ -4888,7 +4718,7 @@
       <c r="P260" s="11"/>
       <c r="Q260" s="4"/>
     </row>
-    <row r="261" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="261" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D261" s="2"/>
       <c r="E261" s="11"/>
       <c r="G261" s="4"/>
@@ -4900,7 +4730,7 @@
       <c r="P261" s="11"/>
       <c r="Q261" s="4"/>
     </row>
-    <row r="262" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="262" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D262" s="2"/>
       <c r="E262" s="11"/>
       <c r="G262" s="4"/>
@@ -4912,7 +4742,7 @@
       <c r="P262" s="11"/>
       <c r="Q262" s="4"/>
     </row>
-    <row r="263" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="263" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D263" s="2"/>
       <c r="E263" s="11"/>
       <c r="G263" s="4"/>
@@ -4924,7 +4754,7 @@
       <c r="P263" s="11"/>
       <c r="Q263" s="4"/>
     </row>
-    <row r="264" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="264" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D264" s="2"/>
       <c r="E264" s="11"/>
       <c r="G264" s="4"/>
@@ -4936,7 +4766,7 @@
       <c r="P264" s="11"/>
       <c r="Q264" s="4"/>
     </row>
-    <row r="265" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="265" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D265" s="2"/>
       <c r="E265" s="11"/>
       <c r="G265" s="4"/>
@@ -4948,7 +4778,7 @@
       <c r="P265" s="11"/>
       <c r="Q265" s="4"/>
     </row>
-    <row r="266" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="266" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D266" s="2"/>
       <c r="E266" s="11"/>
       <c r="G266" s="4"/>
@@ -4960,7 +4790,7 @@
       <c r="P266" s="11"/>
       <c r="Q266" s="4"/>
     </row>
-    <row r="267" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="267" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D267" s="2"/>
       <c r="E267" s="11"/>
       <c r="G267" s="4"/>
@@ -4972,7 +4802,7 @@
       <c r="P267" s="11"/>
       <c r="Q267" s="4"/>
     </row>
-    <row r="268" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="268" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D268" s="2"/>
       <c r="E268" s="11"/>
       <c r="G268" s="4"/>
@@ -4984,7 +4814,7 @@
       <c r="P268" s="11"/>
       <c r="Q268" s="4"/>
     </row>
-    <row r="269" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="269" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D269" s="2"/>
       <c r="E269" s="11"/>
       <c r="G269" s="4"/>
@@ -4996,7 +4826,7 @@
       <c r="P269" s="11"/>
       <c r="Q269" s="4"/>
     </row>
-    <row r="270" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="270" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D270" s="2"/>
       <c r="E270" s="11"/>
       <c r="G270" s="4"/>
@@ -5008,7 +4838,7 @@
       <c r="P270" s="11"/>
       <c r="Q270" s="4"/>
     </row>
-    <row r="271" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="271" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D271" s="2"/>
       <c r="E271" s="11"/>
       <c r="G271" s="4"/>
@@ -5020,7 +4850,7 @@
       <c r="P271" s="11"/>
       <c r="Q271" s="4"/>
     </row>
-    <row r="272" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="272" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D272" s="2"/>
       <c r="E272" s="11"/>
       <c r="G272" s="4"/>
@@ -5032,7 +4862,7 @@
       <c r="P272" s="11"/>
       <c r="Q272" s="4"/>
     </row>
-    <row r="273" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="273" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D273" s="2"/>
       <c r="E273" s="11"/>
       <c r="G273" s="4"/>
@@ -5044,7 +4874,7 @@
       <c r="P273" s="11"/>
       <c r="Q273" s="4"/>
     </row>
-    <row r="274" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="274" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D274" s="2"/>
       <c r="E274" s="11"/>
       <c r="G274" s="4"/>
@@ -5056,7 +4886,7 @@
       <c r="P274" s="11"/>
       <c r="Q274" s="4"/>
     </row>
-    <row r="275" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="275" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D275" s="2"/>
       <c r="E275" s="11"/>
       <c r="G275" s="4"/>
@@ -5068,7 +4898,7 @@
       <c r="P275" s="11"/>
       <c r="Q275" s="4"/>
     </row>
-    <row r="276" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="276" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D276" s="2"/>
       <c r="E276" s="11"/>
       <c r="G276" s="4"/>
@@ -5080,7 +4910,7 @@
       <c r="P276" s="11"/>
       <c r="Q276" s="4"/>
     </row>
-    <row r="277" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="277" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D277" s="2"/>
       <c r="E277" s="11"/>
       <c r="G277" s="4"/>
@@ -5092,7 +4922,7 @@
       <c r="P277" s="11"/>
       <c r="Q277" s="4"/>
     </row>
-    <row r="278" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="278" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D278" s="2"/>
       <c r="E278" s="11"/>
       <c r="G278" s="4"/>
@@ -5104,7 +4934,7 @@
       <c r="P278" s="11"/>
       <c r="Q278" s="4"/>
     </row>
-    <row r="279" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="279" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D279" s="2"/>
       <c r="E279" s="11"/>
       <c r="G279" s="4"/>
@@ -5116,7 +4946,7 @@
       <c r="P279" s="11"/>
       <c r="Q279" s="4"/>
     </row>
-    <row r="280" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="280" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D280" s="2"/>
       <c r="E280" s="11"/>
       <c r="G280" s="4"/>
@@ -5128,7 +4958,7 @@
       <c r="P280" s="11"/>
       <c r="Q280" s="4"/>
     </row>
-    <row r="281" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="281" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D281" s="2"/>
       <c r="E281" s="11"/>
       <c r="G281" s="4"/>
@@ -5140,7 +4970,7 @@
       <c r="P281" s="11"/>
       <c r="Q281" s="4"/>
     </row>
-    <row r="282" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="282" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D282" s="2"/>
       <c r="E282" s="11"/>
       <c r="G282" s="4"/>
@@ -5152,7 +4982,7 @@
       <c r="P282" s="11"/>
       <c r="Q282" s="4"/>
     </row>
-    <row r="283" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="283" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D283" s="2"/>
       <c r="E283" s="11"/>
       <c r="G283" s="4"/>
@@ -5164,7 +4994,7 @@
       <c r="P283" s="11"/>
       <c r="Q283" s="4"/>
     </row>
-    <row r="284" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="284" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D284" s="2"/>
       <c r="E284" s="11"/>
       <c r="G284" s="4"/>
@@ -5176,7 +5006,7 @@
       <c r="P284" s="11"/>
       <c r="Q284" s="4"/>
     </row>
-    <row r="285" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="285" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D285" s="2"/>
       <c r="E285" s="11"/>
       <c r="G285" s="4"/>
@@ -5188,7 +5018,7 @@
       <c r="P285" s="11"/>
       <c r="Q285" s="4"/>
     </row>
-    <row r="286" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="286" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D286" s="2"/>
       <c r="E286" s="11"/>
       <c r="G286" s="4"/>
@@ -5200,7 +5030,7 @@
       <c r="P286" s="11"/>
       <c r="Q286" s="4"/>
     </row>
-    <row r="287" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="287" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D287" s="2"/>
       <c r="E287" s="11"/>
       <c r="G287" s="4"/>
@@ -5212,7 +5042,7 @@
       <c r="P287" s="11"/>
       <c r="Q287" s="4"/>
     </row>
-    <row r="288" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="288" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D288" s="2"/>
       <c r="E288" s="11"/>
       <c r="G288" s="4"/>
@@ -5224,7 +5054,7 @@
       <c r="P288" s="11"/>
       <c r="Q288" s="4"/>
     </row>
-    <row r="289" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="289" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D289" s="2"/>
       <c r="E289" s="11"/>
       <c r="G289" s="4"/>
@@ -5236,7 +5066,7 @@
       <c r="P289" s="11"/>
       <c r="Q289" s="4"/>
     </row>
-    <row r="290" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="290" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D290" s="2"/>
       <c r="E290" s="11"/>
       <c r="G290" s="4"/>
@@ -5248,7 +5078,7 @@
       <c r="P290" s="11"/>
       <c r="Q290" s="4"/>
     </row>
-    <row r="291" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="291" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D291" s="2"/>
       <c r="E291" s="11"/>
       <c r="G291" s="4"/>
@@ -5260,7 +5090,7 @@
       <c r="P291" s="11"/>
       <c r="Q291" s="4"/>
     </row>
-    <row r="292" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="292" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D292" s="2"/>
       <c r="E292" s="11"/>
       <c r="G292" s="4"/>
@@ -5272,7 +5102,7 @@
       <c r="P292" s="11"/>
       <c r="Q292" s="4"/>
     </row>
-    <row r="293" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="293" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D293" s="2"/>
       <c r="E293" s="11"/>
       <c r="G293" s="4"/>
@@ -5284,7 +5114,7 @@
       <c r="P293" s="11"/>
       <c r="Q293" s="4"/>
     </row>
-    <row r="294" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="294" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D294" s="2"/>
       <c r="E294" s="11"/>
       <c r="G294" s="4"/>
@@ -5296,7 +5126,7 @@
       <c r="P294" s="11"/>
       <c r="Q294" s="4"/>
     </row>
-    <row r="295" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="295" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D295" s="2"/>
       <c r="E295" s="11"/>
       <c r="G295" s="4"/>
@@ -5308,7 +5138,7 @@
       <c r="P295" s="11"/>
       <c r="Q295" s="4"/>
     </row>
-    <row r="296" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="296" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D296" s="2"/>
       <c r="E296" s="11"/>
       <c r="G296" s="4"/>
@@ -5320,7 +5150,7 @@
       <c r="P296" s="11"/>
       <c r="Q296" s="4"/>
     </row>
-    <row r="297" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="297" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D297" s="2"/>
       <c r="E297" s="11"/>
       <c r="G297" s="4"/>
@@ -5332,7 +5162,7 @@
       <c r="P297" s="11"/>
       <c r="Q297" s="4"/>
     </row>
-    <row r="298" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="298" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D298" s="2"/>
       <c r="E298" s="11"/>
       <c r="G298" s="4"/>
@@ -5344,7 +5174,7 @@
       <c r="P298" s="11"/>
       <c r="Q298" s="4"/>
     </row>
-    <row r="299" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="299" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D299" s="2"/>
       <c r="E299" s="11"/>
       <c r="G299" s="4"/>
@@ -5356,7 +5186,7 @@
       <c r="P299" s="11"/>
       <c r="Q299" s="4"/>
     </row>
-    <row r="300" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="300" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D300" s="2"/>
       <c r="E300" s="11"/>
       <c r="G300" s="4"/>
@@ -5368,7 +5198,7 @@
       <c r="P300" s="11"/>
       <c r="Q300" s="4"/>
     </row>
-    <row r="301" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="301" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D301" s="2"/>
       <c r="E301" s="11"/>
       <c r="G301" s="4"/>
@@ -5380,7 +5210,7 @@
       <c r="P301" s="11"/>
       <c r="Q301" s="4"/>
     </row>
-    <row r="302" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="302" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D302" s="2"/>
       <c r="E302" s="11"/>
       <c r="G302" s="4"/>
@@ -5392,7 +5222,7 @@
       <c r="P302" s="11"/>
       <c r="Q302" s="4"/>
     </row>
-    <row r="303" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="303" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D303" s="2"/>
       <c r="E303" s="11"/>
       <c r="G303" s="4"/>
@@ -5404,7 +5234,7 @@
       <c r="P303" s="11"/>
       <c r="Q303" s="4"/>
     </row>
-    <row r="304" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="304" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D304" s="2"/>
       <c r="E304" s="11"/>
       <c r="G304" s="4"/>
@@ -5416,7 +5246,7 @@
       <c r="P304" s="11"/>
       <c r="Q304" s="4"/>
     </row>
-    <row r="305" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="305" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D305" s="2"/>
       <c r="E305" s="11"/>
       <c r="G305" s="4"/>
@@ -5428,7 +5258,7 @@
       <c r="P305" s="11"/>
       <c r="Q305" s="4"/>
     </row>
-    <row r="306" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="306" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D306" s="2"/>
       <c r="E306" s="11"/>
       <c r="G306" s="4"/>
@@ -5440,7 +5270,7 @@
       <c r="P306" s="11"/>
       <c r="Q306" s="4"/>
     </row>
-    <row r="307" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="307" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D307" s="2"/>
       <c r="E307" s="11"/>
       <c r="G307" s="4"/>
@@ -5452,7 +5282,7 @@
       <c r="P307" s="11"/>
       <c r="Q307" s="4"/>
     </row>
-    <row r="308" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="308" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D308" s="2"/>
       <c r="E308" s="11"/>
       <c r="G308" s="4"/>
@@ -5464,7 +5294,7 @@
       <c r="P308" s="11"/>
       <c r="Q308" s="4"/>
     </row>
-    <row r="309" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="309" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D309" s="2"/>
       <c r="E309" s="11"/>
       <c r="G309" s="4"/>
@@ -5476,7 +5306,7 @@
       <c r="P309" s="11"/>
       <c r="Q309" s="4"/>
     </row>
-    <row r="310" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="310" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D310" s="2"/>
       <c r="E310" s="11"/>
       <c r="G310" s="4"/>
@@ -5488,7 +5318,7 @@
       <c r="P310" s="11"/>
       <c r="Q310" s="4"/>
     </row>
-    <row r="311" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="311" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D311" s="2"/>
       <c r="E311" s="11"/>
       <c r="G311" s="4"/>
@@ -5500,7 +5330,7 @@
       <c r="P311" s="11"/>
       <c r="Q311" s="4"/>
     </row>
-    <row r="312" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="312" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D312" s="2"/>
       <c r="E312" s="11"/>
       <c r="G312" s="4"/>
@@ -5512,7 +5342,7 @@
       <c r="P312" s="11"/>
       <c r="Q312" s="4"/>
     </row>
-    <row r="313" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="313" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D313" s="2"/>
       <c r="E313" s="11"/>
       <c r="G313" s="4"/>
@@ -5524,7 +5354,7 @@
       <c r="P313" s="11"/>
       <c r="Q313" s="4"/>
     </row>
-    <row r="314" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="314" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D314" s="2"/>
       <c r="E314" s="11"/>
       <c r="G314" s="4"/>
@@ -5536,7 +5366,7 @@
       <c r="P314" s="11"/>
       <c r="Q314" s="4"/>
     </row>
-    <row r="315" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="315" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D315" s="2"/>
       <c r="E315" s="11"/>
       <c r="G315" s="4"/>
@@ -5548,7 +5378,7 @@
       <c r="P315" s="11"/>
       <c r="Q315" s="4"/>
     </row>
-    <row r="316" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="316" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D316" s="2"/>
       <c r="E316" s="11"/>
       <c r="G316" s="4"/>
@@ -5560,7 +5390,7 @@
       <c r="P316" s="11"/>
       <c r="Q316" s="4"/>
     </row>
-    <row r="317" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="317" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D317" s="2"/>
       <c r="E317" s="11"/>
       <c r="G317" s="4"/>
@@ -5572,7 +5402,7 @@
       <c r="P317" s="11"/>
       <c r="Q317" s="4"/>
     </row>
-    <row r="318" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="318" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D318" s="2"/>
       <c r="E318" s="11"/>
       <c r="G318" s="4"/>
@@ -5584,7 +5414,7 @@
       <c r="P318" s="11"/>
       <c r="Q318" s="4"/>
     </row>
-    <row r="319" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="319" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D319" s="2"/>
       <c r="E319" s="11"/>
       <c r="G319" s="4"/>
@@ -5596,7 +5426,7 @@
       <c r="P319" s="11"/>
       <c r="Q319" s="4"/>
     </row>
-    <row r="320" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="320" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D320" s="2"/>
       <c r="E320" s="11"/>
       <c r="G320" s="4"/>
@@ -5608,7 +5438,7 @@
       <c r="P320" s="11"/>
       <c r="Q320" s="4"/>
     </row>
-    <row r="321" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="321" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D321" s="2"/>
       <c r="E321" s="11"/>
       <c r="G321" s="4"/>
@@ -5620,7 +5450,7 @@
       <c r="P321" s="11"/>
       <c r="Q321" s="4"/>
     </row>
-    <row r="322" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="322" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D322" s="2"/>
       <c r="E322" s="11"/>
       <c r="G322" s="4"/>
@@ -5632,7 +5462,7 @@
       <c r="P322" s="11"/>
       <c r="Q322" s="4"/>
     </row>
-    <row r="323" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="323" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D323" s="2"/>
       <c r="E323" s="11"/>
       <c r="G323" s="4"/>
@@ -5644,7 +5474,7 @@
       <c r="P323" s="11"/>
       <c r="Q323" s="4"/>
     </row>
-    <row r="324" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="324" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D324" s="2"/>
       <c r="E324" s="11"/>
       <c r="G324" s="4"/>
@@ -5656,7 +5486,7 @@
       <c r="P324" s="11"/>
       <c r="Q324" s="4"/>
     </row>
-    <row r="325" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="325" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D325" s="2"/>
       <c r="E325" s="11"/>
       <c r="G325" s="4"/>
@@ -5668,7 +5498,7 @@
       <c r="P325" s="11"/>
       <c r="Q325" s="4"/>
     </row>
-    <row r="326" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="326" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D326" s="2"/>
       <c r="E326" s="11"/>
       <c r="G326" s="4"/>
@@ -5680,7 +5510,7 @@
       <c r="P326" s="11"/>
       <c r="Q326" s="4"/>
     </row>
-    <row r="327" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="327" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D327" s="2"/>
       <c r="E327" s="11"/>
       <c r="G327" s="4"/>
@@ -5692,7 +5522,7 @@
       <c r="P327" s="11"/>
       <c r="Q327" s="4"/>
     </row>
-    <row r="328" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="328" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D328" s="2"/>
       <c r="E328" s="11"/>
       <c r="G328" s="4"/>
@@ -5704,7 +5534,7 @@
       <c r="P328" s="11"/>
       <c r="Q328" s="4"/>
     </row>
-    <row r="329" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="329" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D329" s="2"/>
       <c r="E329" s="11"/>
       <c r="G329" s="4"/>
@@ -5716,7 +5546,7 @@
       <c r="P329" s="11"/>
       <c r="Q329" s="4"/>
     </row>
-    <row r="330" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="330" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D330" s="2"/>
       <c r="E330" s="11"/>
       <c r="G330" s="4"/>
@@ -5728,7 +5558,7 @@
       <c r="P330" s="11"/>
       <c r="Q330" s="4"/>
     </row>
-    <row r="331" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="331" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D331" s="2"/>
       <c r="E331" s="11"/>
       <c r="G331" s="4"/>
@@ -5740,7 +5570,7 @@
       <c r="P331" s="11"/>
       <c r="Q331" s="4"/>
     </row>
-    <row r="332" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="332" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D332" s="2"/>
       <c r="E332" s="11"/>
       <c r="G332" s="4"/>
@@ -5752,7 +5582,7 @@
       <c r="P332" s="11"/>
       <c r="Q332" s="4"/>
     </row>
-    <row r="333" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="333" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D333" s="2"/>
       <c r="E333" s="11"/>
       <c r="G333" s="4"/>
@@ -5764,7 +5594,7 @@
       <c r="P333" s="11"/>
       <c r="Q333" s="4"/>
     </row>
-    <row r="334" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="334" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D334" s="2"/>
       <c r="E334" s="11"/>
       <c r="G334" s="4"/>
@@ -5776,7 +5606,7 @@
       <c r="P334" s="11"/>
       <c r="Q334" s="4"/>
     </row>
-    <row r="335" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="335" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D335" s="2"/>
       <c r="E335" s="11"/>
       <c r="G335" s="4"/>
@@ -5788,7 +5618,7 @@
       <c r="P335" s="11"/>
       <c r="Q335" s="4"/>
     </row>
-    <row r="336" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="336" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D336" s="2"/>
       <c r="E336" s="11"/>
       <c r="G336" s="4"/>
@@ -5800,7 +5630,7 @@
       <c r="P336" s="11"/>
       <c r="Q336" s="4"/>
     </row>
-    <row r="337" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="337" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D337" s="2"/>
       <c r="E337" s="11"/>
       <c r="G337" s="4"/>
@@ -5812,7 +5642,7 @@
       <c r="P337" s="11"/>
       <c r="Q337" s="4"/>
     </row>
-    <row r="338" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="338" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D338" s="2"/>
       <c r="E338" s="11"/>
       <c r="G338" s="4"/>
@@ -5824,7 +5654,7 @@
       <c r="P338" s="11"/>
       <c r="Q338" s="4"/>
     </row>
-    <row r="339" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="339" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D339" s="2"/>
       <c r="E339" s="11"/>
       <c r="G339" s="4"/>
@@ -5836,7 +5666,7 @@
       <c r="P339" s="11"/>
       <c r="Q339" s="4"/>
     </row>
-    <row r="340" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="340" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D340" s="2"/>
       <c r="E340" s="11"/>
       <c r="G340" s="4"/>
@@ -5848,7 +5678,7 @@
       <c r="P340" s="11"/>
       <c r="Q340" s="4"/>
     </row>
-    <row r="341" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="341" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D341" s="2"/>
       <c r="E341" s="11"/>
       <c r="G341" s="4"/>
@@ -5860,7 +5690,7 @@
       <c r="P341" s="11"/>
       <c r="Q341" s="4"/>
     </row>
-    <row r="342" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="342" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D342" s="2"/>
       <c r="E342" s="11"/>
       <c r="G342" s="4"/>
@@ -5872,7 +5702,7 @@
       <c r="P342" s="11"/>
       <c r="Q342" s="4"/>
     </row>
-    <row r="343" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="343" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D343" s="2"/>
       <c r="E343" s="11"/>
       <c r="G343" s="4"/>
@@ -5884,7 +5714,7 @@
       <c r="P343" s="11"/>
       <c r="Q343" s="4"/>
     </row>
-    <row r="344" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="344" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D344" s="2"/>
       <c r="E344" s="11"/>
       <c r="G344" s="4"/>
@@ -5896,7 +5726,7 @@
       <c r="P344" s="11"/>
       <c r="Q344" s="4"/>
     </row>
-    <row r="345" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="345" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D345" s="2"/>
       <c r="E345" s="11"/>
       <c r="G345" s="4"/>
@@ -5908,7 +5738,7 @@
       <c r="P345" s="11"/>
       <c r="Q345" s="4"/>
     </row>
-    <row r="346" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="346" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D346" s="2"/>
       <c r="E346" s="11"/>
       <c r="G346" s="4"/>
@@ -5920,7 +5750,7 @@
       <c r="P346" s="11"/>
       <c r="Q346" s="4"/>
     </row>
-    <row r="347" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="347" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D347" s="2"/>
       <c r="E347" s="11"/>
       <c r="G347" s="4"/>
@@ -5932,7 +5762,7 @@
       <c r="P347" s="11"/>
       <c r="Q347" s="4"/>
     </row>
-    <row r="348" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="348" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D348" s="2"/>
       <c r="E348" s="11"/>
       <c r="G348" s="4"/>
@@ -5944,7 +5774,7 @@
       <c r="P348" s="11"/>
       <c r="Q348" s="4"/>
     </row>
-    <row r="349" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="349" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D349" s="2"/>
       <c r="E349" s="11"/>
       <c r="G349" s="4"/>
@@ -5956,7 +5786,7 @@
       <c r="P349" s="11"/>
       <c r="Q349" s="4"/>
     </row>
-    <row r="350" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="350" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D350" s="2"/>
       <c r="E350" s="11"/>
       <c r="G350" s="4"/>
@@ -5968,7 +5798,7 @@
       <c r="P350" s="11"/>
       <c r="Q350" s="4"/>
     </row>
-    <row r="351" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="351" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D351" s="2"/>
       <c r="E351" s="11"/>
       <c r="G351" s="4"/>
@@ -5980,7 +5810,7 @@
       <c r="P351" s="11"/>
       <c r="Q351" s="4"/>
     </row>
-    <row r="352" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="352" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D352" s="2"/>
       <c r="E352" s="11"/>
       <c r="G352" s="4"/>
@@ -5992,7 +5822,7 @@
       <c r="P352" s="11"/>
       <c r="Q352" s="4"/>
     </row>
-    <row r="353" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="353" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D353" s="2"/>
       <c r="E353" s="11"/>
       <c r="G353" s="4"/>
@@ -6004,7 +5834,7 @@
       <c r="P353" s="11"/>
       <c r="Q353" s="4"/>
     </row>
-    <row r="354" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="354" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D354" s="2"/>
       <c r="E354" s="11"/>
       <c r="G354" s="4"/>
@@ -6016,7 +5846,7 @@
       <c r="P354" s="11"/>
       <c r="Q354" s="4"/>
     </row>
-    <row r="355" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="355" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D355" s="2"/>
       <c r="E355" s="11"/>
       <c r="G355" s="4"/>
@@ -6028,7 +5858,7 @@
       <c r="P355" s="11"/>
       <c r="Q355" s="4"/>
     </row>
-    <row r="356" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="356" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D356" s="2"/>
       <c r="E356" s="11"/>
       <c r="G356" s="4"/>
@@ -6040,7 +5870,7 @@
       <c r="P356" s="11"/>
       <c r="Q356" s="4"/>
     </row>
-    <row r="357" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="357" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D357" s="2"/>
       <c r="E357" s="11"/>
       <c r="G357" s="4"/>
@@ -6052,7 +5882,7 @@
       <c r="P357" s="11"/>
       <c r="Q357" s="4"/>
     </row>
-    <row r="358" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="358" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D358" s="2"/>
       <c r="E358" s="11"/>
       <c r="G358" s="4"/>
@@ -6064,7 +5894,7 @@
       <c r="P358" s="11"/>
       <c r="Q358" s="4"/>
     </row>
-    <row r="359" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="359" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D359" s="2"/>
       <c r="E359" s="11"/>
       <c r="G359" s="4"/>
@@ -6076,7 +5906,7 @@
       <c r="P359" s="11"/>
       <c r="Q359" s="4"/>
     </row>
-    <row r="360" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="360" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D360" s="2"/>
       <c r="E360" s="11"/>
       <c r="G360" s="4"/>
@@ -6088,7 +5918,7 @@
       <c r="P360" s="11"/>
       <c r="Q360" s="4"/>
     </row>
-    <row r="361" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="361" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D361" s="2"/>
       <c r="E361" s="11"/>
       <c r="G361" s="4"/>
@@ -6100,7 +5930,7 @@
       <c r="P361" s="11"/>
       <c r="Q361" s="4"/>
     </row>
-    <row r="362" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="362" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D362" s="2"/>
       <c r="E362" s="11"/>
       <c r="G362" s="4"/>
@@ -6112,7 +5942,7 @@
       <c r="P362" s="11"/>
       <c r="Q362" s="4"/>
     </row>
-    <row r="363" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="363" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D363" s="2"/>
       <c r="E363" s="11"/>
       <c r="G363" s="4"/>
@@ -6124,7 +5954,7 @@
       <c r="P363" s="11"/>
       <c r="Q363" s="4"/>
     </row>
-    <row r="364" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="364" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D364" s="2"/>
       <c r="E364" s="11"/>
       <c r="G364" s="4"/>
@@ -6136,7 +5966,7 @@
       <c r="P364" s="11"/>
       <c r="Q364" s="4"/>
     </row>
-    <row r="365" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="365" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D365" s="2"/>
       <c r="E365" s="11"/>
       <c r="G365" s="4"/>
@@ -6148,7 +5978,7 @@
       <c r="P365" s="11"/>
       <c r="Q365" s="4"/>
     </row>
-    <row r="366" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="366" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D366" s="2"/>
       <c r="E366" s="11"/>
       <c r="G366" s="4"/>
@@ -6160,7 +5990,7 @@
       <c r="P366" s="11"/>
       <c r="Q366" s="4"/>
     </row>
-    <row r="367" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="367" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D367" s="2"/>
       <c r="E367" s="11"/>
       <c r="G367" s="4"/>
@@ -6172,7 +6002,7 @@
       <c r="P367" s="11"/>
       <c r="Q367" s="4"/>
     </row>
-    <row r="368" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="368" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D368" s="2"/>
       <c r="E368" s="11"/>
       <c r="G368" s="4"/>
@@ -6184,7 +6014,7 @@
       <c r="P368" s="11"/>
       <c r="Q368" s="4"/>
     </row>
-    <row r="369" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="369" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D369" s="2"/>
       <c r="E369" s="11"/>
       <c r="G369" s="4"/>
@@ -6196,7 +6026,7 @@
       <c r="P369" s="11"/>
       <c r="Q369" s="4"/>
     </row>
-    <row r="370" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="370" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D370" s="2"/>
       <c r="E370" s="11"/>
       <c r="G370" s="4"/>
@@ -6208,7 +6038,7 @@
       <c r="P370" s="11"/>
       <c r="Q370" s="4"/>
     </row>
-    <row r="371" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="371" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D371" s="2"/>
       <c r="E371" s="11"/>
       <c r="G371" s="4"/>
@@ -6220,7 +6050,7 @@
       <c r="P371" s="11"/>
       <c r="Q371" s="4"/>
     </row>
-    <row r="372" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="372" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D372" s="2"/>
       <c r="E372" s="11"/>
       <c r="G372" s="4"/>
@@ -6232,7 +6062,7 @@
       <c r="P372" s="11"/>
       <c r="Q372" s="4"/>
     </row>
-    <row r="373" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="373" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D373" s="2"/>
       <c r="E373" s="11"/>
       <c r="G373" s="4"/>
@@ -6244,7 +6074,7 @@
       <c r="P373" s="11"/>
       <c r="Q373" s="4"/>
     </row>
-    <row r="374" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="374" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D374" s="2"/>
       <c r="E374" s="11"/>
       <c r="G374" s="4"/>
@@ -6256,7 +6086,7 @@
       <c r="P374" s="11"/>
       <c r="Q374" s="4"/>
     </row>
-    <row r="375" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="375" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D375" s="2"/>
       <c r="E375" s="11"/>
       <c r="G375" s="4"/>
@@ -6268,7 +6098,7 @@
       <c r="P375" s="11"/>
       <c r="Q375" s="4"/>
     </row>
-    <row r="376" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="376" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D376" s="2"/>
       <c r="E376" s="11"/>
       <c r="G376" s="4"/>
@@ -6280,7 +6110,7 @@
       <c r="P376" s="11"/>
       <c r="Q376" s="4"/>
     </row>
-    <row r="377" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="377" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D377" s="2"/>
       <c r="E377" s="11"/>
       <c r="G377" s="4"/>
@@ -6292,7 +6122,7 @@
       <c r="P377" s="11"/>
       <c r="Q377" s="4"/>
     </row>
-    <row r="378" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="378" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D378" s="2"/>
       <c r="E378" s="11"/>
       <c r="G378" s="4"/>
@@ -6304,7 +6134,7 @@
       <c r="P378" s="11"/>
       <c r="Q378" s="4"/>
     </row>
-    <row r="379" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="379" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D379" s="2"/>
       <c r="E379" s="11"/>
       <c r="G379" s="4"/>
@@ -6316,7 +6146,7 @@
       <c r="P379" s="11"/>
       <c r="Q379" s="4"/>
     </row>
-    <row r="380" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="380" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D380" s="2"/>
       <c r="E380" s="11"/>
       <c r="G380" s="4"/>
@@ -6328,7 +6158,7 @@
       <c r="P380" s="11"/>
       <c r="Q380" s="4"/>
     </row>
-    <row r="381" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="381" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D381" s="2"/>
       <c r="E381" s="11"/>
       <c r="G381" s="4"/>
@@ -6340,7 +6170,7 @@
       <c r="P381" s="11"/>
       <c r="Q381" s="4"/>
     </row>
-    <row r="382" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="382" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D382" s="2"/>
       <c r="E382" s="11"/>
       <c r="G382" s="4"/>
@@ -6352,7 +6182,7 @@
       <c r="P382" s="11"/>
       <c r="Q382" s="4"/>
     </row>
-    <row r="383" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="383" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D383" s="2"/>
       <c r="E383" s="11"/>
       <c r="G383" s="4"/>
@@ -6364,7 +6194,7 @@
       <c r="P383" s="11"/>
       <c r="Q383" s="4"/>
     </row>
-    <row r="384" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="384" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D384" s="2"/>
       <c r="E384" s="11"/>
       <c r="G384" s="4"/>
@@ -6376,7 +6206,7 @@
       <c r="P384" s="11"/>
       <c r="Q384" s="4"/>
     </row>
-    <row r="385" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="385" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D385" s="2"/>
       <c r="E385" s="11"/>
       <c r="G385" s="4"/>
@@ -6388,7 +6218,7 @@
       <c r="P385" s="11"/>
       <c r="Q385" s="4"/>
     </row>
-    <row r="386" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="386" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D386" s="2"/>
       <c r="E386" s="11"/>
       <c r="G386" s="4"/>
@@ -6400,7 +6230,7 @@
       <c r="P386" s="11"/>
       <c r="Q386" s="4"/>
     </row>
-    <row r="387" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="387" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D387" s="2"/>
       <c r="E387" s="11"/>
       <c r="G387" s="4"/>
@@ -6412,7 +6242,7 @@
       <c r="P387" s="11"/>
       <c r="Q387" s="4"/>
     </row>
-    <row r="388" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="388" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D388" s="2"/>
       <c r="E388" s="11"/>
       <c r="G388" s="4"/>
@@ -6424,7 +6254,7 @@
       <c r="P388" s="11"/>
       <c r="Q388" s="4"/>
     </row>
-    <row r="389" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="389" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D389" s="2"/>
       <c r="E389" s="11"/>
       <c r="G389" s="4"/>
@@ -6436,7 +6266,7 @@
       <c r="P389" s="11"/>
       <c r="Q389" s="4"/>
     </row>
-    <row r="390" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="390" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D390" s="2"/>
       <c r="E390" s="11"/>
       <c r="G390" s="4"/>
@@ -6448,7 +6278,7 @@
       <c r="P390" s="11"/>
       <c r="Q390" s="4"/>
     </row>
-    <row r="391" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="391" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D391" s="2"/>
       <c r="E391" s="11"/>
       <c r="G391" s="4"/>
@@ -6460,7 +6290,7 @@
       <c r="P391" s="11"/>
       <c r="Q391" s="4"/>
     </row>
-    <row r="392" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="392" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D392" s="2"/>
       <c r="E392" s="11"/>
       <c r="G392" s="4"/>
@@ -6472,7 +6302,7 @@
       <c r="P392" s="11"/>
       <c r="Q392" s="4"/>
     </row>
-    <row r="393" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="393" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D393" s="2"/>
       <c r="E393" s="11"/>
       <c r="G393" s="4"/>
@@ -6484,7 +6314,7 @@
       <c r="P393" s="11"/>
       <c r="Q393" s="4"/>
     </row>
-    <row r="394" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="394" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D394" s="2"/>
       <c r="E394" s="11"/>
       <c r="G394" s="4"/>
@@ -6496,7 +6326,7 @@
       <c r="P394" s="11"/>
       <c r="Q394" s="4"/>
     </row>
-    <row r="395" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="395" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D395" s="2"/>
       <c r="E395" s="11"/>
       <c r="G395" s="4"/>
@@ -6508,7 +6338,7 @@
       <c r="P395" s="11"/>
       <c r="Q395" s="4"/>
     </row>
-    <row r="396" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="396" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D396" s="2"/>
       <c r="E396" s="11"/>
       <c r="G396" s="4"/>
@@ -6520,7 +6350,7 @@
       <c r="P396" s="11"/>
       <c r="Q396" s="4"/>
     </row>
-    <row r="397" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="397" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D397" s="2"/>
       <c r="E397" s="11"/>
       <c r="G397" s="4"/>
@@ -6532,7 +6362,7 @@
       <c r="P397" s="11"/>
       <c r="Q397" s="4"/>
     </row>
-    <row r="398" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="398" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D398" s="2"/>
       <c r="E398" s="11"/>
       <c r="G398" s="4"/>
@@ -6544,7 +6374,7 @@
       <c r="P398" s="11"/>
       <c r="Q398" s="4"/>
     </row>
-    <row r="399" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="399" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D399" s="2"/>
       <c r="E399" s="11"/>
       <c r="G399" s="4"/>
@@ -6556,7 +6386,7 @@
       <c r="P399" s="11"/>
       <c r="Q399" s="4"/>
     </row>
-    <row r="400" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="400" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D400" s="2"/>
       <c r="E400" s="11"/>
       <c r="G400" s="4"/>
@@ -6568,7 +6398,7 @@
       <c r="P400" s="11"/>
       <c r="Q400" s="4"/>
     </row>
-    <row r="401" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="401" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D401" s="2"/>
       <c r="E401" s="11"/>
       <c r="G401" s="4"/>
@@ -6580,7 +6410,7 @@
       <c r="P401" s="11"/>
       <c r="Q401" s="4"/>
     </row>
-    <row r="402" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="402" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D402" s="2"/>
       <c r="E402" s="11"/>
       <c r="G402" s="4"/>
@@ -6592,7 +6422,7 @@
       <c r="P402" s="11"/>
       <c r="Q402" s="4"/>
     </row>
-    <row r="403" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="403" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D403" s="2"/>
       <c r="E403" s="11"/>
       <c r="G403" s="4"/>
@@ -6604,7 +6434,7 @@
       <c r="P403" s="11"/>
       <c r="Q403" s="4"/>
     </row>
-    <row r="404" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="404" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D404" s="2"/>
       <c r="E404" s="11"/>
       <c r="G404" s="4"/>
@@ -6616,7 +6446,7 @@
       <c r="P404" s="11"/>
       <c r="Q404" s="4"/>
     </row>
-    <row r="405" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="405" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D405" s="2"/>
       <c r="E405" s="11"/>
       <c r="G405" s="4"/>
@@ -6628,7 +6458,7 @@
       <c r="P405" s="11"/>
       <c r="Q405" s="4"/>
     </row>
-    <row r="406" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="406" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D406" s="2"/>
       <c r="E406" s="11"/>
       <c r="G406" s="4"/>
@@ -6640,7 +6470,7 @@
       <c r="P406" s="11"/>
       <c r="Q406" s="4"/>
     </row>
-    <row r="407" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="407" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D407" s="2"/>
       <c r="E407" s="11"/>
       <c r="G407" s="4"/>
@@ -6652,7 +6482,7 @@
       <c r="P407" s="11"/>
       <c r="Q407" s="4"/>
     </row>
-    <row r="408" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="408" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D408" s="2"/>
       <c r="E408" s="11"/>
       <c r="G408" s="4"/>
@@ -6664,7 +6494,7 @@
       <c r="P408" s="11"/>
       <c r="Q408" s="4"/>
     </row>
-    <row r="409" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="409" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D409" s="2"/>
       <c r="E409" s="11"/>
       <c r="G409" s="4"/>
@@ -6676,7 +6506,7 @@
       <c r="P409" s="11"/>
       <c r="Q409" s="4"/>
     </row>
-    <row r="410" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="410" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D410" s="2"/>
       <c r="E410" s="11"/>
       <c r="G410" s="4"/>
@@ -6688,7 +6518,7 @@
       <c r="P410" s="11"/>
       <c r="Q410" s="4"/>
     </row>
-    <row r="411" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="411" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D411" s="2"/>
       <c r="E411" s="11"/>
       <c r="G411" s="4"/>
@@ -6700,7 +6530,7 @@
       <c r="P411" s="11"/>
       <c r="Q411" s="4"/>
     </row>
-    <row r="412" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="412" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D412" s="2"/>
       <c r="E412" s="11"/>
       <c r="G412" s="4"/>
@@ -6712,7 +6542,7 @@
       <c r="P412" s="11"/>
       <c r="Q412" s="4"/>
     </row>
-    <row r="413" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="413" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D413" s="2"/>
       <c r="E413" s="11"/>
       <c r="G413" s="4"/>
@@ -6724,7 +6554,7 @@
       <c r="P413" s="11"/>
       <c r="Q413" s="4"/>
     </row>
-    <row r="414" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="414" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D414" s="2"/>
       <c r="E414" s="11"/>
       <c r="G414" s="4"/>
@@ -6736,7 +6566,7 @@
       <c r="P414" s="11"/>
       <c r="Q414" s="4"/>
     </row>
-    <row r="415" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="415" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D415" s="2"/>
       <c r="E415" s="11"/>
       <c r="G415" s="4"/>
@@ -6748,7 +6578,7 @@
       <c r="P415" s="11"/>
       <c r="Q415" s="4"/>
     </row>
-    <row r="416" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="416" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D416" s="2"/>
       <c r="E416" s="11"/>
       <c r="G416" s="4"/>
@@ -6760,7 +6590,7 @@
       <c r="P416" s="11"/>
       <c r="Q416" s="4"/>
     </row>
-    <row r="417" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="417" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D417" s="2"/>
       <c r="E417" s="11"/>
       <c r="G417" s="4"/>
@@ -6772,7 +6602,7 @@
       <c r="P417" s="11"/>
       <c r="Q417" s="4"/>
     </row>
-    <row r="418" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="418" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D418" s="2"/>
       <c r="E418" s="11"/>
       <c r="G418" s="4"/>
@@ -6784,7 +6614,7 @@
       <c r="P418" s="11"/>
       <c r="Q418" s="4"/>
     </row>
-    <row r="419" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="419" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D419" s="2"/>
       <c r="E419" s="11"/>
       <c r="G419" s="4"/>
@@ -6796,7 +6626,7 @@
       <c r="P419" s="11"/>
       <c r="Q419" s="4"/>
     </row>
-    <row r="420" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="420" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D420" s="2"/>
       <c r="E420" s="11"/>
       <c r="G420" s="4"/>
@@ -6808,7 +6638,7 @@
       <c r="P420" s="11"/>
       <c r="Q420" s="4"/>
     </row>
-    <row r="421" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="421" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D421" s="2"/>
       <c r="E421" s="11"/>
       <c r="G421" s="4"/>
@@ -6820,7 +6650,7 @@
       <c r="P421" s="11"/>
       <c r="Q421" s="4"/>
     </row>
-    <row r="422" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="422" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D422" s="2"/>
       <c r="E422" s="11"/>
       <c r="G422" s="4"/>
@@ -6832,7 +6662,7 @@
       <c r="P422" s="11"/>
       <c r="Q422" s="4"/>
     </row>
-    <row r="423" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="423" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D423" s="2"/>
       <c r="E423" s="11"/>
       <c r="G423" s="4"/>
@@ -6844,7 +6674,7 @@
       <c r="P423" s="11"/>
       <c r="Q423" s="4"/>
     </row>
-    <row r="424" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="424" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D424" s="2"/>
       <c r="E424" s="11"/>
       <c r="G424" s="4"/>
@@ -6856,7 +6686,7 @@
       <c r="P424" s="11"/>
       <c r="Q424" s="4"/>
     </row>
-    <row r="425" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="425" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D425" s="2"/>
       <c r="E425" s="11"/>
       <c r="G425" s="4"/>
@@ -6868,7 +6698,7 @@
       <c r="P425" s="11"/>
       <c r="Q425" s="4"/>
     </row>
-    <row r="426" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="426" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D426" s="2"/>
       <c r="E426" s="11"/>
       <c r="G426" s="4"/>
@@ -6880,7 +6710,7 @@
       <c r="P426" s="11"/>
       <c r="Q426" s="4"/>
     </row>
-    <row r="427" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="427" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D427" s="2"/>
       <c r="E427" s="11"/>
       <c r="G427" s="4"/>
@@ -6892,7 +6722,7 @@
       <c r="P427" s="11"/>
       <c r="Q427" s="4"/>
     </row>
-    <row r="428" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="428" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D428" s="2"/>
       <c r="E428" s="11"/>
       <c r="G428" s="4"/>
@@ -6904,7 +6734,7 @@
       <c r="P428" s="11"/>
       <c r="Q428" s="4"/>
     </row>
-    <row r="429" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="429" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D429" s="2"/>
       <c r="E429" s="11"/>
       <c r="G429" s="4"/>
@@ -6916,7 +6746,7 @@
       <c r="P429" s="11"/>
       <c r="Q429" s="4"/>
     </row>
-    <row r="430" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="430" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D430" s="2"/>
       <c r="E430" s="11"/>
       <c r="G430" s="4"/>
@@ -6928,7 +6758,7 @@
       <c r="P430" s="11"/>
       <c r="Q430" s="4"/>
     </row>
-    <row r="431" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="431" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D431" s="2"/>
       <c r="E431" s="11"/>
       <c r="G431" s="4"/>
@@ -6940,7 +6770,7 @@
       <c r="P431" s="11"/>
       <c r="Q431" s="4"/>
     </row>
-    <row r="432" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="432" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D432" s="2"/>
       <c r="E432" s="11"/>
       <c r="G432" s="4"/>
@@ -6952,7 +6782,7 @@
       <c r="P432" s="11"/>
       <c r="Q432" s="4"/>
     </row>
-    <row r="433" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="433" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D433" s="2"/>
       <c r="E433" s="11"/>
       <c r="G433" s="4"/>
@@ -6964,7 +6794,7 @@
       <c r="P433" s="11"/>
       <c r="Q433" s="4"/>
     </row>
-    <row r="434" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="434" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D434" s="2"/>
       <c r="E434" s="11"/>
       <c r="G434" s="4"/>
@@ -6976,7 +6806,7 @@
       <c r="P434" s="11"/>
       <c r="Q434" s="4"/>
     </row>
-    <row r="435" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="435" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D435" s="2"/>
       <c r="E435" s="11"/>
       <c r="G435" s="4"/>
@@ -6988,7 +6818,7 @@
       <c r="P435" s="11"/>
       <c r="Q435" s="4"/>
     </row>
-    <row r="436" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="436" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D436" s="2"/>
       <c r="E436" s="11"/>
       <c r="G436" s="4"/>
@@ -7000,7 +6830,7 @@
       <c r="P436" s="11"/>
       <c r="Q436" s="4"/>
     </row>
-    <row r="437" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="437" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D437" s="2"/>
       <c r="E437" s="11"/>
       <c r="G437" s="4"/>
@@ -7012,7 +6842,7 @@
       <c r="P437" s="11"/>
       <c r="Q437" s="4"/>
     </row>
-    <row r="438" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="438" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D438" s="2"/>
       <c r="E438" s="11"/>
       <c r="G438" s="4"/>
@@ -7024,7 +6854,7 @@
       <c r="P438" s="11"/>
       <c r="Q438" s="4"/>
     </row>
-    <row r="439" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="439" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D439" s="2"/>
       <c r="E439" s="11"/>
       <c r="G439" s="4"/>
@@ -7036,7 +6866,7 @@
       <c r="P439" s="11"/>
       <c r="Q439" s="4"/>
     </row>
-    <row r="440" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="440" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D440" s="2"/>
       <c r="E440" s="11"/>
       <c r="G440" s="4"/>
@@ -7048,7 +6878,7 @@
       <c r="P440" s="11"/>
       <c r="Q440" s="4"/>
     </row>
-    <row r="441" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="441" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D441" s="2"/>
       <c r="E441" s="11"/>
       <c r="G441" s="4"/>
@@ -7060,7 +6890,7 @@
       <c r="P441" s="11"/>
       <c r="Q441" s="4"/>
     </row>
-    <row r="442" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="442" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D442" s="2"/>
       <c r="E442" s="11"/>
       <c r="G442" s="4"/>
@@ -7072,7 +6902,7 @@
       <c r="P442" s="11"/>
       <c r="Q442" s="4"/>
     </row>
-    <row r="443" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="443" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D443" s="2"/>
       <c r="E443" s="11"/>
       <c r="G443" s="4"/>
@@ -7084,7 +6914,7 @@
       <c r="P443" s="11"/>
       <c r="Q443" s="4"/>
     </row>
-    <row r="444" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="444" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D444" s="2"/>
       <c r="E444" s="11"/>
       <c r="G444" s="4"/>
@@ -7094,7 +6924,7 @@
       <c r="N444" s="4"/>
       <c r="P444" s="11"/>
     </row>
-    <row r="445" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="445" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D445" s="2"/>
       <c r="E445" s="11"/>
       <c r="G445" s="4"/>
@@ -7104,7 +6934,7 @@
       <c r="N445" s="4"/>
       <c r="P445" s="11"/>
     </row>
-    <row r="446" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="446" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D446" s="2"/>
       <c r="E446" s="11"/>
       <c r="G446" s="4"/>
@@ -7114,7 +6944,7 @@
       <c r="N446" s="4"/>
       <c r="P446" s="11"/>
     </row>
-    <row r="447" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="447" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D447" s="2"/>
       <c r="E447" s="11"/>
       <c r="G447" s="4"/>
@@ -7124,7 +6954,7 @@
       <c r="N447" s="4"/>
       <c r="P447" s="11"/>
     </row>
-    <row r="448" spans="4:17" x14ac:dyDescent="0.3">
+    <row r="448" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D448" s="2"/>
       <c r="E448" s="11"/>
       <c r="G448" s="4"/>
@@ -7134,7 +6964,7 @@
       <c r="N448" s="4"/>
       <c r="P448" s="11"/>
     </row>
-    <row r="449" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="449" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D449" s="2"/>
       <c r="E449" s="11"/>
       <c r="G449" s="4"/>
@@ -7144,7 +6974,7 @@
       <c r="N449" s="4"/>
       <c r="P449" s="11"/>
     </row>
-    <row r="450" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="450" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D450" s="2"/>
       <c r="E450" s="11"/>
       <c r="G450" s="7"/>
@@ -7154,7 +6984,7 @@
       <c r="N450" s="4"/>
       <c r="P450" s="11"/>
     </row>
-    <row r="451" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="451" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D451" s="2"/>
       <c r="E451" s="11"/>
       <c r="G451" s="4"/>
@@ -7164,7 +6994,7 @@
       <c r="N451" s="4"/>
       <c r="P451" s="11"/>
     </row>
-    <row r="452" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="452" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D452" s="2"/>
       <c r="E452" s="11"/>
       <c r="G452" s="7"/>
@@ -7174,7 +7004,7 @@
       <c r="N452" s="4"/>
       <c r="P452" s="11"/>
     </row>
-    <row r="453" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="453" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D453" s="2"/>
       <c r="E453" s="11"/>
       <c r="G453" s="4"/>
@@ -7184,7 +7014,7 @@
       <c r="N453" s="4"/>
       <c r="P453" s="11"/>
     </row>
-    <row r="454" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="454" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D454" s="2"/>
       <c r="E454" s="11"/>
       <c r="G454" s="4"/>
@@ -7194,7 +7024,7 @@
       <c r="N454" s="4"/>
       <c r="P454" s="11"/>
     </row>
-    <row r="455" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="455" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D455" s="2"/>
       <c r="E455" s="11"/>
       <c r="G455" s="4"/>
@@ -7204,7 +7034,7 @@
       <c r="N455" s="4"/>
       <c r="P455" s="11"/>
     </row>
-    <row r="456" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="456" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D456" s="2"/>
       <c r="E456" s="11"/>
       <c r="G456" s="4"/>
@@ -7214,7 +7044,7 @@
       <c r="N456" s="4"/>
       <c r="P456" s="11"/>
     </row>
-    <row r="457" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="457" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D457" s="2"/>
       <c r="E457" s="11"/>
       <c r="G457" s="4"/>
@@ -7224,7 +7054,7 @@
       <c r="N457" s="4"/>
       <c r="P457" s="11"/>
     </row>
-    <row r="458" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="458" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D458" s="2"/>
       <c r="E458" s="11"/>
       <c r="G458" s="4"/>
@@ -7234,7 +7064,7 @@
       <c r="N458" s="4"/>
       <c r="P458" s="11"/>
     </row>
-    <row r="459" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="459" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D459" s="2"/>
       <c r="E459" s="11"/>
       <c r="G459" s="4"/>
@@ -7244,7 +7074,7 @@
       <c r="N459" s="4"/>
       <c r="P459" s="11"/>
     </row>
-    <row r="460" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="460" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D460" s="2"/>
       <c r="E460" s="11"/>
       <c r="G460" s="4"/>
@@ -7254,7 +7084,7 @@
       <c r="N460" s="4"/>
       <c r="P460" s="11"/>
     </row>
-    <row r="461" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="461" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D461" s="2"/>
       <c r="E461" s="11"/>
       <c r="G461" s="4"/>
@@ -7264,7 +7094,7 @@
       <c r="N461" s="4"/>
       <c r="P461" s="11"/>
     </row>
-    <row r="462" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="462" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D462" s="2"/>
       <c r="E462" s="11"/>
       <c r="G462" s="4"/>
@@ -7274,7 +7104,7 @@
       <c r="N462" s="4"/>
       <c r="P462" s="11"/>
     </row>
-    <row r="463" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="463" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D463" s="2"/>
       <c r="E463" s="11"/>
       <c r="G463" s="4"/>
@@ -7284,7 +7114,7 @@
       <c r="N463" s="4"/>
       <c r="P463" s="11"/>
     </row>
-    <row r="464" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="464" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D464" s="2"/>
       <c r="E464" s="11"/>
       <c r="G464" s="7"/>
@@ -7294,7 +7124,7 @@
       <c r="N464" s="4"/>
       <c r="P464" s="11"/>
     </row>
-    <row r="465" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="465" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D465" s="2"/>
       <c r="E465" s="11"/>
       <c r="G465" s="4"/>
@@ -7304,7 +7134,7 @@
       <c r="N465" s="4"/>
       <c r="P465" s="11"/>
     </row>
-    <row r="466" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="466" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D466" s="2"/>
       <c r="E466" s="11"/>
       <c r="G466" s="7"/>
@@ -7314,7 +7144,7 @@
       <c r="N466" s="4"/>
       <c r="P466" s="11"/>
     </row>
-    <row r="467" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="467" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D467" s="2"/>
       <c r="E467" s="11"/>
       <c r="G467" s="4"/>
@@ -7324,7 +7154,7 @@
       <c r="N467" s="4"/>
       <c r="P467" s="11"/>
     </row>
-    <row r="468" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="468" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D468" s="2"/>
       <c r="E468" s="11"/>
       <c r="G468" s="4"/>
@@ -7334,7 +7164,7 @@
       <c r="N468" s="4"/>
       <c r="P468" s="11"/>
     </row>
-    <row r="469" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="469" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D469" s="2"/>
       <c r="E469" s="11"/>
       <c r="G469" s="4"/>
@@ -7344,7 +7174,7 @@
       <c r="N469" s="4"/>
       <c r="P469" s="11"/>
     </row>
-    <row r="470" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="470" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D470" s="2"/>
       <c r="E470" s="11"/>
       <c r="G470" s="4"/>
@@ -7354,7 +7184,7 @@
       <c r="N470" s="4"/>
       <c r="P470" s="11"/>
     </row>
-    <row r="471" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="471" spans="4:16" x14ac:dyDescent="0.25">
       <c r="E471" s="11"/>
       <c r="G471" s="4"/>
       <c r="H471" s="4"/>
@@ -7363,7 +7193,7 @@
       <c r="N471" s="4"/>
       <c r="P471" s="11"/>
     </row>
-    <row r="472" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="472" spans="4:16" x14ac:dyDescent="0.25">
       <c r="E472" s="11"/>
       <c r="G472" s="4"/>
       <c r="H472" s="4"/>
@@ -7377,20 +7207,19 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC130FB4-2F37-4474-8AA2-B01341A5EC99}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="57.88671875" customWidth="1"/>
-    <col min="2" max="2" width="52.6640625" customWidth="1"/>
+    <col min="1" max="1" width="57.85546875" customWidth="1"/>
+    <col min="2" max="2" width="52.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>21</v>
       </c>
@@ -7398,7 +7227,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>23</v>
       </c>
@@ -7406,7 +7235,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>24</v>
       </c>
@@ -7414,7 +7243,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>25</v>
       </c>
@@ -7422,7 +7251,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>26</v>
       </c>
@@ -7438,13 +7267,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DB5104C-39AB-4F23-89F3-98B2DF5E239C}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48.6640625" customWidth="1"/>
-    <col min="2" max="2" width="66.88671875" customWidth="1"/>
+    <col min="1" max="1" width="48.7109375" customWidth="1"/>
+    <col min="2" max="2" width="66.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>21</v>
       </c>
@@ -7452,7 +7281,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>23</v>
       </c>
@@ -7460,7 +7289,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>25</v>
       </c>
@@ -7468,7 +7297,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>26</v>
       </c>
